--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,19 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA68280-0E01-42E0-B513-CF466FE4B0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346FA73E-98BB-43E5-A553-9289A40573FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId2"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId3"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId4"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId5"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId6"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId7"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId8"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId6"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId8"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId10"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="83">
   <si>
     <t>Dati originali</t>
   </si>
@@ -271,6 +280,27 @@
   </si>
   <si>
     <t>g=0.0003</t>
+  </si>
+  <si>
+    <t>n = 11 -&gt; 1.1 -&gt; 2</t>
+  </si>
+  <si>
+    <t>n = 11 -&gt; 2.2 -&gt; 3</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c1 </t>
+  </si>
+  <si>
+    <t>STDAUG</t>
+  </si>
+  <si>
+    <t>PARBS</t>
+  </si>
+  <si>
+    <t>ONLYMIN</t>
   </si>
 </sst>
 </file>
@@ -589,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -993,12 +1023,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="G18">
         <v>15.075757575757576</v>
       </c>
@@ -1030,8 +1060,779 @@
         <v>0.54711603167310885</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>16.333333333333332</v>
+      </c>
+      <c r="H19">
+        <v>3.5266839949164712</v>
+      </c>
+      <c r="I19">
+        <v>15</v>
+      </c>
+      <c r="J19">
+        <v>3.2596012026013246</v>
+      </c>
+      <c r="K19">
+        <v>25.611111111111111</v>
+      </c>
+      <c r="L19">
+        <v>3.3426951866885926</v>
+      </c>
+      <c r="N19">
+        <v>18.981481481481485</v>
+      </c>
+      <c r="O19">
+        <v>1.4706490546610054</v>
+      </c>
+      <c r="P19">
+        <v>1.6419753086419753</v>
+      </c>
+      <c r="Q19">
+        <v>0.9103787330478087</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>16.333333333333332</v>
+      </c>
+      <c r="H20">
+        <v>3.5266839949164712</v>
+      </c>
+      <c r="I20">
+        <v>15</v>
+      </c>
+      <c r="J20">
+        <v>3.2596012026013246</v>
+      </c>
+      <c r="K20">
+        <v>25.611111111111111</v>
+      </c>
+      <c r="L20">
+        <v>3.3426951866885926</v>
+      </c>
+      <c r="N20">
+        <v>18.981481481481485</v>
+      </c>
+      <c r="O20">
+        <v>1.4706490546610054</v>
+      </c>
+      <c r="P20">
+        <v>1.6419753086419753</v>
+      </c>
+      <c r="Q20">
+        <v>0.9103787330478087</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21">
+        <v>16.333333333333332</v>
+      </c>
+      <c r="H21">
+        <v>3.5266839949164712</v>
+      </c>
+      <c r="I21">
+        <v>15</v>
+      </c>
+      <c r="J21">
+        <v>3.2596012026013246</v>
+      </c>
+      <c r="K21">
+        <v>25.611111111111111</v>
+      </c>
+      <c r="L21">
+        <v>3.3426951866885926</v>
+      </c>
+      <c r="N21">
+        <v>18.981481481481485</v>
+      </c>
+      <c r="O21">
+        <v>1.4706490546610054</v>
+      </c>
+      <c r="P21">
+        <v>1.6419753086419753</v>
+      </c>
+      <c r="Q21">
+        <v>0.9103787330478087</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="I24">
+        <v>19.25</v>
+      </c>
+      <c r="J24">
+        <v>3.8405728739343039</v>
+      </c>
+      <c r="K24">
+        <v>35.75</v>
+      </c>
+      <c r="L24">
+        <v>6.3966136874651625</v>
+      </c>
+      <c r="N24">
+        <v>23.333333333333332</v>
+      </c>
+      <c r="O24">
+        <v>2.5531389540169025</v>
+      </c>
+      <c r="P24">
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="Q24">
+        <v>0.73842229768062817</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25">
+        <v>14.75</v>
+      </c>
+      <c r="H25">
+        <v>3.2015621187164243</v>
+      </c>
+      <c r="I25">
+        <v>18.625</v>
+      </c>
+      <c r="J25">
+        <v>1.0307764064044151</v>
+      </c>
+      <c r="K25">
+        <v>29.625</v>
+      </c>
+      <c r="L25">
+        <v>5.4524459343185301</v>
+      </c>
+      <c r="N25">
+        <v>21</v>
+      </c>
+      <c r="O25">
+        <v>1.5335748602046966</v>
+      </c>
+      <c r="P25">
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="Q25">
+        <v>1.113423519670919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27">
+        <v>15.9</v>
+      </c>
+      <c r="H27">
+        <v>1.8506755523321778</v>
+      </c>
+      <c r="I27">
+        <v>20</v>
+      </c>
+      <c r="J27">
+        <v>1.4577379737113252</v>
+      </c>
+      <c r="K27">
+        <v>32.9</v>
+      </c>
+      <c r="L27">
+        <v>3.150396800404673</v>
+      </c>
+      <c r="N27">
+        <v>22.933333333333334</v>
+      </c>
+      <c r="O27">
+        <v>0.72264944628929306</v>
+      </c>
+      <c r="P27">
+        <v>2.3444444444444441</v>
+      </c>
+      <c r="Q27">
+        <v>0.67059030564473054</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>16.5</v>
+      </c>
+      <c r="H30">
+        <v>1.2909944487358056</v>
+      </c>
+      <c r="I30">
+        <v>19.375</v>
+      </c>
+      <c r="J30">
+        <v>1.6007810593582121</v>
+      </c>
+      <c r="K30">
+        <v>28.5</v>
+      </c>
+      <c r="L30">
+        <v>1.6832508230603465</v>
+      </c>
+      <c r="N30">
+        <v>21.458333333333332</v>
+      </c>
+      <c r="O30">
+        <v>0.89623698916120498</v>
+      </c>
+      <c r="P30">
+        <v>1.7361111111111107</v>
+      </c>
+      <c r="Q30">
+        <v>0.19966535789673939</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>17.5</v>
+      </c>
+      <c r="H32">
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="I32">
+        <v>17</v>
+      </c>
+      <c r="J32">
+        <v>4.924428900898052</v>
+      </c>
+      <c r="K32">
+        <v>35.666666666666664</v>
+      </c>
+      <c r="L32">
+        <v>4.6457866215887762</v>
+      </c>
+      <c r="N32">
+        <v>23.388888888888889</v>
+      </c>
+      <c r="O32">
+        <v>2.3353166174426341</v>
+      </c>
+      <c r="P32">
+        <v>3.074074074074074</v>
+      </c>
+      <c r="Q32">
+        <v>1.1129614223197588</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="H33">
+        <v>7.0710678118654755</v>
+      </c>
+      <c r="I33">
+        <v>20.25</v>
+      </c>
+      <c r="J33">
+        <v>3.8890872965260113</v>
+      </c>
+      <c r="K33">
+        <v>41</v>
+      </c>
+      <c r="L33">
+        <v>12.727922061357855</v>
+      </c>
+      <c r="N33">
+        <v>28.583333333333332</v>
+      </c>
+      <c r="O33">
+        <v>7.8960257232497773</v>
+      </c>
+      <c r="P33">
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="Q33">
+        <v>1.3356461422412567</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>4.5825756949558398</v>
+      </c>
+      <c r="I36">
+        <v>17.166666666666668</v>
+      </c>
+      <c r="J36">
+        <v>4.1633319989322635</v>
+      </c>
+      <c r="K36">
+        <v>31</v>
+      </c>
+      <c r="L36">
+        <v>2.5</v>
+      </c>
+      <c r="N36">
+        <v>21.055555555555557</v>
+      </c>
+      <c r="O36">
+        <v>1.0046189622236181</v>
+      </c>
+      <c r="P36">
+        <v>2.8518518518518516</v>
+      </c>
+      <c r="Q36">
+        <v>0.40950637754622288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
+  <dimension ref="A2:AF9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>74</v>
+      </c>
+      <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="L4">
+        <v>63</v>
+      </c>
+      <c r="M4">
+        <v>37</v>
+      </c>
+      <c r="N4">
+        <v>45</v>
+      </c>
+      <c r="O4">
+        <v>55</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>23</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>13</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>41</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>13</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>4.2222222222222223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>80</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>45</v>
+      </c>
+      <c r="O7">
+        <v>55</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C7,D7)</f>
+        <v>23</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H7,I7)</f>
+        <v>13</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M7,N7)</f>
+        <v>41</v>
+      </c>
+      <c r="T7">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q7:S7)</f>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="U7">
+        <f>AVERAGE(Q7:Q9)</f>
+        <v>17.5</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.STDEV.S(Q7:Q9)</f>
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="W7">
+        <f>AVERAGE(R7:R9)</f>
+        <v>17</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.STDEV.S(R7:R9)</f>
+        <v>4.924428900898052</v>
+      </c>
+      <c r="Y7">
+        <f>AVERAGE(S7:S9)</f>
+        <v>35.666666666666664</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.STDEV.S(S7:S9)</f>
+        <v>4.6457866215887762</v>
+      </c>
+      <c r="AA7">
+        <f>AVERAGE(T7:T9)</f>
+        <v>23.388888888888889</v>
+      </c>
+      <c r="AB7">
+        <f>_xlfn.STDEV.S(T7:T9)</f>
+        <v>2.3353166174426341</v>
+      </c>
+      <c r="AC7">
+        <f>MIN(Q7:S7)</f>
+        <v>13</v>
+      </c>
+      <c r="AD7">
+        <f>(1/3)*(T7-AC7)</f>
+        <v>4.2222222222222223</v>
+      </c>
+      <c r="AE7">
+        <f>AVERAGE(AD7:AD9)</f>
+        <v>3.074074074074074</v>
+      </c>
+      <c r="AF7">
+        <f>_xlfn.STDEV.S(AD7:AD9)</f>
+        <v>1.1129614223197588</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>87</v>
+      </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>22</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>91</v>
+      </c>
+      <c r="L8">
+        <v>62</v>
+      </c>
+      <c r="M8">
+        <v>38</v>
+      </c>
+      <c r="N8">
+        <v>27</v>
+      </c>
+      <c r="O8">
+        <v>73</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" ref="AC8:AC9" si="4">MIN(Q8:S8)</f>
+        <v>15</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" ref="AD8:AD9" si="5">(1/3)*(T8-AC8)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>95</v>
+      </c>
+      <c r="G9">
+        <v>67</v>
+      </c>
+      <c r="H9">
+        <v>33</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>88</v>
+      </c>
+      <c r="L9">
+        <v>58</v>
+      </c>
+      <c r="M9">
+        <v>42</v>
+      </c>
+      <c r="N9">
+        <v>25</v>
+      </c>
+      <c r="O9">
+        <v>75</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>33.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>23.5</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -1040,10 +1841,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AH99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="28" max="28" width="23.21875" customWidth="1"/>
+    <col min="32" max="32" width="19.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1146,6 +1951,52 @@
       <c r="O3">
         <v>65</v>
       </c>
+      <c r="Q3">
+        <f>AVERAGE(C3,D3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="R3">
+        <f>AVERAGE(H3,I3)</f>
+        <v>21.5</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGE(M3,N3)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T3">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>23.5</v>
+      </c>
+      <c r="U3">
+        <f>MIN(Q3:S3)</f>
+        <v>18.5</v>
+      </c>
+      <c r="V3">
+        <f>(1/3)*(T3-U3)</f>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGE(T3:T12)</f>
+        <v>20.966666666666665</v>
+      </c>
+      <c r="X3">
+        <f>_xlfn.STDEV.S(T3:T12)</f>
+        <v>1.9764040172763697</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGE(V3:V12)</f>
+        <v>1.7388888888888889</v>
+      </c>
+      <c r="Z3">
+        <f>_xlfn.STDEV.S(V3:V12)</f>
+        <v>0.47071291114520358</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B4">
@@ -1184,6 +2035,48 @@
       <c r="O4">
         <v>67</v>
       </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q67" si="0">AVERAGE(C4,D4)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R67" si="1">AVERAGE(H4,I4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S67" si="2">AVERAGE(M4,N4)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T67" si="3">AVERAGE(Q4:S4)</f>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U67" si="4">MIN(Q4:S4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V67" si="5">(1/3)*(T4-U4)</f>
+        <v>1.2222222222222225</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4">
+        <v>18.981481481481485</v>
+      </c>
+      <c r="AD4">
+        <v>1.6419753086419753</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG4">
+        <v>18.981481481481485</v>
+      </c>
+      <c r="AH4">
+        <v>1.6419753086419753</v>
+      </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B5">
@@ -1222,6 +2115,48 @@
       <c r="O5">
         <v>73</v>
       </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC5">
+        <v>19.333333333333336</v>
+      </c>
+      <c r="AD5">
+        <v>1.7777777777777779</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG5">
+        <v>19.333333333333336</v>
+      </c>
+      <c r="AH5">
+        <v>1.7777777777777779</v>
+      </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B6">
@@ -1260,6 +2195,39 @@
       <c r="O6">
         <v>70</v>
       </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>1.8888888888888893</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG6">
+        <v>19.740740740740744</v>
+      </c>
+      <c r="AH6">
+        <v>1.8024691358024691</v>
+      </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B7">
@@ -1298,6 +2266,30 @@
       <c r="O7">
         <v>69</v>
       </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B8">
@@ -1336,6 +2328,30 @@
       <c r="O8">
         <v>74</v>
       </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>2.2777777777777772</v>
+      </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B9">
@@ -1374,6 +2390,30 @@
       <c r="O9">
         <v>78</v>
       </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>21.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>16.5</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B10">
@@ -1412,6 +2452,30 @@
       <c r="O10">
         <v>76</v>
       </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>1.8888888888888893</v>
+      </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B11">
@@ -1450,6 +2514,30 @@
       <c r="O11">
         <v>77</v>
       </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>1.2222222222222225</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B12">
@@ -1488,6 +2576,30 @@
       <c r="O12">
         <v>67</v>
       </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>1.0555555555555558</v>
+      </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1499,6 +2611,24 @@
       <c r="K14" t="s">
         <v>29</v>
       </c>
+      <c r="AB14" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B15">
@@ -1537,6 +2667,70 @@
       <c r="O15">
         <v>86</v>
       </c>
+      <c r="Q15">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+      <c r="W15">
+        <f>AVERAGE(T15:T23)</f>
+        <v>18.981481481481485</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.STDEV.S(T15:T23)</f>
+        <v>1.4706490546610054</v>
+      </c>
+      <c r="Y15">
+        <f>AVERAGE(V15:V23)</f>
+        <v>1.6419753086419753</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.STDEV.S(V15:V23)</f>
+        <v>0.9103787330478087</v>
+      </c>
+      <c r="AB15">
+        <f>AVERAGE(Q15:Q23)</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="AC15">
+        <f>_xlfn.STDEV.S(Q15:Q23)</f>
+        <v>3.5266839949164712</v>
+      </c>
+      <c r="AD15">
+        <f>AVERAGE(R15:R23)</f>
+        <v>15</v>
+      </c>
+      <c r="AE15">
+        <f>_xlfn.STDEV.S(R15:R23)</f>
+        <v>3.2596012026013246</v>
+      </c>
+      <c r="AF15">
+        <f>AVERAGE(S15:S23)</f>
+        <v>25.611111111111111</v>
+      </c>
+      <c r="AG15">
+        <f>_xlfn.STDEV.S(S15:S23)</f>
+        <v>3.3426951866885926</v>
+      </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B16">
@@ -1575,8 +2769,32 @@
       <c r="O16">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="5"/>
+        <v>0.11111111111111072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>84</v>
       </c>
@@ -1613,8 +2831,32 @@
       <c r="O17">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q17">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="5"/>
+        <v>3.6111111111111107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>81</v>
       </c>
@@ -1651,8 +2893,32 @@
       <c r="O18">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="3"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="5"/>
+        <v>1.2222222222222225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>91</v>
       </c>
@@ -1689,8 +2955,32 @@
       <c r="O19">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q19">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="3"/>
+        <v>16.833333333333332</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>91</v>
       </c>
@@ -1727,8 +3017,32 @@
       <c r="O20">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q20">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="3"/>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="5"/>
+        <v>1.8888888888888893</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>88</v>
       </c>
@@ -1765,8 +3079,32 @@
       <c r="O21">
         <v>71</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q21">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="5"/>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>91</v>
       </c>
@@ -1803,8 +3141,32 @@
       <c r="O22">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="3"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>84</v>
       </c>
@@ -1841,8 +3203,32 @@
       <c r="O23">
         <v>79</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="3"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="5"/>
+        <v>1.444444444444444</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1853,7 +3239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>96</v>
       </c>
@@ -1890,8 +3276,48 @@
       <c r="O26">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="5"/>
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="W26">
+        <f>AVERAGE(T26:T28)</f>
+        <v>20.111111111111111</v>
+      </c>
+      <c r="X26">
+        <f>_xlfn.STDEV.S(T26:T28)</f>
+        <v>0.94770678384622253</v>
+      </c>
+      <c r="Y26">
+        <f>AVERAGE(V26:V28)</f>
+        <v>2.4259259259259256</v>
+      </c>
+      <c r="Z26">
+        <f>_xlfn.STDEV.S(V26:V28)</f>
+        <v>0.56199966316642636</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>84</v>
       </c>
@@ -1928,8 +3354,32 @@
       <c r="O27">
         <v>78</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="3"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>87</v>
       </c>
@@ -1966,8 +3416,32 @@
       <c r="O28">
         <v>75</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="3"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="5"/>
+        <v>2.7222222222222223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1978,7 +3452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>80</v>
       </c>
@@ -2015,8 +3489,48 @@
       <c r="O31">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q31">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="3"/>
+        <v>21.5</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="5"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="W31">
+        <f>AVERAGE(T31:T39)</f>
+        <v>19.962962962962965</v>
+      </c>
+      <c r="X31">
+        <f>_xlfn.STDEV.S(T31:T39)</f>
+        <v>2.2060173040298174</v>
+      </c>
+      <c r="Y31">
+        <f>AVERAGE(V31:V39)</f>
+        <v>1.7098765432098761</v>
+      </c>
+      <c r="Z31">
+        <f>_xlfn.STDEV.S(V31:V39)</f>
+        <v>0.42833457430445854</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>80</v>
       </c>
@@ -2053,8 +3567,32 @@
       <c r="O32">
         <v>72</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q32">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="3"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="5"/>
+        <v>1.7222222222222225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>88</v>
       </c>
@@ -2091,8 +3629,32 @@
       <c r="O33">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q33">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>88</v>
       </c>
@@ -2129,8 +3691,32 @@
       <c r="O34">
         <v>74</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q34">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>94</v>
       </c>
@@ -2167,8 +3753,32 @@
       <c r="O35">
         <v>76</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q35">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="3"/>
+        <v>16.5</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="5"/>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>87</v>
       </c>
@@ -2205,8 +3815,32 @@
       <c r="O36">
         <v>75</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>92</v>
       </c>
@@ -2243,8 +3877,32 @@
       <c r="O37">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q37">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="5"/>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>91</v>
       </c>
@@ -2281,8 +3939,32 @@
       <c r="O38">
         <v>71</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q38">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="2"/>
+        <v>24.5</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="3"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>89</v>
       </c>
@@ -2319,8 +4001,32 @@
       <c r="O39">
         <v>79</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q39">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -2331,7 +4037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>87</v>
       </c>
@@ -2368,8 +4074,48 @@
       <c r="O42">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q42">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="3"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="5"/>
+        <v>1.1111111111111107</v>
+      </c>
+      <c r="W42">
+        <f>AVERAGE(T42:T50)</f>
+        <v>20.222222222222221</v>
+      </c>
+      <c r="X42">
+        <f>_xlfn.STDEV.S(T42:T50)</f>
+        <v>2.0395397084200693</v>
+      </c>
+      <c r="Y42">
+        <f>AVERAGE(V42:V50)</f>
+        <v>1.8703703703703698</v>
+      </c>
+      <c r="Z42">
+        <f>_xlfn.STDEV.S(V42:V50)</f>
+        <v>0.60984717778056097</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>91</v>
       </c>
@@ -2406,8 +4152,32 @@
       <c r="O43">
         <v>69</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q43">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="5"/>
+        <v>1.3888888888888893</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>88</v>
       </c>
@@ -2444,8 +4214,32 @@
       <c r="O44">
         <v>76</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q44">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666665</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>88</v>
       </c>
@@ -2482,8 +4276,32 @@
       <c r="O45">
         <v>70</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q45">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>82</v>
       </c>
@@ -2520,8 +4338,32 @@
       <c r="O46">
         <v>75</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q46">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="3"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="5"/>
+        <v>2.4444444444444438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>85</v>
       </c>
@@ -2558,8 +4400,32 @@
       <c r="O47">
         <v>83</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q47">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="3"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V47">
+        <f t="shared" si="5"/>
+        <v>1.944444444444444</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>89</v>
       </c>
@@ -2596,8 +4462,32 @@
       <c r="O48">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q48">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="5"/>
+        <v>3.1666666666666665</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>91</v>
       </c>
@@ -2634,8 +4524,32 @@
       <c r="O49">
         <v>82</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q49">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="3"/>
+        <v>16.833333333333332</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>89</v>
       </c>
@@ -2672,8 +4586,32 @@
       <c r="O50">
         <v>82</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q50">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>73</v>
       </c>
@@ -2684,7 +4622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>83</v>
       </c>
@@ -2721,8 +4659,48 @@
       <c r="O53">
         <v>73</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q53">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="2"/>
+        <v>28.5</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="W53">
+        <f>AVERAGE(T53:T54)</f>
+        <v>19.333333333333336</v>
+      </c>
+      <c r="X53">
+        <f>_xlfn.STDEV.S(T53,T54)</f>
+        <v>0.94280904158206247</v>
+      </c>
+      <c r="Y53">
+        <f>AVERAGE(V53:V54)</f>
+        <v>1.7777777777777779</v>
+      </c>
+      <c r="Z53">
+        <f>_xlfn.STDEV.S(V53,V54)</f>
+        <v>0.15713484026367761</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>85</v>
       </c>
@@ -2759,8 +4737,32 @@
       <c r="O54">
         <v>83</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q54">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="2"/>
+        <v>28.5</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="3"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="5"/>
+        <v>1.8888888888888893</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>74</v>
       </c>
@@ -2771,7 +4773,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>85</v>
       </c>
@@ -2808,8 +4810,48 @@
       <c r="O57">
         <v>85</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q57">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U57">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V57">
+        <f t="shared" si="5"/>
+        <v>2.0555555555555558</v>
+      </c>
+      <c r="W57">
+        <f>AVERAGE(T57:T63)</f>
+        <v>21.190476190476193</v>
+      </c>
+      <c r="X57">
+        <f>_xlfn.STDEV.S(T57:T63)</f>
+        <v>1.6027423588284766</v>
+      </c>
+      <c r="Y57">
+        <f>AVERAGE(V57:V63)</f>
+        <v>1.8015873015873012</v>
+      </c>
+      <c r="Z57">
+        <f>_xlfn.STDEV.S(V57:V63)</f>
+        <v>0.43254575016374236</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>76</v>
       </c>
@@ -2846,8 +4888,32 @@
       <c r="O58">
         <v>82</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q58">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="U58">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V58">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>83</v>
       </c>
@@ -2884,8 +4950,32 @@
       <c r="O59">
         <v>64</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q59">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T59">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U59">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V59">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>82</v>
       </c>
@@ -2922,8 +5012,32 @@
       <c r="O60">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q60">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="2"/>
+        <v>33.5</v>
+      </c>
+      <c r="T60">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="U60">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V60">
+        <f t="shared" si="5"/>
+        <v>1.944444444444444</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>87</v>
       </c>
@@ -2960,8 +5074,32 @@
       <c r="O61">
         <v>73</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q61">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R61">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S61">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T61">
+        <f t="shared" si="3"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U61">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V61">
+        <f t="shared" si="5"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>92</v>
       </c>
@@ -2998,8 +5136,32 @@
       <c r="O62">
         <v>76</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q62">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="R62">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S62">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T62">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="U62">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="V62">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>84</v>
       </c>
@@ -3036,8 +5198,32 @@
       <c r="O63">
         <v>79</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q63">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R63">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S63">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T63">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U63">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="V63">
+        <f t="shared" si="5"/>
+        <v>1.1111111111111107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>35</v>
       </c>
@@ -3048,7 +5234,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>85</v>
       </c>
@@ -3085,8 +5271,48 @@
       <c r="O66">
         <v>87</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q66">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R66">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S66">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="T66">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="U66">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V66">
+        <f t="shared" si="5"/>
+        <v>1.2777777777777772</v>
+      </c>
+      <c r="W66">
+        <f>AVERAGE(T66:T68)</f>
+        <v>20.222222222222221</v>
+      </c>
+      <c r="X66">
+        <f>_xlfn.STDEV.S(T66:T68)</f>
+        <v>1.8584142981864142</v>
+      </c>
+      <c r="Y66">
+        <f>AVERAGE(V66:V68)</f>
+        <v>1.7962962962962958</v>
+      </c>
+      <c r="Z66">
+        <f>_xlfn.STDEV.S(V66:V68)</f>
+        <v>0.52802138627345419</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>90</v>
       </c>
@@ -3123,8 +5349,32 @@
       <c r="O67">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q67">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S67">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="T67">
+        <f t="shared" si="3"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U67">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="V67">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>84</v>
       </c>
@@ -3161,8 +5411,32 @@
       <c r="O68">
         <v>84</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q68">
+        <f t="shared" ref="Q68:Q99" si="6">AVERAGE(C68,D68)</f>
+        <v>14.5</v>
+      </c>
+      <c r="R68">
+        <f t="shared" ref="R68:R99" si="7">AVERAGE(H68,I68)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S68">
+        <f t="shared" ref="S68:S99" si="8">AVERAGE(M68,N68)</f>
+        <v>31.5</v>
+      </c>
+      <c r="T68">
+        <f t="shared" ref="T68:T99" si="9">AVERAGE(Q68:S68)</f>
+        <v>19.5</v>
+      </c>
+      <c r="U68">
+        <f t="shared" ref="U68:U99" si="10">MIN(Q68:S68)</f>
+        <v>12.5</v>
+      </c>
+      <c r="V68">
+        <f t="shared" ref="V68:V99" si="11">(1/3)*(T68-U68)</f>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>36</v>
       </c>
@@ -3173,7 +5447,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>89</v>
       </c>
@@ -3210,8 +5484,48 @@
       <c r="O71">
         <v>65</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q71">
+        <f t="shared" si="6"/>
+        <v>18.5</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S71">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T71">
+        <f t="shared" si="9"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U71">
+        <f t="shared" si="10"/>
+        <v>17.5</v>
+      </c>
+      <c r="V71">
+        <f t="shared" si="11"/>
+        <v>1.444444444444444</v>
+      </c>
+      <c r="W71">
+        <f>AVERAGE(T71:T80)</f>
+        <v>20.516666666666662</v>
+      </c>
+      <c r="X71">
+        <f>_xlfn.STDEV.S(T71:T80)</f>
+        <v>1.0983995090500904</v>
+      </c>
+      <c r="Y71">
+        <f>AVERAGE(V71:V80)</f>
+        <v>1.838888888888889</v>
+      </c>
+      <c r="Z71">
+        <f>_xlfn.STDEV.S(V71:V80)</f>
+        <v>0.62220568761099626</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>86</v>
       </c>
@@ -3248,8 +5562,32 @@
       <c r="O72">
         <v>73</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q72">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="7"/>
+        <v>19.5</v>
+      </c>
+      <c r="S72">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T72">
+        <f t="shared" si="9"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U72">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="V72">
+        <f t="shared" si="11"/>
+        <v>1.944444444444444</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>88</v>
       </c>
@@ -3286,8 +5624,32 @@
       <c r="O73">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q73">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="R73">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S73">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T73">
+        <f t="shared" si="9"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U73">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="V73">
+        <f t="shared" si="11"/>
+        <v>2.3888888888888893</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>82</v>
       </c>
@@ -3324,8 +5686,32 @@
       <c r="O74">
         <v>83</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q74">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T74">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="U74">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="V74">
+        <f t="shared" si="11"/>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>90</v>
       </c>
@@ -3362,8 +5748,32 @@
       <c r="O75">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q75">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R75">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S75">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="9"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U75">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="V75">
+        <f t="shared" si="11"/>
+        <v>1.944444444444444</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>90</v>
       </c>
@@ -3400,8 +5810,32 @@
       <c r="O76">
         <v>71</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q76">
+        <f t="shared" si="6"/>
+        <v>13.5</v>
+      </c>
+      <c r="R76">
+        <f t="shared" si="7"/>
+        <v>14.5</v>
+      </c>
+      <c r="S76">
+        <f t="shared" si="8"/>
+        <v>26.5</v>
+      </c>
+      <c r="T76">
+        <f t="shared" si="9"/>
+        <v>18.166666666666668</v>
+      </c>
+      <c r="U76">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V76">
+        <f t="shared" si="11"/>
+        <v>1.5555555555555558</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>86</v>
       </c>
@@ -3438,8 +5872,32 @@
       <c r="O77">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q77">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R77">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S77">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T77">
+        <f t="shared" si="9"/>
+        <v>20.5</v>
+      </c>
+      <c r="U77">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="V77">
+        <f t="shared" si="11"/>
+        <v>1.6666666666666665</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>85</v>
       </c>
@@ -3476,8 +5934,32 @@
       <c r="O78">
         <v>79</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q78">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="R78">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S78">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T78">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="U78">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V78">
+        <f t="shared" si="11"/>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>82</v>
       </c>
@@ -3514,8 +5996,32 @@
       <c r="O79">
         <v>79</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q79">
+        <f t="shared" si="6"/>
+        <v>19.5</v>
+      </c>
+      <c r="R79">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S79">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="T79">
+        <f t="shared" si="9"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="U79">
+        <f t="shared" si="10"/>
+        <v>18.5</v>
+      </c>
+      <c r="V79">
+        <f t="shared" si="11"/>
+        <v>0.38888888888888928</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>88</v>
       </c>
@@ -3552,8 +6058,32 @@
       <c r="O80">
         <v>65</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q80">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="R80">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S80">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="T80">
+        <f t="shared" si="9"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U80">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V80">
+        <f t="shared" si="11"/>
+        <v>2.3888888888888893</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>37</v>
       </c>
@@ -3564,7 +6094,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>90</v>
       </c>
@@ -3601,8 +6131,48 @@
       <c r="O83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q83">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S83">
+        <f t="shared" si="8"/>
+        <v>29</v>
+      </c>
+      <c r="T83">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="U83">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="V83">
+        <f t="shared" si="11"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="W83">
+        <f>AVERAGE(T83:T88)</f>
+        <v>21.222222222222221</v>
+      </c>
+      <c r="X83">
+        <f>_xlfn.STDEV.S(T83:T88)</f>
+        <v>1.5190152755674997</v>
+      </c>
+      <c r="Y83">
+        <f>AVERAGE(V83:V88)</f>
+        <v>1.8240740740740737</v>
+      </c>
+      <c r="Z83">
+        <f>_xlfn.STDEV.S(V83:V88)</f>
+        <v>0.58522620578213735</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>83</v>
       </c>
@@ -3639,8 +6209,32 @@
       <c r="O84">
         <v>74</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q84">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R84">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S84">
+        <f t="shared" si="8"/>
+        <v>27.5</v>
+      </c>
+      <c r="T84">
+        <f t="shared" si="9"/>
+        <v>19.5</v>
+      </c>
+      <c r="U84">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="V84">
+        <f t="shared" si="11"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>89</v>
       </c>
@@ -3677,8 +6271,32 @@
       <c r="O85">
         <v>64</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q85">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="R85">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="S85">
+        <f t="shared" si="8"/>
+        <v>34</v>
+      </c>
+      <c r="T85">
+        <f t="shared" si="9"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U85">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="V85">
+        <f t="shared" si="11"/>
+        <v>2.7777777777777772</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>93</v>
       </c>
@@ -3715,8 +6333,32 @@
       <c r="O86">
         <v>62</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q86">
+        <f t="shared" si="6"/>
+        <v>19.5</v>
+      </c>
+      <c r="R86">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S86">
+        <f t="shared" si="8"/>
+        <v>33.5</v>
+      </c>
+      <c r="T86">
+        <f t="shared" si="9"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U86">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="V86">
+        <f t="shared" si="11"/>
+        <v>2.1111111111111107</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>85</v>
       </c>
@@ -3753,8 +6395,32 @@
       <c r="O87">
         <v>77</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q87">
+        <f t="shared" si="6"/>
+        <v>18.5</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="7"/>
+        <v>21.5</v>
+      </c>
+      <c r="S87">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="9"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="10"/>
+        <v>18.5</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="11"/>
+        <v>1.0555555555555558</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>88</v>
       </c>
@@ -3791,8 +6457,32 @@
       <c r="O88">
         <v>73</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q88">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R88">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S88">
+        <f t="shared" si="8"/>
+        <v>33</v>
+      </c>
+      <c r="T88">
+        <f t="shared" si="9"/>
+        <v>22.5</v>
+      </c>
+      <c r="U88">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="V88">
+        <f t="shared" si="11"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>75</v>
       </c>
@@ -3803,7 +6493,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>85</v>
       </c>
@@ -3840,8 +6530,48 @@
       <c r="O91">
         <v>75</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q91">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R91">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S91">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="T91">
+        <f t="shared" si="9"/>
+        <v>20.5</v>
+      </c>
+      <c r="U91">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V91">
+        <f t="shared" si="11"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="W91">
+        <f>AVERAGE(T91:T99)</f>
+        <v>19.740740740740744</v>
+      </c>
+      <c r="X91">
+        <f>_xlfn.STDEV.S(T91:T99)</f>
+        <v>1.7482354419510628</v>
+      </c>
+      <c r="Y91">
+        <f>AVERAGE(V91:V99)</f>
+        <v>1.8024691358024691</v>
+      </c>
+      <c r="Z91">
+        <f>_xlfn.STDEV.S(V91:V99)</f>
+        <v>0.36441978989174728</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>82</v>
       </c>
@@ -3878,8 +6608,32 @@
       <c r="O92">
         <v>69</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q92">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S92">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T92">
+        <f t="shared" si="9"/>
+        <v>22.5</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="V92">
+        <f t="shared" si="11"/>
+        <v>2.1666666666666665</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>84</v>
       </c>
@@ -3916,8 +6670,32 @@
       <c r="O93">
         <v>77</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q93">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S93">
+        <f t="shared" si="8"/>
+        <v>26.5</v>
+      </c>
+      <c r="T93">
+        <f t="shared" si="9"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U93">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="V93">
+        <f t="shared" si="11"/>
+        <v>1.444444444444444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>93</v>
       </c>
@@ -3954,8 +6732,32 @@
       <c r="O94">
         <v>77</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q94">
+        <f t="shared" si="6"/>
+        <v>12.5</v>
+      </c>
+      <c r="R94">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S94">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="T94">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="U94">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="V94">
+        <f t="shared" si="11"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>85</v>
       </c>
@@ -3992,8 +6794,32 @@
       <c r="O95">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q95">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="S95">
+        <f t="shared" si="8"/>
+        <v>22.5</v>
+      </c>
+      <c r="T95">
+        <f t="shared" si="9"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="U95">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="V95">
+        <f t="shared" si="11"/>
+        <v>1.6111111111111107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>87</v>
       </c>
@@ -4030,8 +6856,32 @@
       <c r="O96">
         <v>80</v>
       </c>
-    </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="Q96">
+        <f t="shared" si="6"/>
+        <v>14.5</v>
+      </c>
+      <c r="R96">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S96">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T96">
+        <f t="shared" si="9"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U96">
+        <f t="shared" si="10"/>
+        <v>14.5</v>
+      </c>
+      <c r="V96">
+        <f t="shared" si="11"/>
+        <v>2.1111111111111107</v>
+      </c>
+    </row>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>84</v>
       </c>
@@ -4068,8 +6918,32 @@
       <c r="O97">
         <v>82</v>
       </c>
-    </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="Q97">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
+      <c r="R97">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S97">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="T97">
+        <f t="shared" si="9"/>
+        <v>19.5</v>
+      </c>
+      <c r="U97">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="V97">
+        <f t="shared" si="11"/>
+        <v>1.1666666666666665</v>
+      </c>
+    </row>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>89</v>
       </c>
@@ -4106,8 +6980,32 @@
       <c r="O98">
         <v>89</v>
       </c>
-    </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="Q98">
+        <f t="shared" si="6"/>
+        <v>11.5</v>
+      </c>
+      <c r="R98">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S98">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T98">
+        <f t="shared" si="9"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U98">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="V98">
+        <f t="shared" si="11"/>
+        <v>2.1111111111111107</v>
+      </c>
+    </row>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>87</v>
       </c>
@@ -4143,6 +7041,30 @@
       </c>
       <c r="O99">
         <v>68</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R99">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S99">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T99">
+        <f t="shared" si="9"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U99">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="V99">
+        <f t="shared" si="11"/>
+        <v>1.6111111111111107</v>
       </c>
     </row>
   </sheetData>
@@ -4150,7 +7072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6308,7 +9230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6879,7 +9801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8602,7 +11524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AL36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8797,27 +11719,27 @@
         <v>91</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q35" si="0">AVERAGE(C4,D4)</f>
+        <f t="shared" ref="Q4:Q27" si="0">AVERAGE(C4,D4)</f>
         <v>19.5</v>
       </c>
       <c r="R4">
-        <f t="shared" ref="R4:R35" si="1">AVERAGE(H4,I4)</f>
+        <f t="shared" ref="R4:R27" si="1">AVERAGE(H4,I4)</f>
         <v>28.5</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4:S35" si="2">AVERAGE(M4,N4)</f>
+        <f t="shared" ref="S4:S27" si="2">AVERAGE(M4,N4)</f>
         <v>37.5</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T35" si="3">AVERAGE(Q4:S4)</f>
+        <f t="shared" ref="T4:T27" si="3">AVERAGE(Q4:S4)</f>
         <v>28.5</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U35" si="4">MIN(Q4:S4)</f>
+        <f t="shared" ref="U4:U27" si="4">MIN(Q4:S4)</f>
         <v>19.5</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4:V35" si="5">(1/3)*(T4-U4)</f>
+        <f t="shared" ref="V4:V27" si="5">(1/3)*(T4-U4)</f>
         <v>3</v>
       </c>
       <c r="AB4" t="s">
@@ -9923,27 +12845,27 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <f>AVERAGE(C31,D31)</f>
+        <f t="shared" ref="Q31:Q36" si="6">AVERAGE(C31,D31)</f>
         <v>23.5</v>
       </c>
       <c r="R31">
-        <f>AVERAGE(H31,I31)</f>
+        <f t="shared" ref="R31:R36" si="7">AVERAGE(H31,I31)</f>
         <v>28.5</v>
       </c>
       <c r="S31">
-        <f>AVERAGE(M31,N31)</f>
+        <f t="shared" ref="S31:S36" si="8">AVERAGE(M31,N31)</f>
         <v>46.5</v>
       </c>
       <c r="T31">
-        <f>AVERAGE(Q31:S31)</f>
+        <f t="shared" ref="T31:T36" si="9">AVERAGE(Q31:S31)</f>
         <v>32.833333333333336</v>
       </c>
       <c r="U31">
-        <f>MIN(Q31:S31)</f>
+        <f t="shared" ref="U31:U36" si="10">MIN(Q31:S31)</f>
         <v>23.5</v>
       </c>
       <c r="V31">
-        <f>(1/3)*(T31-U31)</f>
+        <f t="shared" ref="V31:V36" si="11">(1/3)*(T31-U31)</f>
         <v>3.1111111111111116</v>
       </c>
       <c r="W31">
@@ -10001,27 +12923,27 @@
         <v>98</v>
       </c>
       <c r="Q32">
-        <f>AVERAGE(C32,D32)</f>
+        <f t="shared" si="6"/>
         <v>24.5</v>
       </c>
       <c r="R32">
-        <f>AVERAGE(H32,I32)</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="S32">
-        <f>AVERAGE(M32,N32)</f>
+        <f t="shared" si="8"/>
         <v>39</v>
       </c>
       <c r="T32">
-        <f>AVERAGE(Q32:S32)</f>
+        <f t="shared" si="9"/>
         <v>30.833333333333332</v>
       </c>
       <c r="U32">
-        <f>MIN(Q32:S32)</f>
+        <f t="shared" si="10"/>
         <v>24.5</v>
       </c>
       <c r="V32">
-        <f>(1/3)*(T32-U32)</f>
+        <f t="shared" si="11"/>
         <v>2.1111111111111107</v>
       </c>
     </row>
@@ -10063,27 +12985,27 @@
         <v>88</v>
       </c>
       <c r="Q33">
-        <f>AVERAGE(C33,D33)</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="R33">
-        <f>AVERAGE(H33,I33)</f>
+        <f t="shared" si="7"/>
         <v>20.5</v>
       </c>
       <c r="S33">
-        <f>AVERAGE(M33,N33)</f>
+        <f t="shared" si="8"/>
         <v>38.5</v>
       </c>
       <c r="T33">
-        <f>AVERAGE(Q33:S33)</f>
+        <f t="shared" si="9"/>
         <v>26.333333333333332</v>
       </c>
       <c r="U33">
-        <f>MIN(Q33:S33)</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="V33">
-        <f>(1/3)*(T33-U33)</f>
+        <f t="shared" si="11"/>
         <v>2.1111111111111107</v>
       </c>
     </row>
@@ -10125,27 +13047,27 @@
         <v>93</v>
       </c>
       <c r="Q34">
-        <f>AVERAGE(C34,D34)</f>
+        <f t="shared" si="6"/>
         <v>15.5</v>
       </c>
       <c r="R34">
-        <f>AVERAGE(H34,I34)</f>
+        <f t="shared" si="7"/>
         <v>24.5</v>
       </c>
       <c r="S34">
-        <f>AVERAGE(M34,N34)</f>
+        <f t="shared" si="8"/>
         <v>39.5</v>
       </c>
       <c r="T34">
-        <f>AVERAGE(Q34:S34)</f>
+        <f t="shared" si="9"/>
         <v>26.5</v>
       </c>
       <c r="U34">
-        <f>MIN(Q34:S34)</f>
+        <f t="shared" si="10"/>
         <v>15.5</v>
       </c>
       <c r="V34">
-        <f>(1/3)*(T34-U34)</f>
+        <f t="shared" si="11"/>
         <v>3.6666666666666665</v>
       </c>
     </row>
@@ -10187,27 +13109,27 @@
         <v>96</v>
       </c>
       <c r="Q35">
-        <f>AVERAGE(C35,D35)</f>
+        <f t="shared" si="6"/>
         <v>22.5</v>
       </c>
       <c r="R35">
-        <f>AVERAGE(H35,I35)</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="S35">
-        <f>AVERAGE(M35,N35)</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="T35">
-        <f>AVERAGE(Q35:S35)</f>
+        <f t="shared" si="9"/>
         <v>30.166666666666668</v>
       </c>
       <c r="U35">
-        <f>MIN(Q35:S35)</f>
+        <f t="shared" si="10"/>
         <v>22.5</v>
       </c>
       <c r="V35">
-        <f>(1/3)*(T35-U35)</f>
+        <f t="shared" si="11"/>
         <v>2.5555555555555558</v>
       </c>
     </row>
@@ -10249,27 +13171,27 @@
         <v>88</v>
       </c>
       <c r="Q36">
-        <f>AVERAGE(C36,D36)</f>
+        <f t="shared" si="6"/>
         <v>19.5</v>
       </c>
       <c r="R36">
-        <f>AVERAGE(H36,I36)</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="S36">
-        <f>AVERAGE(M36,N36)</f>
+        <f t="shared" si="8"/>
         <v>34.5</v>
       </c>
       <c r="T36">
-        <f>AVERAGE(Q36:S36)</f>
+        <f t="shared" si="9"/>
         <v>24.333333333333332</v>
       </c>
       <c r="U36">
-        <f>MIN(Q36:S36)</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="V36">
-        <f>(1/3)*(T36-U36)</f>
+        <f t="shared" si="11"/>
         <v>1.7777777777777772</v>
       </c>
     </row>
@@ -10278,7 +13200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:U106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10811,7 +13733,7 @@
       <c r="L14">
         <v>15</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14">
         <v>16</v>
       </c>
       <c r="N14">
@@ -11668,7 +14590,7 @@
         <v>95</v>
       </c>
       <c r="F39">
-        <f>AVERAGE(B39,C39)</f>
+        <f t="shared" ref="F39:F71" si="4">AVERAGE(B39,C39)</f>
         <v>18.5</v>
       </c>
       <c r="H39">
@@ -11694,7 +14616,7 @@
         <v>90</v>
       </c>
       <c r="F40">
-        <f>AVERAGE(B40,C40)</f>
+        <f t="shared" si="4"/>
         <v>24.5</v>
       </c>
     </row>
@@ -11712,7 +14634,7 @@
         <v>95</v>
       </c>
       <c r="F41">
-        <f>AVERAGE(B41,C41)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
     </row>
@@ -11730,7 +14652,7 @@
         <v>94</v>
       </c>
       <c r="F42">
-        <f>AVERAGE(B42,C42)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
     </row>
@@ -11748,7 +14670,7 @@
         <v>97</v>
       </c>
       <c r="F43">
-        <f>AVERAGE(B43,C43)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11766,7 +14688,7 @@
         <v>89</v>
       </c>
       <c r="F44">
-        <f>AVERAGE(B44,C44)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11784,7 +14706,7 @@
         <v>92</v>
       </c>
       <c r="F45">
-        <f>AVERAGE(B45,C45)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
     </row>
@@ -11802,7 +14724,7 @@
         <v>94</v>
       </c>
       <c r="F46">
-        <f>AVERAGE(B46,C46)</f>
+        <f t="shared" si="4"/>
         <v>14.5</v>
       </c>
     </row>
@@ -11820,7 +14742,7 @@
         <v>97</v>
       </c>
       <c r="F47">
-        <f>AVERAGE(B47,C47)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
@@ -11838,7 +14760,7 @@
         <v>96</v>
       </c>
       <c r="F48">
-        <f>AVERAGE(B48,C48)</f>
+        <f t="shared" si="4"/>
         <v>15.5</v>
       </c>
     </row>
@@ -11856,7 +14778,7 @@
         <v>98</v>
       </c>
       <c r="F49">
-        <f>AVERAGE(B49,C49)</f>
+        <f t="shared" si="4"/>
         <v>20.5</v>
       </c>
     </row>
@@ -11874,7 +14796,7 @@
         <v>95</v>
       </c>
       <c r="F50">
-        <f>AVERAGE(B50,C50)</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
@@ -11892,7 +14814,7 @@
         <v>94</v>
       </c>
       <c r="F51">
-        <f>AVERAGE(B51,C51)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
     </row>
@@ -11910,7 +14832,7 @@
         <v>93</v>
       </c>
       <c r="F52">
-        <f>AVERAGE(B52,C52)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
     </row>
@@ -11928,7 +14850,7 @@
         <v>95</v>
       </c>
       <c r="F53">
-        <f>AVERAGE(B53,C53)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
@@ -11946,7 +14868,7 @@
         <v>94</v>
       </c>
       <c r="F54">
-        <f>AVERAGE(B54,C54)</f>
+        <f t="shared" si="4"/>
         <v>18.5</v>
       </c>
     </row>
@@ -11964,7 +14886,7 @@
         <v>91</v>
       </c>
       <c r="F55">
-        <f>AVERAGE(B55,C55)</f>
+        <f t="shared" si="4"/>
         <v>18.5</v>
       </c>
     </row>
@@ -11982,7 +14904,7 @@
         <v>88</v>
       </c>
       <c r="F56">
-        <f>AVERAGE(B56,C56)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -12000,7 +14922,7 @@
         <v>95</v>
       </c>
       <c r="F57">
-        <f>AVERAGE(B57,C57)</f>
+        <f t="shared" si="4"/>
         <v>23.5</v>
       </c>
     </row>
@@ -12018,7 +14940,7 @@
         <v>90</v>
       </c>
       <c r="F58">
-        <f>AVERAGE(B58,C58)</f>
+        <f t="shared" si="4"/>
         <v>23.5</v>
       </c>
     </row>
@@ -12036,7 +14958,7 @@
         <v>94</v>
       </c>
       <c r="F59">
-        <f>AVERAGE(B59,C59)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
     </row>
@@ -12054,7 +14976,7 @@
         <v>97</v>
       </c>
       <c r="F60">
-        <f>AVERAGE(B60,C60)</f>
+        <f t="shared" si="4"/>
         <v>22.5</v>
       </c>
     </row>
@@ -12072,7 +14994,7 @@
         <v>87</v>
       </c>
       <c r="F61">
-        <f>AVERAGE(B61,C61)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
     </row>
@@ -12090,7 +15012,7 @@
         <v>98</v>
       </c>
       <c r="F62">
-        <f>AVERAGE(B62,C62)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
     </row>
@@ -12108,7 +15030,7 @@
         <v>92</v>
       </c>
       <c r="F63">
-        <f>AVERAGE(B63,C63)</f>
+        <f t="shared" si="4"/>
         <v>25.5</v>
       </c>
     </row>
@@ -12126,7 +15048,7 @@
         <v>93</v>
       </c>
       <c r="F64">
-        <f>AVERAGE(B64,C64)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
     </row>
@@ -12144,7 +15066,7 @@
         <v>98</v>
       </c>
       <c r="F65">
-        <f>AVERAGE(B65,C65)</f>
+        <f t="shared" si="4"/>
         <v>21.5</v>
       </c>
     </row>
@@ -12162,7 +15084,7 @@
         <v>96</v>
       </c>
       <c r="F66">
-        <f>AVERAGE(B66,C66)</f>
+        <f t="shared" si="4"/>
         <v>17.5</v>
       </c>
     </row>
@@ -12180,7 +15102,7 @@
         <v>95</v>
       </c>
       <c r="F67">
-        <f>AVERAGE(B67,C67)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
     </row>
@@ -12198,7 +15120,7 @@
         <v>96</v>
       </c>
       <c r="F68">
-        <f>AVERAGE(B68,C68)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
@@ -12216,7 +15138,7 @@
         <v>90</v>
       </c>
       <c r="F69">
-        <f>AVERAGE(B69,C69)</f>
+        <f t="shared" si="4"/>
         <v>21.5</v>
       </c>
     </row>
@@ -12234,7 +15156,7 @@
         <v>94</v>
       </c>
       <c r="F70">
-        <f>AVERAGE(B70,C70)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
     </row>
@@ -12252,7 +15174,7 @@
         <v>91</v>
       </c>
       <c r="F71">
-        <f>AVERAGE(B71,C71)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -12275,7 +15197,7 @@
         <v>83</v>
       </c>
       <c r="F74">
-        <f>AVERAGE(B74,C74)</f>
+        <f t="shared" ref="F74:F106" si="5">AVERAGE(B74,C74)</f>
         <v>26.5</v>
       </c>
       <c r="H74">
@@ -12301,7 +15223,7 @@
         <v>86</v>
       </c>
       <c r="F75">
-        <f>AVERAGE(B75,C75)</f>
+        <f t="shared" si="5"/>
         <v>24.5</v>
       </c>
     </row>
@@ -12319,7 +15241,7 @@
         <v>76</v>
       </c>
       <c r="F76">
-        <f>AVERAGE(B76,C76)</f>
+        <f t="shared" si="5"/>
         <v>32.5</v>
       </c>
     </row>
@@ -12337,7 +15259,7 @@
         <v>83</v>
       </c>
       <c r="F77">
-        <f>AVERAGE(B77,C77)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
     </row>
@@ -12355,7 +15277,7 @@
         <v>80</v>
       </c>
       <c r="F78">
-        <f>AVERAGE(B78,C78)</f>
+        <f t="shared" si="5"/>
         <v>28.5</v>
       </c>
     </row>
@@ -12373,7 +15295,7 @@
         <v>84</v>
       </c>
       <c r="F79">
-        <f>AVERAGE(B79,C79)</f>
+        <f t="shared" si="5"/>
         <v>24.5</v>
       </c>
     </row>
@@ -12391,7 +15313,7 @@
         <v>82</v>
       </c>
       <c r="F80">
-        <f>AVERAGE(B80,C80)</f>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
@@ -12409,7 +15331,7 @@
         <v>79</v>
       </c>
       <c r="F81">
-        <f>AVERAGE(B81,C81)</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
     </row>
@@ -12427,7 +15349,7 @@
         <v>75</v>
       </c>
       <c r="F82">
-        <f>AVERAGE(B82,C82)</f>
+        <f t="shared" si="5"/>
         <v>31.5</v>
       </c>
     </row>
@@ -12445,7 +15367,7 @@
         <v>72</v>
       </c>
       <c r="F83">
-        <f>AVERAGE(B83,C83)</f>
+        <f t="shared" si="5"/>
         <v>27.5</v>
       </c>
     </row>
@@ -12463,7 +15385,7 @@
         <v>84</v>
       </c>
       <c r="F84">
-        <f>AVERAGE(B84,C84)</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
     </row>
@@ -12481,7 +15403,7 @@
         <v>78</v>
       </c>
       <c r="F85">
-        <f>AVERAGE(B85,C85)</f>
+        <f t="shared" si="5"/>
         <v>31.5</v>
       </c>
     </row>
@@ -12499,7 +15421,7 @@
         <v>75</v>
       </c>
       <c r="F86">
-        <f>AVERAGE(B86,C86)</f>
+        <f t="shared" si="5"/>
         <v>31.5</v>
       </c>
     </row>
@@ -12517,7 +15439,7 @@
         <v>78</v>
       </c>
       <c r="F87">
-        <f>AVERAGE(B87,C87)</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
     </row>
@@ -12535,7 +15457,7 @@
         <v>77</v>
       </c>
       <c r="F88">
-        <f>AVERAGE(B88,C88)</f>
+        <f t="shared" si="5"/>
         <v>26.5</v>
       </c>
     </row>
@@ -12553,7 +15475,7 @@
         <v>80</v>
       </c>
       <c r="F89">
-        <f>AVERAGE(B89,C89)</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
     </row>
@@ -12571,7 +15493,7 @@
         <v>71</v>
       </c>
       <c r="F90">
-        <f>AVERAGE(B90,C90)</f>
+        <f t="shared" si="5"/>
         <v>28.5</v>
       </c>
     </row>
@@ -12589,7 +15511,7 @@
         <v>75</v>
       </c>
       <c r="F91">
-        <f>AVERAGE(B91,C91)</f>
+        <f t="shared" si="5"/>
         <v>28.5</v>
       </c>
     </row>
@@ -12607,7 +15529,7 @@
         <v>84</v>
       </c>
       <c r="F92">
-        <f>AVERAGE(B92,C92)</f>
+        <f t="shared" si="5"/>
         <v>27.5</v>
       </c>
     </row>
@@ -12625,7 +15547,7 @@
         <v>78</v>
       </c>
       <c r="F93">
-        <f>AVERAGE(B93,C93)</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
     </row>
@@ -12643,7 +15565,7 @@
         <v>81</v>
       </c>
       <c r="F94">
-        <f>AVERAGE(B94,C94)</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
     </row>
@@ -12661,7 +15583,7 @@
         <v>87</v>
       </c>
       <c r="F95">
-        <f>AVERAGE(B95,C95)</f>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
     </row>
@@ -12679,7 +15601,7 @@
         <v>71</v>
       </c>
       <c r="F96">
-        <f>AVERAGE(B96,C96)</f>
+        <f t="shared" si="5"/>
         <v>25.5</v>
       </c>
     </row>
@@ -12697,7 +15619,7 @@
         <v>63</v>
       </c>
       <c r="F97">
-        <f>AVERAGE(B97,C97)</f>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
     </row>
@@ -12715,7 +15637,7 @@
         <v>80</v>
       </c>
       <c r="F98">
-        <f>AVERAGE(B98,C98)</f>
+        <f t="shared" si="5"/>
         <v>29.5</v>
       </c>
     </row>
@@ -12733,7 +15655,7 @@
         <v>77</v>
       </c>
       <c r="F99">
-        <f>AVERAGE(B99,C99)</f>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
@@ -12751,7 +15673,7 @@
         <v>92</v>
       </c>
       <c r="F100">
-        <f>AVERAGE(B100,C100)</f>
+        <f t="shared" si="5"/>
         <v>30.5</v>
       </c>
     </row>
@@ -12769,7 +15691,7 @@
         <v>72</v>
       </c>
       <c r="F101">
-        <f>AVERAGE(B101,C101)</f>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
     </row>
@@ -12787,7 +15709,7 @@
         <v>73</v>
       </c>
       <c r="F102">
-        <f>AVERAGE(B102,C102)</f>
+        <f t="shared" si="5"/>
         <v>31.5</v>
       </c>
     </row>
@@ -12805,7 +15727,7 @@
         <v>82</v>
       </c>
       <c r="F103">
-        <f>AVERAGE(B103,C103)</f>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
     </row>
@@ -12823,7 +15745,7 @@
         <v>79</v>
       </c>
       <c r="F104">
-        <f>AVERAGE(B104,C104)</f>
+        <f t="shared" si="5"/>
         <v>29.5</v>
       </c>
     </row>
@@ -12841,7 +15763,7 @@
         <v>84</v>
       </c>
       <c r="F105">
-        <f>AVERAGE(B105,C105)</f>
+        <f t="shared" si="5"/>
         <v>27.5</v>
       </c>
     </row>
@@ -12859,7 +15781,7 @@
         <v>79</v>
       </c>
       <c r="F106">
-        <f>AVERAGE(B106,C106)</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
     </row>
@@ -12869,7 +15791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AL109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18241,4 +21163,3135 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
+  <dimension ref="A2:AF11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>82</v>
+      </c>
+      <c r="G4">
+        <v>72</v>
+      </c>
+      <c r="H4">
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>94</v>
+      </c>
+      <c r="L4">
+        <v>56</v>
+      </c>
+      <c r="M4">
+        <v>44</v>
+      </c>
+      <c r="N4">
+        <v>14</v>
+      </c>
+      <c r="O4">
+        <v>86</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>18</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>17</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>29</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q5)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R5)</f>
+        <v>18.75</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S5)</f>
+        <v>29.75</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S5)</f>
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T5)</f>
+        <v>22</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T5)</f>
+        <v>0.94280904158206502</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>17</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD5)</f>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD5)</f>
+        <v>0.31426968052735654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>86</v>
+      </c>
+      <c r="G5">
+        <v>64</v>
+      </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>95</v>
+      </c>
+      <c r="L5">
+        <v>58</v>
+      </c>
+      <c r="M5">
+        <v>42</v>
+      </c>
+      <c r="N5">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>81</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q11" si="0">AVERAGE(C5,D5)</f>
+        <v>17</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R11" si="1">AVERAGE(H5,I5)</f>
+        <v>20.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S11" si="2">AVERAGE(M5,N5)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T11" si="3">AVERAGE(Q5:S5)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC11" si="4">MIN(Q5:S5)</f>
+        <v>17</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD11" si="5">(1/3)*(T5-AC5)</f>
+        <v>1.8888888888888893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>82</v>
+      </c>
+      <c r="G8">
+        <v>72</v>
+      </c>
+      <c r="H8">
+        <v>28</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>44</v>
+      </c>
+      <c r="N8">
+        <v>14</v>
+      </c>
+      <c r="O8">
+        <v>86</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f>AVERAGE(Q8:Q11)</f>
+        <v>16.5</v>
+      </c>
+      <c r="V8">
+        <f>_xlfn.STDEV.S(Q8:Q11)</f>
+        <v>1.2909944487358056</v>
+      </c>
+      <c r="W8">
+        <f>AVERAGE(R8:R11)</f>
+        <v>19.375</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.STDEV.S(R8:R11)</f>
+        <v>1.6007810593582121</v>
+      </c>
+      <c r="Y8">
+        <f>AVERAGE(S8:S11)</f>
+        <v>28.5</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.STDEV.S(S8:S11)</f>
+        <v>1.6832508230603465</v>
+      </c>
+      <c r="AA8">
+        <f>AVERAGE(T8:T11)</f>
+        <v>21.458333333333332</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.STDEV.S(T8:T11)</f>
+        <v>0.89623698916120498</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AE8">
+        <f>AVERAGE(AD8:AD11)</f>
+        <v>1.7361111111111107</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.STDEV.S(AD8:AD11)</f>
+        <v>0.19966535789673939</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>64</v>
+      </c>
+      <c r="H9">
+        <v>36</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>95</v>
+      </c>
+      <c r="L9">
+        <v>58</v>
+      </c>
+      <c r="M9">
+        <v>42</v>
+      </c>
+      <c r="N9">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>81</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>1.8888888888888893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>85</v>
+      </c>
+      <c r="G10">
+        <v>74</v>
+      </c>
+      <c r="H10">
+        <v>26</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10">
+        <v>86</v>
+      </c>
+      <c r="L10">
+        <v>68</v>
+      </c>
+      <c r="M10">
+        <v>32</v>
+      </c>
+      <c r="N10">
+        <v>21</v>
+      </c>
+      <c r="O10">
+        <v>79</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>26.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>20.5</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>85</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11">
+        <v>83</v>
+      </c>
+      <c r="G11">
+        <v>73</v>
+      </c>
+      <c r="H11">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <v>87</v>
+      </c>
+      <c r="L11">
+        <v>68</v>
+      </c>
+      <c r="M11">
+        <v>32</v>
+      </c>
+      <c r="N11">
+        <v>24</v>
+      </c>
+      <c r="O11">
+        <v>76</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>1.7777777777777772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
+  <dimension ref="A2:AF5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>73</v>
+      </c>
+      <c r="H4">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>86</v>
+      </c>
+      <c r="L4">
+        <v>63</v>
+      </c>
+      <c r="M4">
+        <v>37</v>
+      </c>
+      <c r="N4">
+        <v>39</v>
+      </c>
+      <c r="O4">
+        <v>61</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>14</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>20.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>38</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4,Q5)</f>
+        <v>15.75</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4,Q5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4,R5)</f>
+        <v>19.5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4,R5)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4,S5)</f>
+        <v>34.25</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4,S5)</f>
+        <v>5.3033008588991066</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4,T5)</f>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4,T5)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>14</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>3.3888888888888893</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4,AD5)</f>
+        <v>2.4722222222222223</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4,AD5)</f>
+        <v>1.2963624321753378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>79</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>86</v>
+      </c>
+      <c r="G5">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>86</v>
+      </c>
+      <c r="L5">
+        <v>61</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>22</v>
+      </c>
+      <c r="O5">
+        <v>78</v>
+      </c>
+      <c r="Q5">
+        <f>AVERAGE(C5,D5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="R5">
+        <f>AVERAGE(H5,I5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="S5">
+        <f>AVERAGE(M5,N5)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T5">
+        <f>AVERAGE(Q5:S5)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f>MIN(Q5:S5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="AD5">
+        <f>(1/3)*(T5-AC5)</f>
+        <v>1.5555555555555558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <v>79</v>
+      </c>
+      <c r="G4">
+        <v>85</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="L4">
+        <v>76</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4">
+        <v>43</v>
+      </c>
+      <c r="O4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>79</v>
+      </c>
+      <c r="G8">
+        <v>85</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>76</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
+      </c>
+      <c r="N8">
+        <v>43</v>
+      </c>
+      <c r="O8">
+        <v>57</v>
+      </c>
+      <c r="Q8">
+        <f>AVERAGE(C8,D8)</f>
+        <v>20</v>
+      </c>
+      <c r="R8">
+        <f>AVERAGE(H8:I8)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S8">
+        <f>AVERAGE(M8,N8)</f>
+        <v>33.5</v>
+      </c>
+      <c r="T8">
+        <f>AVERAGE(Q8:S8)</f>
+        <v>22</v>
+      </c>
+      <c r="U8">
+        <f>AVERAGE(Q8,Q9:Q10)</f>
+        <v>15</v>
+      </c>
+      <c r="V8">
+        <f>_xlfn.STDEV.S(Q8,Q9:Q10)</f>
+        <v>4.5825756949558398</v>
+      </c>
+      <c r="W8">
+        <f>AVERAGE(R8,R9:R10)</f>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.STDEV.S(R8,R9:R10)</f>
+        <v>4.1633319989322635</v>
+      </c>
+      <c r="Y8">
+        <f>AVERAGE(S8,S9:S10)</f>
+        <v>31</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.STDEV.S(S8,S9:S10)</f>
+        <v>2.5</v>
+      </c>
+      <c r="AA8">
+        <f>AVERAGE(T8,T9:T10)</f>
+        <v>21.055555555555557</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.STDEV.S(T8,T9:T10)</f>
+        <v>1.0046189622236181</v>
+      </c>
+      <c r="AC8">
+        <f>MIN(Q8:S8)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD8">
+        <f>(1/3)*(T8-AC8)</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="AE8">
+        <f>AVERAGE(AD8,AD9:AD10)</f>
+        <v>2.8518518518518516</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.STDEV.S(AD8,AD9:AD10)</f>
+        <v>0.40950637754622288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>87</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>91</v>
+      </c>
+      <c r="G9">
+        <v>70</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>68</v>
+      </c>
+      <c r="M9">
+        <v>32</v>
+      </c>
+      <c r="N9">
+        <v>25</v>
+      </c>
+      <c r="O9">
+        <v>75</v>
+      </c>
+      <c r="Q9">
+        <f>AVERAGE(C9,D9)</f>
+        <v>11</v>
+      </c>
+      <c r="R9">
+        <f>AVERAGE(H9:I9)</f>
+        <v>20.5</v>
+      </c>
+      <c r="S9">
+        <f>AVERAGE(M9,N9)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T9">
+        <f>AVERAGE(Q9:S9)</f>
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <f>MIN(Q9:S9)</f>
+        <v>11</v>
+      </c>
+      <c r="AD9">
+        <f>(1/3)*(T9-AC9)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>87</v>
+      </c>
+      <c r="G10">
+        <v>77</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10">
+        <v>86</v>
+      </c>
+      <c r="L10">
+        <v>71</v>
+      </c>
+      <c r="M10">
+        <v>29</v>
+      </c>
+      <c r="N10">
+        <v>33</v>
+      </c>
+      <c r="O10">
+        <v>67</v>
+      </c>
+      <c r="Q10">
+        <f>AVERAGE(C10,D10)</f>
+        <v>14</v>
+      </c>
+      <c r="R10">
+        <f>AVERAGE(H10:I10)</f>
+        <v>18.5</v>
+      </c>
+      <c r="S10">
+        <f>AVERAGE(M10,N10)</f>
+        <v>31</v>
+      </c>
+      <c r="T10">
+        <f>AVERAGE(Q10:S10)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC10">
+        <f>MIN(Q10:S10)</f>
+        <v>14</v>
+      </c>
+      <c r="AD10">
+        <f>(1/3)*(T10-AC10)</f>
+        <v>2.3888888888888893</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
+  <dimension ref="A2:AF12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>92</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>78</v>
+      </c>
+      <c r="G4">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>29</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>94</v>
+      </c>
+      <c r="L4">
+        <v>53</v>
+      </c>
+      <c r="M4">
+        <v>47</v>
+      </c>
+      <c r="N4">
+        <v>21</v>
+      </c>
+      <c r="O4">
+        <v>79</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>34</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4,Q5)</f>
+        <v>15.5</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4,Q5)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4,R5)</f>
+        <v>19.25</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4,R5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4,S5)</f>
+        <v>31.75</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4,S5)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4,T5)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4,T5)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>15</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>2.3888888888888893</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4,AD5)</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD5,AD4)</f>
+        <v>0.23570226039551595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>88</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>70</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>88</v>
+      </c>
+      <c r="L5">
+        <v>61</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>20</v>
+      </c>
+      <c r="O5">
+        <v>80</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q12" si="0">AVERAGE(C5,D5)</f>
+        <v>16</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R12" si="1">AVERAGE(H5,I5)</f>
+        <v>21</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S12" si="2">AVERAGE(M5,N5)</f>
+        <v>29.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T12" si="3">AVERAGE(Q5:S5)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC12" si="4">MIN(Q5:S5)</f>
+        <v>16</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD12" si="5">(1/3)*(T5-AC5)</f>
+        <v>2.0555555555555558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>92</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>78</v>
+      </c>
+      <c r="G8">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>53</v>
+      </c>
+      <c r="M8">
+        <v>47</v>
+      </c>
+      <c r="N8">
+        <v>21</v>
+      </c>
+      <c r="O8">
+        <v>79</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U8">
+        <f>AVERAGE(Q8,Q9:Q12)</f>
+        <v>15.9</v>
+      </c>
+      <c r="V8">
+        <f>_xlfn.STDEV.S(Q8,Q9:Q12)</f>
+        <v>1.8506755523321778</v>
+      </c>
+      <c r="W8">
+        <f>AVERAGE(R8,R9:R12)</f>
+        <v>20</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.STDEV.S(R8,R9:R12)</f>
+        <v>1.4577379737113252</v>
+      </c>
+      <c r="Y8">
+        <f>AVERAGE(S8,S9:S12)</f>
+        <v>32.9</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.STDEV.S(S8,S9:S12)</f>
+        <v>3.150396800404673</v>
+      </c>
+      <c r="AA8">
+        <f>AVERAGE(T8,T9:T12)</f>
+        <v>22.933333333333334</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.STDEV.S(T8,T9:T12)</f>
+        <v>0.72264944628929306</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>2.3888888888888893</v>
+      </c>
+      <c r="AE8">
+        <f>AVERAGE(AD8:AD12)</f>
+        <v>2.3444444444444441</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.STDEV.S(AD8:AD12)</f>
+        <v>0.67059030564473054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>70</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>88</v>
+      </c>
+      <c r="L9">
+        <v>61</v>
+      </c>
+      <c r="M9">
+        <v>39</v>
+      </c>
+      <c r="N9">
+        <v>20</v>
+      </c>
+      <c r="O9">
+        <v>80</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>2.0555555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>81</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>75</v>
+      </c>
+      <c r="H10">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>62</v>
+      </c>
+      <c r="M10">
+        <v>38</v>
+      </c>
+      <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
+        <v>77</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>1.5555555555555558</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>81</v>
+      </c>
+      <c r="G11">
+        <v>78</v>
+      </c>
+      <c r="H11">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+      <c r="J11">
+        <v>80</v>
+      </c>
+      <c r="L11">
+        <v>69</v>
+      </c>
+      <c r="M11">
+        <v>31</v>
+      </c>
+      <c r="N11">
+        <v>35</v>
+      </c>
+      <c r="O11">
+        <v>65</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>23.5</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>88</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <v>67</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>93</v>
+      </c>
+      <c r="L12">
+        <v>50</v>
+      </c>
+      <c r="M12">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>25</v>
+      </c>
+      <c r="O12">
+        <v>75</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>37.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="5"/>
+        <v>3.3888888888888893</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
+  <dimension ref="A2:AF8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>73</v>
+      </c>
+      <c r="H4">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>81</v>
+      </c>
+      <c r="L4">
+        <v>57</v>
+      </c>
+      <c r="M4">
+        <v>43</v>
+      </c>
+      <c r="N4">
+        <v>57</v>
+      </c>
+      <c r="O4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>81</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>73</v>
+      </c>
+      <c r="H7">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>19</v>
+      </c>
+      <c r="J7">
+        <v>81</v>
+      </c>
+      <c r="L7">
+        <v>57</v>
+      </c>
+      <c r="M7">
+        <v>43</v>
+      </c>
+      <c r="N7">
+        <v>57</v>
+      </c>
+      <c r="O7">
+        <v>43</v>
+      </c>
+      <c r="Q7">
+        <f>AVERAGE(C7,D7)</f>
+        <v>29.5</v>
+      </c>
+      <c r="R7">
+        <f>AVERAGE(H7,I7)</f>
+        <v>23</v>
+      </c>
+      <c r="S7">
+        <f>AVERAGE(M7,N7)</f>
+        <v>50</v>
+      </c>
+      <c r="T7">
+        <f>AVERAGE(Q7:S7)</f>
+        <v>34.166666666666664</v>
+      </c>
+      <c r="U7">
+        <f>AVERAGE(Q7,Q8)</f>
+        <v>24.5</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.STDEV.S(Q7,Q8)</f>
+        <v>7.0710678118654755</v>
+      </c>
+      <c r="W7">
+        <f>AVERAGE(R7:R8)</f>
+        <v>20.25</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.STDEV.S(R7,R8)</f>
+        <v>3.8890872965260113</v>
+      </c>
+      <c r="Y7">
+        <f>AVERAGE(S7,S8)</f>
+        <v>41</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.STDEV.S(S7,S8)</f>
+        <v>12.727922061357855</v>
+      </c>
+      <c r="AA7">
+        <f>AVERAGE(T7,T8)</f>
+        <v>28.583333333333332</v>
+      </c>
+      <c r="AB7">
+        <f>_xlfn.STDEV.S(T7,T8)</f>
+        <v>7.8960257232497773</v>
+      </c>
+      <c r="AC7">
+        <f>MIN(Q7:S7)</f>
+        <v>23</v>
+      </c>
+      <c r="AD7">
+        <f>(1/3)*(T7-AC7)</f>
+        <v>3.7222222222222214</v>
+      </c>
+      <c r="AE7">
+        <f>AVERAGE(AD7,AD8)</f>
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="AF7">
+        <f>_xlfn.STDEV.S(AD7,AD8)</f>
+        <v>1.3356461422412567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>22</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>87</v>
+      </c>
+      <c r="L8">
+        <v>66</v>
+      </c>
+      <c r="M8">
+        <v>34</v>
+      </c>
+      <c r="N8">
+        <v>30</v>
+      </c>
+      <c r="O8">
+        <v>70</v>
+      </c>
+      <c r="Q8">
+        <f>AVERAGE(C8,D8)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R8">
+        <f>AVERAGE(H8,I8)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S8">
+        <f>AVERAGE(M8,N8)</f>
+        <v>32</v>
+      </c>
+      <c r="T8">
+        <f>AVERAGE(Q8:S8)</f>
+        <v>23</v>
+      </c>
+      <c r="AC8">
+        <f>MIN(Q8:S8)</f>
+        <v>17.5</v>
+      </c>
+      <c r="AD8">
+        <f>(1/3)*(T8-AC8)</f>
+        <v>1.8333333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
+  <dimension ref="A2:AF5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>83</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>76</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>69</v>
+      </c>
+      <c r="M4">
+        <v>31</v>
+      </c>
+      <c r="N4">
+        <v>31</v>
+      </c>
+      <c r="O4">
+        <v>69</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(D4,C4)</f>
+        <v>15.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>18</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>31</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.5</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4,Q5)</f>
+        <v>17</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4,Q5)</f>
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4,R5)</f>
+        <v>19.5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4,R5)</f>
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4,S5)</f>
+        <v>32.75</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4,S5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4,T5)</f>
+        <v>23.083333333333336</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4,T5)</f>
+        <v>2.2391714737574016</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>15.5</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4,AD5)</f>
+        <v>2.0277777777777777</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD5,AD4)</f>
+        <v>3.9283710065919485E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>82</v>
+      </c>
+      <c r="G5">
+        <v>76</v>
+      </c>
+      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>82</v>
+      </c>
+      <c r="L5">
+        <v>61</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>30</v>
+      </c>
+      <c r="O5">
+        <v>70</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q6" si="0">AVERAGE(D5,C5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R6" si="1">AVERAGE(H5,I5)</f>
+        <v>21</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S6" si="2">AVERAGE(M5,N5)</f>
+        <v>34.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T6" si="3">AVERAGE(Q5:S5)</f>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC6" si="4">MIN(Q5:S5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD6" si="5">(1/3)*(T5-AC5)</f>
+        <v>2.0555555555555558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>88</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>80</v>
+      </c>
+      <c r="L4">
+        <v>60</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>26</v>
+      </c>
+      <c r="O4">
+        <v>74</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>16</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>33</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4)</f>
+        <v>15</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4)</f>
+        <v>16</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4)</f>
+        <v>33</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(U4,W4,Y4)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(U4,W4,Y4)</f>
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <f>(1/3)*(AA4-AC4)</f>
+        <v>2.1111111111111107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>84</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>80</v>
+      </c>
+      <c r="L7">
+        <v>60</v>
+      </c>
+      <c r="M7">
+        <v>40</v>
+      </c>
+      <c r="N7">
+        <v>26</v>
+      </c>
+      <c r="O7">
+        <v>74</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C7,D7)</f>
+        <v>15</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H7,I7)</f>
+        <v>16</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M7,N7)</f>
+        <v>33</v>
+      </c>
+      <c r="T7">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q7:S7)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U7">
+        <f>AVERAGE(Q7:Q10)</f>
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.STDEV.S(Q7:Q10)</f>
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="W7">
+        <f>AVERAGE(R7:R10)</f>
+        <v>19.25</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.STDEV.S(R7:R10)</f>
+        <v>3.8405728739343039</v>
+      </c>
+      <c r="Y7">
+        <f>AVERAGE(S7:S10)</f>
+        <v>35.75</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.STDEV.S(S7:S10)</f>
+        <v>6.3966136874651625</v>
+      </c>
+      <c r="AA7">
+        <f>AVERAGE(T7:T10)</f>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="AB7">
+        <f>_xlfn.STDEV.S(T7:T10)</f>
+        <v>2.5531389540169025</v>
+      </c>
+      <c r="AC7">
+        <f>MIN(Q7:S7)</f>
+        <v>15</v>
+      </c>
+      <c r="AD7">
+        <f>(1/3)*(T7-AC7)</f>
+        <v>2.1111111111111107</v>
+      </c>
+      <c r="AE7">
+        <f>AVERAGE(AD7:AD10)</f>
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="AF7">
+        <f>_xlfn.STDEV.S(AD7:AD10)</f>
+        <v>0.73842229768062817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>85</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>85</v>
+      </c>
+      <c r="G8">
+        <v>89</v>
+      </c>
+      <c r="H8">
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>79</v>
+      </c>
+      <c r="L8">
+        <v>55</v>
+      </c>
+      <c r="M8">
+        <v>45</v>
+      </c>
+      <c r="N8">
+        <v>37</v>
+      </c>
+      <c r="O8">
+        <v>63</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" ref="AC8:AC10" si="4">MIN(Q8:S8)</f>
+        <v>15</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" ref="AD8:AD10" si="5">(1/3)*(T8-AC8)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>86</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>83</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <v>73</v>
+      </c>
+      <c r="L9">
+        <v>58</v>
+      </c>
+      <c r="M9">
+        <v>42</v>
+      </c>
+      <c r="N9">
+        <v>40</v>
+      </c>
+      <c r="O9">
+        <v>60</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>23.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>3.7222222222222223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>83</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
+        <v>16</v>
+      </c>
+      <c r="I10">
+        <v>27</v>
+      </c>
+      <c r="J10">
+        <v>73</v>
+      </c>
+      <c r="L10">
+        <v>66</v>
+      </c>
+      <c r="M10">
+        <v>34</v>
+      </c>
+      <c r="N10">
+        <v>22</v>
+      </c>
+      <c r="O10">
+        <v>78</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>2.2777777777777772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>89</v>
+      </c>
+      <c r="G4">
+        <v>76</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>70</v>
+      </c>
+      <c r="M4">
+        <v>30</v>
+      </c>
+      <c r="N4">
+        <v>21</v>
+      </c>
+      <c r="O4">
+        <v>79</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>16</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>18</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>16</v>
+      </c>
+      <c r="AD4">
+        <f>(1/3)*(T4-AC4)</f>
+        <v>1.2777777777777772</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>79</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>89</v>
+      </c>
+      <c r="G7">
+        <v>76</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>88</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>30</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+      <c r="O7">
+        <v>79</v>
+      </c>
+      <c r="Q7">
+        <f>AVERAGE(C7,D7)</f>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f>AVERAGE(H7,I7)</f>
+        <v>18</v>
+      </c>
+      <c r="S7">
+        <f>AVERAGE(M7,N7)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T7">
+        <f>AVERAGE(Q7:S7)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U7">
+        <f>AVERAGE(Q7:Q10)</f>
+        <v>14.75</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.STDEV.S(Q7:Q10)</f>
+        <v>3.2015621187164243</v>
+      </c>
+      <c r="W7">
+        <f>AVERAGE(R7:R10)</f>
+        <v>18.625</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.STDEV.S(R7:R10)</f>
+        <v>1.0307764064044151</v>
+      </c>
+      <c r="Y7">
+        <f>AVERAGE(S7:S10)</f>
+        <v>29.625</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.STDEV.S(S7:S10)</f>
+        <v>5.4524459343185301</v>
+      </c>
+      <c r="AA7">
+        <f>AVERAGE(T7:T10)</f>
+        <v>21</v>
+      </c>
+      <c r="AB7">
+        <f>_xlfn.STDEV.S(T7:T10)</f>
+        <v>1.5335748602046966</v>
+      </c>
+      <c r="AC7">
+        <f>MIN(Q7:S7)</f>
+        <v>16</v>
+      </c>
+      <c r="AD7">
+        <f>(1/3)*(T7-AC7)</f>
+        <v>1.2777777777777772</v>
+      </c>
+      <c r="AE7">
+        <f>AVERAGE(AD7:AD10)</f>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="AF7">
+        <f>_xlfn.STDEV.S(AD7:AD10)</f>
+        <v>1.113423519670919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>90</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
+      <c r="H8">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>61</v>
+      </c>
+      <c r="M8">
+        <v>39</v>
+      </c>
+      <c r="N8">
+        <v>32</v>
+      </c>
+      <c r="O8">
+        <v>68</v>
+      </c>
+      <c r="Q8">
+        <f>AVERAGE(C8,D8)</f>
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <f>AVERAGE(H8:I8)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S8">
+        <f>AVERAGE(M8,N8)</f>
+        <v>35.5</v>
+      </c>
+      <c r="T8">
+        <f>AVERAGE(Q8:S8)</f>
+        <v>21</v>
+      </c>
+      <c r="AC8">
+        <f>MIN(Q8:S8)</f>
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <f>(1/3)*(T8-AC8)</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>79</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>87</v>
+      </c>
+      <c r="H9">
+        <v>13</v>
+      </c>
+      <c r="I9">
+        <v>26</v>
+      </c>
+      <c r="J9">
+        <v>74</v>
+      </c>
+      <c r="L9">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>36</v>
+      </c>
+      <c r="N9">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>70</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q9:Q10" si="0">AVERAGE(C9,D9)</f>
+        <v>17</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R9:R10" si="1">AVERAGE(H9:I9)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S9:S10" si="2">AVERAGE(M9,N9)</f>
+        <v>33</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T9:T10" si="3">AVERAGE(Q9:S9)</f>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC9:AC10" si="4">MIN(Q9:S9)</f>
+        <v>17</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD9:AD10" si="5">(1/3)*(T9-AC9)</f>
+        <v>2.0555555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>83</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>85</v>
+      </c>
+      <c r="G10">
+        <v>77</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>75</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>24</v>
+      </c>
+      <c r="O10">
+        <v>76</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>24.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609E35F6-F40F-4A73-A5F1-CD42FBFBF511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B343D2EE-9133-4F32-902A-F5041EE2736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
     <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
     <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId6"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
     <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
     <sheet name="MIT_STDAUG" sheetId="12" r:id="rId8"/>
     <sheet name="MIT_NOAUG" sheetId="11" r:id="rId9"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="81">
   <si>
     <t>Dati originali</t>
   </si>
@@ -180,12 +180,6 @@
     <t>n=11 -&gt; 2.2 -&gt; 3</t>
   </si>
   <si>
-    <t>tau=10%</t>
-  </si>
-  <si>
-    <t>tau=20%</t>
-  </si>
-  <si>
     <t>eps=0.1</t>
   </si>
   <si>
@@ -296,6 +290,12 @@
   <si>
     <t>MIN_i</t>
   </si>
+  <si>
+    <t>g=0.01</t>
+  </si>
+  <si>
+    <t>88,12,19,81</t>
+  </si>
 </sst>
 </file>
 
@@ -344,12 +344,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -630,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -750,333 +751,528 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>42</v>
+      <c r="C5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E6" t="s">
-        <v>43</v>
+      <c r="D6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
-        <v>52</v>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>18.75</v>
+      </c>
+      <c r="H7">
+        <v>3.8890872965260113</v>
+      </c>
+      <c r="I7">
+        <v>22.75</v>
+      </c>
+      <c r="J7">
+        <v>8.1317279836452965</v>
+      </c>
+      <c r="K7">
+        <v>32.25</v>
+      </c>
+      <c r="L7">
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="M7">
+        <v>24.583333333333332</v>
+      </c>
+      <c r="N7">
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="O7">
+        <v>8.0833333333333321</v>
+      </c>
+      <c r="P7">
+        <v>1.7677669529663689</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G9">
-        <v>18.75</v>
+        <v>15.25</v>
       </c>
       <c r="H9">
-        <v>3.8890872965260113</v>
+        <v>5.3033008588991066</v>
       </c>
       <c r="I9">
-        <v>22.75</v>
+        <v>24.25</v>
       </c>
       <c r="J9">
-        <v>8.1317279836452965</v>
+        <v>2.4748737341529163</v>
       </c>
       <c r="K9">
-        <v>32.25</v>
+        <v>28</v>
       </c>
       <c r="L9">
-        <v>1.0606601717798212</v>
+        <v>1.4142135623730951</v>
       </c>
       <c r="M9">
-        <v>24.583333333333332</v>
+        <v>22.5</v>
       </c>
       <c r="N9">
-        <v>1.0606601717798212</v>
+        <v>2.1213203435596424</v>
       </c>
       <c r="O9">
-        <v>8.0833333333333321</v>
+        <v>7.25</v>
       </c>
       <c r="P9">
-        <v>1.7677669529663689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>58</v>
+        <v>3.1819805153394638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>14.857142857142858</v>
+      </c>
+      <c r="H10">
+        <v>2.0354009783964311</v>
+      </c>
+      <c r="I10">
+        <v>24.285714285714285</v>
+      </c>
+      <c r="J10">
+        <v>4.8550415622761252</v>
+      </c>
+      <c r="K10">
+        <v>31.214285714285715</v>
+      </c>
+      <c r="L10">
+        <v>0.95118973121134176</v>
+      </c>
+      <c r="M10">
+        <v>23.452380952380953</v>
+      </c>
+      <c r="N10">
+        <v>2.1531937642124515</v>
+      </c>
+      <c r="O10">
+        <v>8.5952380952380967</v>
+      </c>
+      <c r="P10">
+        <v>0.87589712135373932</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="F12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12">
-        <v>15.25</v>
-      </c>
-      <c r="H12">
-        <v>5.3033008588991066</v>
-      </c>
-      <c r="I12">
-        <v>24.25</v>
-      </c>
-      <c r="J12">
-        <v>2.4748737341529163</v>
-      </c>
-      <c r="K12">
-        <v>28</v>
-      </c>
-      <c r="L12">
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="M12">
-        <v>22.5</v>
-      </c>
-      <c r="N12">
-        <v>2.1213203435596424</v>
-      </c>
-      <c r="O12">
-        <v>7.25</v>
-      </c>
-      <c r="P12">
-        <v>3.1819805153394638</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>56</v>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="H13">
+        <v>1.8715709384839754</v>
+      </c>
+      <c r="I13">
+        <v>21</v>
+      </c>
+      <c r="J13">
+        <v>2.4832774042918899</v>
+      </c>
+      <c r="K13">
+        <v>31.5</v>
+      </c>
+      <c r="L13">
+        <v>3.3499585403736298</v>
+      </c>
+      <c r="M13">
+        <v>23.216666666666669</v>
+      </c>
+      <c r="N13">
+        <v>1.8510090674821758</v>
+      </c>
+      <c r="O13">
+        <v>6.2666666666666657</v>
+      </c>
+      <c r="P13">
+        <v>1.354462218459632</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>17</v>
+      </c>
+      <c r="H15">
+        <v>2.8771127502720115</v>
+      </c>
+      <c r="I15">
+        <v>19.95</v>
+      </c>
+      <c r="J15">
+        <v>1.6741498671796915</v>
+      </c>
+      <c r="K15">
+        <v>29.75</v>
+      </c>
+      <c r="L15">
+        <v>2.226731535981231</v>
+      </c>
+      <c r="M15">
+        <v>22.233333333333327</v>
+      </c>
+      <c r="N15">
+        <v>1.3314801936840213</v>
+      </c>
+      <c r="O15">
+        <v>5.2833333333333341</v>
+      </c>
+      <c r="P15">
+        <v>1.777864581214158</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>14.214285714285714</v>
+      </c>
+      <c r="H18">
+        <v>2.0987524639084736</v>
+      </c>
+      <c r="I18">
+        <v>23</v>
+      </c>
+      <c r="J18">
+        <v>2.5495097567963922</v>
+      </c>
+      <c r="K18">
+        <v>31.428571428571427</v>
+      </c>
+      <c r="L18">
+        <v>5.2870011303555522</v>
+      </c>
+      <c r="M18">
+        <v>22.88095238095238</v>
+      </c>
+      <c r="N18">
+        <v>2.2601914981845255</v>
+      </c>
+      <c r="O18">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="P18">
+        <v>2.0971762320196583</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
-        <v>43</v>
+      <c r="G19">
+        <v>14.916666666666666</v>
+      </c>
+      <c r="H19">
+        <v>2.1775368347439388</v>
+      </c>
+      <c r="I19">
+        <v>20.416666666666668</v>
+      </c>
+      <c r="J19">
+        <v>2.4983327774071045</v>
+      </c>
+      <c r="K19">
+        <v>26.416666666666668</v>
+      </c>
+      <c r="L19">
+        <v>1.4288690166235207</v>
+      </c>
+      <c r="M19">
+        <v>20.583333333333332</v>
+      </c>
+      <c r="N19">
+        <v>1.0368220676663862</v>
+      </c>
+      <c r="O19">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="P19">
+        <v>1.7224014243685055</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>71</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="G21">
+        <v>15.05</v>
+      </c>
+      <c r="H21">
+        <v>1.571446608843089</v>
+      </c>
+      <c r="I21">
+        <v>19.8</v>
+      </c>
+      <c r="J21">
+        <v>2.9925834249951238</v>
+      </c>
+      <c r="K21">
+        <v>27.35</v>
+      </c>
+      <c r="L21">
+        <v>3.1976553910638899</v>
+      </c>
+      <c r="M21">
+        <v>20.733333333333334</v>
+      </c>
+      <c r="N21">
+        <v>1.2794674818208691</v>
+      </c>
+      <c r="O21">
+        <v>5.6833333333333327</v>
+      </c>
+      <c r="P21">
+        <v>1.780293359096877</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22">
+        <v>15.05</v>
+      </c>
+      <c r="H22">
+        <v>1.571446608843089</v>
+      </c>
+      <c r="I22">
+        <v>19.8</v>
+      </c>
+      <c r="J22">
+        <v>2.9925834249951238</v>
+      </c>
+      <c r="K22">
+        <v>27.35</v>
+      </c>
+      <c r="L22">
+        <v>3.1976553910638899</v>
+      </c>
+      <c r="M22">
+        <v>20.733333333333334</v>
+      </c>
+      <c r="N22">
+        <v>1.2794674818208691</v>
+      </c>
+      <c r="O22">
+        <v>5.6833333333333327</v>
+      </c>
+      <c r="P22">
+        <v>1.780293359096877</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24">
+        <v>15.625</v>
+      </c>
+      <c r="H24">
+        <v>1.6007810593582121</v>
+      </c>
+      <c r="I24">
+        <v>18.625</v>
+      </c>
+      <c r="J24">
+        <v>2.75</v>
+      </c>
+      <c r="K24">
+        <v>20.291666666666668</v>
+      </c>
+      <c r="L24">
+        <v>4.6435439052516774</v>
+      </c>
+      <c r="M24">
+        <v>20.291666666666668</v>
+      </c>
+      <c r="N24">
+        <v>1.8923579255834544</v>
+      </c>
+      <c r="O24">
+        <v>4.791666666666667</v>
+      </c>
+      <c r="P24">
+        <v>1.7393858004948073</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>4</v>
       </c>
-      <c r="G24">
-        <v>14.214285714285714</v>
-      </c>
-      <c r="H24">
-        <v>2.0987524639084736</v>
-      </c>
-      <c r="I24">
-        <v>23</v>
-      </c>
-      <c r="J24">
-        <v>2.5495097567963922</v>
-      </c>
-      <c r="K24">
-        <v>31.428571428571427</v>
-      </c>
-      <c r="L24">
-        <v>5.2870011303555522</v>
-      </c>
-      <c r="M24">
-        <v>22.88095238095238</v>
-      </c>
-      <c r="N24">
-        <v>2.2601914981845255</v>
-      </c>
-      <c r="O24">
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="P24">
-        <v>2.0971762320196583</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
+      <c r="G27">
+        <v>16.416666666666668</v>
+      </c>
+      <c r="H27">
+        <v>2.8881943609574914</v>
+      </c>
+      <c r="I27">
+        <v>15.416666666666666</v>
+      </c>
+      <c r="J27">
+        <v>1.2812754062521714</v>
+      </c>
+      <c r="K27">
+        <v>29.916666666666668</v>
+      </c>
+      <c r="L27">
+        <v>2.437553418218084</v>
+      </c>
+      <c r="M27">
+        <v>20.583333333333332</v>
+      </c>
+      <c r="N27">
+        <v>1.3570801990548194</v>
+      </c>
+      <c r="O27">
+        <v>5.916666666666667</v>
+      </c>
+      <c r="P27">
+        <v>1.0527741131569135</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28">
+        <v>16.8</v>
+      </c>
+      <c r="H28">
+        <v>0.57008771254956903</v>
+      </c>
+      <c r="I28">
+        <v>17.7</v>
+      </c>
+      <c r="J28">
+        <v>1.7175564037317668</v>
+      </c>
+      <c r="K28">
+        <v>28.9</v>
+      </c>
+      <c r="L28">
+        <v>3.8794329482541587</v>
+      </c>
+      <c r="M28">
+        <v>21.133333333333333</v>
+      </c>
+      <c r="N28">
+        <v>1.5696779570628134</v>
+      </c>
+      <c r="O28">
+        <v>4.7333333333333325</v>
+      </c>
+      <c r="P28">
+        <v>0.90215790684828923</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="F25" t="s">
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31">
+        <v>16.375</v>
+      </c>
+      <c r="H31">
+        <v>3.3008837200563934</v>
+      </c>
+      <c r="I31">
         <v>20</v>
       </c>
-      <c r="G25">
-        <v>14.916666666666666</v>
-      </c>
-      <c r="H25">
-        <v>2.1775368347439388</v>
-      </c>
-      <c r="I25">
-        <v>20.416666666666668</v>
-      </c>
-      <c r="J25">
-        <v>2.4983327774071045</v>
-      </c>
-      <c r="K25">
-        <v>26.416666666666668</v>
-      </c>
-      <c r="L25">
-        <v>1.4288690166235207</v>
-      </c>
-      <c r="M25">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N25">
-        <v>1.0368220676663862</v>
-      </c>
-      <c r="O25">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="P25">
-        <v>1.7224014243685055</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32">
-        <v>16.416666666666668</v>
-      </c>
-      <c r="H32">
-        <v>2.8881943609574914</v>
-      </c>
-      <c r="I32">
-        <v>15.416666666666666</v>
-      </c>
-      <c r="J32">
-        <v>1.2812754062521714</v>
-      </c>
-      <c r="K32">
-        <v>29.916666666666668</v>
-      </c>
-      <c r="L32">
-        <v>2.437553418218084</v>
-      </c>
-      <c r="M32">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N32">
-        <v>1.3570801990548194</v>
-      </c>
-      <c r="O32">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="P32">
-        <v>1.0527741131569135</v>
-      </c>
-    </row>
-    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33">
-        <v>16.8</v>
-      </c>
-      <c r="H33">
-        <v>0.57008771254956903</v>
-      </c>
-      <c r="I33">
-        <v>17.7</v>
-      </c>
-      <c r="J33">
-        <v>1.7175564037317668</v>
-      </c>
-      <c r="K33">
-        <v>28.9</v>
-      </c>
-      <c r="L33">
-        <v>3.8794329482541587</v>
-      </c>
-      <c r="M33">
-        <v>21.133333333333333</v>
-      </c>
-      <c r="N33">
-        <v>1.5696779570628134</v>
-      </c>
-      <c r="O33">
-        <v>4.7333333333333325</v>
-      </c>
-      <c r="P33">
-        <v>0.90215790684828923</v>
-      </c>
-    </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="D35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="E36" t="s">
-        <v>73</v>
+      <c r="J31">
+        <v>3.3166247903553998</v>
+      </c>
+      <c r="K31">
+        <v>26.875</v>
+      </c>
+      <c r="L31">
+        <v>1.796988221070652</v>
+      </c>
+      <c r="M31">
+        <v>21.083333333333332</v>
+      </c>
+      <c r="N31">
+        <v>1.5898986690282424</v>
+      </c>
+      <c r="O31">
+        <v>4.708333333333333</v>
+      </c>
+      <c r="P31">
+        <v>2.9071272570854019</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1288,7 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -1107,22 +1303,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -1148,7 +1344,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -1576,19 +1772,19 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
-  <dimension ref="A1:AH99"/>
+  <dimension ref="A1:AO99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="28" max="28" width="23.21875" customWidth="1"/>
-    <col min="32" max="32" width="19.33203125" customWidth="1"/>
+    <col min="35" max="35" width="23.21875" customWidth="1"/>
+    <col min="39" max="39" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1616,38 +1812,38 @@
       <c r="V2" t="s">
         <v>14</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AD2" t="s">
         <v>1</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AE2" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AF2" t="s">
         <v>18</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AG2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AI2" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AJ2" t="s">
         <v>1</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AK2" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AM2" t="s">
         <v>40</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AN2" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AO2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q3" t="e">
         <f>AVERAGE(C3,D3)</f>
         <v>#DIV/0!</v>
@@ -1672,30 +1868,30 @@
         <f>(1/3)*(T3-U3)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W3" t="e">
+      <c r="AD3" t="e">
         <f>AVERAGE(T3:T12)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X3" t="e">
+      <c r="AE3" t="e">
         <f>_xlfn.STDEV.S(T3:T12)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y3" t="e">
+      <c r="AF3" t="e">
         <f>AVERAGE(V3:V12)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z3" t="e">
+      <c r="AG3" t="e">
         <f>_xlfn.STDEV.S(V3:V12)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q4" t="e">
         <f t="shared" ref="Q4:Q67" si="0">AVERAGE(C4,D4)</f>
         <v>#DIV/0!</v>
@@ -1720,26 +1916,26 @@
         <f t="shared" ref="V4:V67" si="5">(1/3)*(T4-U4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AI4" t="s">
         <v>20</v>
       </c>
-      <c r="AC4">
+      <c r="AJ4">
         <v>18.981481481481485</v>
       </c>
-      <c r="AD4">
+      <c r="AK4">
         <v>1.6419753086419753</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AM4" t="s">
         <v>20</v>
       </c>
-      <c r="AG4">
+      <c r="AN4">
         <v>18.981481481481485</v>
       </c>
-      <c r="AH4">
+      <c r="AO4">
         <v>1.6419753086419753</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q5" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1764,26 +1960,26 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC5">
+      <c r="AI5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ5">
         <v>19.333333333333336</v>
       </c>
-      <c r="AD5">
+      <c r="AK5">
         <v>1.7777777777777779</v>
       </c>
-      <c r="AF5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG5">
+      <c r="AM5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN5">
         <v>19.333333333333336</v>
       </c>
-      <c r="AH5">
+      <c r="AO5">
         <v>1.7777777777777779</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q6" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1808,17 +2004,17 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG6">
+      <c r="AM6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN6">
         <v>19.740740740740744</v>
       </c>
-      <c r="AH6">
+      <c r="AO6">
         <v>1.8024691358024691</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q7" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1844,7 +2040,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q8" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1870,7 +2066,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q9" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1896,7 +2092,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1922,7 +2118,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q11" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1948,7 +2144,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Q12" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1974,309 +2170,749 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
+      <c r="W14" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>9</v>
+      </c>
       <c r="AB14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AJ14" t="s">
         <v>6</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AK14" t="s">
         <v>7</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AL14" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AM14" t="s">
         <v>9</v>
       </c>
-      <c r="AG14" t="s">
+      <c r="AN14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="Q15" t="e">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>81</v>
+      </c>
+      <c r="C15">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>66</v>
+      </c>
+      <c r="H15">
+        <v>34</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>90</v>
+      </c>
+      <c r="L15">
+        <v>72</v>
+      </c>
+      <c r="M15">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>26</v>
+      </c>
+      <c r="O15">
+        <v>74</v>
+      </c>
+      <c r="Q15">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R15" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T15" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U15" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V15" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W15" t="e">
-        <f>AVERAGE(T15:T23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X15" t="e">
-        <f>_xlfn.STDEV.S(T15:T23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y15" t="e">
-        <f>AVERAGE(V15:V23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z15" t="e">
-        <f>_xlfn.STDEV.S(V15:V23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB15" t="e">
+        <v>19.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="V15">
+        <f>(T15-U15)</f>
+        <v>3.3333333333333321</v>
+      </c>
+      <c r="W15">
+        <f>AVERAGE(Q15:Q24)</f>
+        <v>17</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.STDEV.S(Q15:Q24)</f>
+        <v>2.8771127502720115</v>
+      </c>
+      <c r="Y15">
+        <f>AVERAGE(R15:R24)</f>
+        <v>19.95</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.STDEV.S(R15:R24)</f>
+        <v>1.6741498671796915</v>
+      </c>
+      <c r="AA15">
+        <f>AVERAGE(S15:S24)</f>
+        <v>29.75</v>
+      </c>
+      <c r="AB15">
+        <f>_xlfn.STDEV.S(S15:S24)</f>
+        <v>2.226731535981231</v>
+      </c>
+      <c r="AC15">
+        <f>AVERAGE(T15:T24)</f>
+        <v>22.233333333333327</v>
+      </c>
+      <c r="AD15">
+        <f>_xlfn.STDEV.S(T15:T24)</f>
+        <v>1.3314801936840213</v>
+      </c>
+      <c r="AE15">
+        <f>AVERAGE(V15:V24)</f>
+        <v>5.2833333333333341</v>
+      </c>
+      <c r="AF15">
+        <f>_xlfn.STDEV.S(V15:V24)</f>
+        <v>1.777864581214158</v>
+      </c>
+      <c r="AI15">
         <f>AVERAGE(Q15:Q23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC15" t="e">
+        <v>16.777777777777779</v>
+      </c>
+      <c r="AJ15">
         <f>_xlfn.STDEV.S(Q15:Q23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD15" t="e">
+        <v>2.9592134840941196</v>
+      </c>
+      <c r="AK15">
         <f>AVERAGE(R15:R23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE15" t="e">
+        <v>19.944444444444443</v>
+      </c>
+      <c r="AL15">
         <f>_xlfn.STDEV.S(R15:R23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF15" t="e">
+        <v>1.7756063127218762</v>
+      </c>
+      <c r="AM15">
         <f>AVERAGE(S15:S23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG15" t="e">
+        <v>29.666666666666668</v>
+      </c>
+      <c r="AN15">
         <f>_xlfn.STDEV.S(S15:S23)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="Q16" t="e">
+        <v>2.3452078799117149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>76</v>
+      </c>
+      <c r="C16">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>66</v>
+      </c>
+      <c r="H16">
+        <v>34</v>
+      </c>
+      <c r="I16">
+        <v>9</v>
+      </c>
+      <c r="J16">
+        <v>91</v>
+      </c>
+      <c r="L16">
+        <v>63</v>
+      </c>
+      <c r="M16">
+        <v>37</v>
+      </c>
+      <c r="N16">
+        <v>19</v>
+      </c>
+      <c r="O16">
+        <v>81</v>
+      </c>
+      <c r="Q16">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S16" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q17" t="e">
+        <v>22</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="4"/>
+        <v>21.5</v>
+      </c>
+      <c r="V16">
+        <f t="shared" ref="V16:V23" si="6">(T16-U16)</f>
+        <v>2.3333333333333321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>84</v>
+      </c>
+      <c r="G17">
+        <v>69</v>
+      </c>
+      <c r="H17">
+        <v>31</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>90</v>
+      </c>
+      <c r="L17">
+        <v>70</v>
+      </c>
+      <c r="M17">
+        <v>30</v>
+      </c>
+      <c r="N17">
+        <v>26</v>
+      </c>
+      <c r="O17">
+        <v>74</v>
+      </c>
+      <c r="Q17">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S17" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T17" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U17" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V17" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q18" t="e">
+        <v>16</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>21.5</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="6"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>84</v>
+      </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>74</v>
+      </c>
+      <c r="H18">
+        <v>26</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>90</v>
+      </c>
+      <c r="L18">
+        <v>53</v>
+      </c>
+      <c r="M18">
+        <v>47</v>
+      </c>
+      <c r="N18">
+        <v>14</v>
+      </c>
+      <c r="O18">
+        <v>86</v>
+      </c>
+      <c r="Q18">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U18" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V18" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q19" t="e">
+        <v>18</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="3"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="6"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>89</v>
+      </c>
+      <c r="C19">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+      <c r="E19">
+        <v>81</v>
+      </c>
+      <c r="G19">
+        <v>74</v>
+      </c>
+      <c r="H19">
+        <v>26</v>
+      </c>
+      <c r="I19">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>87</v>
+      </c>
+      <c r="L19">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>38</v>
+      </c>
+      <c r="N19">
+        <v>16</v>
+      </c>
+      <c r="O19">
+        <v>84</v>
+      </c>
+      <c r="Q19">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S19" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V19" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q20" t="e">
+        <v>15</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="3"/>
+        <v>20.5</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="6"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>90</v>
+      </c>
+      <c r="G20">
+        <v>71</v>
+      </c>
+      <c r="H20">
+        <v>29</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <v>96</v>
+      </c>
+      <c r="L20">
+        <v>60</v>
+      </c>
+      <c r="M20">
+        <v>40</v>
+      </c>
+      <c r="N20">
+        <v>23</v>
+      </c>
+      <c r="O20">
+        <v>77</v>
+      </c>
+      <c r="Q20">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S20" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U20" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V20" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q21" t="e">
+        <v>12</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>84</v>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>71</v>
+      </c>
+      <c r="H21">
+        <v>29</v>
+      </c>
+      <c r="I21">
+        <v>11</v>
+      </c>
+      <c r="J21">
+        <v>89</v>
+      </c>
+      <c r="L21">
+        <v>69</v>
+      </c>
+      <c r="M21">
+        <v>31</v>
+      </c>
+      <c r="N21">
+        <v>37</v>
+      </c>
+      <c r="O21">
+        <v>63</v>
+      </c>
+      <c r="Q21">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R21" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S21" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T21" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U21" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V21" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q22" t="e">
+        <v>18</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>80</v>
+      </c>
+      <c r="G22">
+        <v>72</v>
+      </c>
+      <c r="H22">
+        <v>28</v>
+      </c>
+      <c r="I22">
+        <v>15</v>
+      </c>
+      <c r="J22">
+        <v>85</v>
+      </c>
+      <c r="L22">
+        <v>62</v>
+      </c>
+      <c r="M22">
+        <v>38</v>
+      </c>
+      <c r="N22">
+        <v>23</v>
+      </c>
+      <c r="O22">
+        <v>77</v>
+      </c>
+      <c r="Q22">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R22" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T22" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U22" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V22" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="Q23" t="e">
+        <v>16</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666679</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>82</v>
+      </c>
+      <c r="C23">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <v>89</v>
+      </c>
+      <c r="G23">
+        <v>70</v>
+      </c>
+      <c r="H23">
+        <v>30</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>90</v>
+      </c>
+      <c r="L23">
+        <v>62</v>
+      </c>
+      <c r="M23">
+        <v>38</v>
+      </c>
+      <c r="N23">
+        <v>23</v>
+      </c>
+      <c r="O23">
+        <v>77</v>
+      </c>
+      <c r="Q23">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R23" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S23" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T23" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U23" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V23" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+        <v>14.5</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="2"/>
+        <v>30.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="6"/>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>79</v>
+      </c>
+      <c r="C24">
+        <v>21</v>
+      </c>
+      <c r="D24">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>83</v>
+      </c>
+      <c r="G24">
+        <v>64</v>
+      </c>
+      <c r="H24">
+        <v>36</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24">
+        <v>96</v>
+      </c>
+      <c r="L24">
+        <v>64</v>
+      </c>
+      <c r="M24">
+        <v>36</v>
+      </c>
+      <c r="N24">
+        <v>25</v>
+      </c>
+      <c r="O24">
+        <v>75</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" ref="Q24" si="7">AVERAGE(C24,D24)</f>
+        <v>19</v>
+      </c>
+      <c r="R24">
+        <f t="shared" ref="R24" si="8">AVERAGE(H24,I24)</f>
+        <v>20</v>
+      </c>
+      <c r="S24">
+        <f t="shared" ref="S24" si="9">AVERAGE(M24,N24)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" ref="T24" si="10">AVERAGE(Q24:S24)</f>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="U24">
+        <f t="shared" ref="U24" si="11">MIN(Q24:S24)</f>
+        <v>19</v>
+      </c>
+      <c r="V24">
+        <f t="shared" ref="V24" si="12">(T24-U24)</f>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q26" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2301,24 +2937,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W26" t="e">
+      <c r="AD26" t="e">
         <f>AVERAGE(T26:T28)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X26" t="e">
+      <c r="AE26" t="e">
         <f>_xlfn.STDEV.S(T26:T28)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y26" t="e">
+      <c r="AF26" t="e">
         <f>AVERAGE(V26:V28)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z26" t="e">
+      <c r="AG26" t="e">
         <f>_xlfn.STDEV.S(V26:V28)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q27" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2344,7 +2980,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q28" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2370,12 +3006,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q31" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2400,24 +3036,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W31" t="e">
+      <c r="AD31" t="e">
         <f>AVERAGE(T31:T39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X31" t="e">
+      <c r="AE31" t="e">
         <f>_xlfn.STDEV.S(T31:T39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y31" t="e">
+      <c r="AF31" t="e">
         <f>AVERAGE(V31:V39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z31" t="e">
+      <c r="AG31" t="e">
         <f>_xlfn.STDEV.S(V31:V39)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q32" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2443,7 +3079,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q33" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2469,7 +3105,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q34" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2495,7 +3131,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q35" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2521,7 +3157,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q36" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2547,7 +3183,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q37" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2573,7 +3209,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q38" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2599,7 +3235,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q39" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2625,12 +3261,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q42" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2655,24 +3291,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W42" t="e">
+      <c r="AD42" t="e">
         <f>AVERAGE(T42:T50)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X42" t="e">
+      <c r="AE42" t="e">
         <f>_xlfn.STDEV.S(T42:T50)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y42" t="e">
+      <c r="AF42" t="e">
         <f>AVERAGE(V42:V50)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z42" t="e">
+      <c r="AG42" t="e">
         <f>_xlfn.STDEV.S(V42:V50)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q43" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2698,7 +3334,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q44" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2724,7 +3360,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q45" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2750,7 +3386,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q46" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2776,7 +3412,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q47" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2802,7 +3438,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q48" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2828,7 +3464,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q49" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2854,7 +3490,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q50" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2880,12 +3516,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q53" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2910,24 +3546,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W53" t="e">
+      <c r="AD53" t="e">
         <f>AVERAGE(T53:T54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X53" t="e">
+      <c r="AE53" t="e">
         <f>_xlfn.STDEV.S(T53,T54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y53" t="e">
+      <c r="AF53" t="e">
         <f>AVERAGE(V53:V54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z53" t="e">
+      <c r="AG53" t="e">
         <f>_xlfn.STDEV.S(V53,V54)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q54" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2953,12 +3589,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q57" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2983,24 +3619,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W57" t="e">
+      <c r="AD57" t="e">
         <f>AVERAGE(T57:T63)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X57" t="e">
+      <c r="AE57" t="e">
         <f>_xlfn.STDEV.S(T57:T63)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y57" t="e">
+      <c r="AF57" t="e">
         <f>AVERAGE(V57:V63)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z57" t="e">
+      <c r="AG57" t="e">
         <f>_xlfn.STDEV.S(V57:V63)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q58" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3026,7 +3662,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q59" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3052,7 +3688,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q60" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3078,7 +3714,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q61" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3104,7 +3740,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q62" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3130,7 +3766,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3156,12 +3792,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q66" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3186,24 +3822,24 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W66" t="e">
+      <c r="AD66" t="e">
         <f>AVERAGE(T66:T68)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X66" t="e">
+      <c r="AE66" t="e">
         <f>_xlfn.STDEV.S(T66:T68)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y66" t="e">
+      <c r="AF66" t="e">
         <f>AVERAGE(V66:V68)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z66" t="e">
+      <c r="AG66" t="e">
         <f>_xlfn.STDEV.S(V66:V68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q67" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -3229,742 +3865,742 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q99" si="6">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q99" si="13">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R99" si="7">AVERAGE(H68,I68)</f>
+        <f t="shared" ref="R68:R99" si="14">AVERAGE(H68,I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S99" si="8">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S99" si="15">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T99" si="9">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T99" si="16">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U99" si="10">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U99" si="17">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V99" si="11">(1/3)*(T68-U68)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" ref="V68:V99" si="18">(1/3)*(T68-U68)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q71" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R71" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S71" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T71" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U71" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V71" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W71" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD71" t="e">
         <f>AVERAGE(T71:T80)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X71" t="e">
+      <c r="AE71" t="e">
         <f>_xlfn.STDEV.S(T71:T80)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y71" t="e">
+      <c r="AF71" t="e">
         <f>AVERAGE(V71:V80)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z71" t="e">
+      <c r="AG71" t="e">
         <f>_xlfn.STDEV.S(V71:V80)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q72" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R72" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S72" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T72" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U72" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V72" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q76" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R76" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S76" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T76" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U76" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V76" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q77" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R77" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S77" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T77" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U77" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V77" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q78" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R78" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S78" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T78" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U78" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V78" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W83" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD83" t="e">
         <f>AVERAGE(T83:T88)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X83" t="e">
+      <c r="AE83" t="e">
         <f>_xlfn.STDEV.S(T83:T88)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y83" t="e">
+      <c r="AF83" t="e">
         <f>AVERAGE(V83:V88)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z83" t="e">
+      <c r="AG83" t="e">
         <f>_xlfn.STDEV.S(V83:V88)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q91" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R91" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S91" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T91" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U91" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V91" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W91" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD91" t="e">
         <f>AVERAGE(T91:T99)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X91" t="e">
+      <c r="AE91" t="e">
         <f>_xlfn.STDEV.S(T91:T99)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y91" t="e">
+      <c r="AF91" t="e">
         <f>AVERAGE(V91:V99)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z91" t="e">
+      <c r="AG91" t="e">
         <f>_xlfn.STDEV.S(V91:V99)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="98" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q98" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R98" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S98" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T98" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U98" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V98" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="99" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q99" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R99" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S99" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T99" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U99" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V99" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3975,7 +4611,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
-  <dimension ref="A1:AG34"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="30" max="30" width="13.44140625" customWidth="1"/>
@@ -4004,22 +4640,22 @@
         <v>15</v>
       </c>
       <c r="V1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" t="s">
         <v>61</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AA1" t="s">
         <v>53</v>
-      </c>
-      <c r="X1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>55</v>
       </c>
       <c r="AB1" t="s">
         <v>1</v>
@@ -4041,901 +4677,663 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R2" t="e">
+      <c r="B2">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>84</v>
+      </c>
+      <c r="G2">
+        <v>70</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>99</v>
+      </c>
+      <c r="L2">
+        <v>68</v>
+      </c>
+      <c r="M2">
+        <v>32</v>
+      </c>
+      <c r="N2">
+        <v>32</v>
+      </c>
+      <c r="O2">
+        <v>68</v>
+      </c>
+      <c r="R2">
         <f>AVERAGE(C2:D2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="S2">
         <f>AVERAGE(H2,I2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="T2">
         <f>AVERAGE(M2:N2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>32</v>
+      </c>
+      <c r="U2">
         <f>AVERAGE(R2:T2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="V2">
         <f>AVERAGE(R2:R34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W2" t="e">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="W2">
         <f>_xlfn.STDEV.S(R2:R34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" t="e">
+        <v>1.8715709384839754</v>
+      </c>
+      <c r="X2">
         <f>AVERAGE(S2:S34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" t="e">
+        <v>21</v>
+      </c>
+      <c r="Y2">
         <f>_xlfn.STDEV.S(S2:S34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>2.4832774042918899</v>
+      </c>
+      <c r="Z2">
         <f>AVERAGE(T2:T34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>31.5</v>
+      </c>
+      <c r="AA2">
         <f>_xlfn.STDEV.S(T2:T34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>3.3499585403736298</v>
+      </c>
+      <c r="AB2">
         <f>AVERAGE(U2:U34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2" t="e">
+        <v>23.216666666666669</v>
+      </c>
+      <c r="AC2">
         <f>_xlfn.STDEV.S(U2:U34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>1.8510090674821758</v>
+      </c>
+      <c r="AD2">
         <f>MIN(R2:T2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE2" t="e">
-        <f>(1/3)*(U2-AD2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF2" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="AE2">
+        <f>(U2-AD2)</f>
+        <v>6.1666666666666679</v>
+      </c>
+      <c r="AF2">
         <f>AVERAGE(AE2:AE34)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2" t="e">
+        <v>6.2666666666666657</v>
+      </c>
+      <c r="AG2">
         <f>_xlfn.STDEV.S(AE2:AE34)</f>
-        <v>#DIV/0!</v>
+        <v>1.354462218459632</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R3" t="e">
+      <c r="B3">
+        <v>85</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>85</v>
+      </c>
+      <c r="G3">
+        <v>64</v>
+      </c>
+      <c r="H3">
+        <v>36</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>92</v>
+      </c>
+      <c r="L3">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>27</v>
+      </c>
+      <c r="O3">
+        <v>73</v>
+      </c>
+      <c r="R3">
         <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S3" t="e">
+        <v>15</v>
+      </c>
+      <c r="S3">
         <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" t="e">
+        <v>22</v>
+      </c>
+      <c r="T3">
         <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U3" t="e">
+        <v>24.5</v>
+      </c>
+      <c r="U3">
         <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD3" t="e">
+        <v>20.5</v>
+      </c>
+      <c r="AD3">
         <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE3" t="e">
-        <f t="shared" ref="AE3:AE34" si="5">(1/3)*(U3-AD3)</f>
-        <v>#DIV/0!</v>
+        <v>15</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" ref="AE3:AE11" si="5">(U3-AD3)</f>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R4" t="e">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>67</v>
+      </c>
+      <c r="H4">
+        <v>33</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>93</v>
+      </c>
+      <c r="L4">
+        <v>65</v>
+      </c>
+      <c r="M4">
+        <v>35</v>
+      </c>
+      <c r="N4">
+        <v>28</v>
+      </c>
+      <c r="O4">
+        <v>72</v>
+      </c>
+      <c r="R4">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
+        <v>14</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AE4">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.8333333333333321</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R5" t="e">
+      <c r="B5">
+        <v>83</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>82</v>
+      </c>
+      <c r="G5">
+        <v>69</v>
+      </c>
+      <c r="H5">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>91</v>
+      </c>
+      <c r="L5">
+        <v>64</v>
+      </c>
+      <c r="M5">
+        <v>36</v>
+      </c>
+      <c r="N5">
+        <v>28</v>
+      </c>
+      <c r="O5">
+        <v>72</v>
+      </c>
+      <c r="R5">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE5" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="AE5">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5.6666666666666679</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R6" t="e">
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>83</v>
+      </c>
+      <c r="G6">
+        <v>62</v>
+      </c>
+      <c r="H6">
+        <v>38</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>87</v>
+      </c>
+      <c r="L6">
+        <v>55</v>
+      </c>
+      <c r="M6">
+        <v>45</v>
+      </c>
+      <c r="N6">
+        <v>28</v>
+      </c>
+      <c r="O6">
+        <v>72</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD6" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE6" t="e">
+        <v>18.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="2"/>
+        <v>36.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="3"/>
+        <v>26.833333333333332</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AE6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R7" t="e">
+      <c r="B7">
+        <v>81</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="G7">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>65</v>
+      </c>
+      <c r="M7">
+        <v>35</v>
+      </c>
+      <c r="N7">
+        <v>29</v>
+      </c>
+      <c r="O7">
+        <v>71</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD7" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE7" t="e">
+        <v>18.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="3"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AE7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5.1666666666666679</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R8" t="e">
+      <c r="B8">
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>82</v>
+      </c>
+      <c r="G8">
+        <v>67</v>
+      </c>
+      <c r="H8">
+        <v>33</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>67</v>
+      </c>
+      <c r="M8">
+        <v>33</v>
+      </c>
+      <c r="N8">
+        <v>30</v>
+      </c>
+      <c r="O8">
+        <v>70</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD8" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE8" t="e">
+        <v>18.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AE8">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5.3333333333333321</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R9" t="e">
+      <c r="B9">
+        <v>86</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>81</v>
+      </c>
+      <c r="G9">
+        <v>66</v>
+      </c>
+      <c r="H9">
+        <v>34</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9">
+        <v>91</v>
+      </c>
+      <c r="L9">
+        <v>74</v>
+      </c>
+      <c r="M9">
+        <v>26</v>
+      </c>
+      <c r="N9">
+        <v>29</v>
+      </c>
+      <c r="O9">
+        <v>71</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE9" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="AE9">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5.3333333333333321</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R10" t="e">
+      <c r="B10">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>84</v>
+      </c>
+      <c r="G10">
+        <v>59</v>
+      </c>
+      <c r="H10">
+        <v>41</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>97</v>
+      </c>
+      <c r="L10">
+        <v>64</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
+      </c>
+      <c r="N10">
+        <v>32</v>
+      </c>
+      <c r="O10">
+        <v>68</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD10" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE10" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AE10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R11" t="e">
+      <c r="B11">
+        <v>81</v>
+      </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>79</v>
+      </c>
+      <c r="G11">
+        <v>64</v>
+      </c>
+      <c r="H11">
+        <v>36</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>93</v>
+      </c>
+      <c r="L11">
+        <v>66</v>
+      </c>
+      <c r="M11">
+        <v>34</v>
+      </c>
+      <c r="N11">
+        <v>33</v>
+      </c>
+      <c r="O11">
+        <v>67</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U11" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD11" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE11" t="e">
+        <v>20</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="2"/>
+        <v>33.5</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="AE11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R12" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S12" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T12" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U12" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R13" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S13" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U13" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD13" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE13" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R14" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S14" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T14" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U14" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD14" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE14" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R15" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T15" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U15" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD15" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE15" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="R16" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S16" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T16" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD16" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE16" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R17" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T17" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U17" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD17" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE17" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R18" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T18" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U18" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD18" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE18" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R19" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S19" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD19" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE19" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R20" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S20" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U20" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD20" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE20" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R21" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S21" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T21" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U21" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD21" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE21" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R22" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S22" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T22" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U22" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD22" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE22" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="23" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R23" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S23" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T23" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U23" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD23" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE23" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="24" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R24" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S24" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T24" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD24" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE24" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R25" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S25" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T25" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U25" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD25" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE25" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="26" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R26" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S26" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T26" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE26" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="27" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R27" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T27" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD27" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE27" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="28" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R28" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD28" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE28" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R29" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S29" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T29" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U29" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD29" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE29" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R30" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S30" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD30" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE30" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R31" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD31" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE31" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R32" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S32" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T32" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U32" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD32" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE32" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R33" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S33" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T33" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U33" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD33" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE33" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="18:31" x14ac:dyDescent="0.3">
-      <c r="R34" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S34" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T34" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U34" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD34" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE34" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4950,7 +5348,7 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -4971,22 +5369,22 @@
         <v>14</v>
       </c>
       <c r="W2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
         <v>61</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AB2" t="s">
         <v>53</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>55</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
@@ -5013,323 +5411,491 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="B4" s="3">
+        <v>82</v>
+      </c>
+      <c r="C4" s="3">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3">
+        <v>80</v>
+      </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="G4" s="2">
+        <v>44</v>
+      </c>
+      <c r="H4" s="2">
+        <v>56</v>
+      </c>
+      <c r="I4" s="2">
+        <v>12</v>
+      </c>
+      <c r="J4" s="2">
+        <v>88</v>
+      </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="Q4" t="e">
+      <c r="L4" s="2">
+        <v>66</v>
+      </c>
+      <c r="M4" s="2">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2">
+        <v>27</v>
+      </c>
+      <c r="O4" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>19</v>
+      </c>
+      <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>34</v>
+      </c>
+      <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>30.5</v>
+      </c>
+      <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
+        <v>27.833333333333332</v>
+      </c>
+      <c r="U4">
         <f>MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
+        <v>19</v>
+      </c>
+      <c r="V4">
         <f>T4-U4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" t="e">
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="W4">
         <f>AVERAGE(Q4:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X4" t="e">
+        <v>14.857142857142858</v>
+      </c>
+      <c r="X4">
         <f>_xlfn.STDEV.S(Q4:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4" t="e">
+        <v>2.0354009783964311</v>
+      </c>
+      <c r="Y4">
         <f>AVERAGE(R4:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" t="e">
+        <v>24.285714285714285</v>
+      </c>
+      <c r="Z4">
         <f>_xlfn.STDEV.S(R4:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" t="e">
+        <v>4.8550415622761252</v>
+      </c>
+      <c r="AA4">
         <f>AVERAGE(S4:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB4" t="e">
+        <v>31.214285714285715</v>
+      </c>
+      <c r="AB4">
         <f>_xlfn.STDEV.S(S4:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4" t="e">
+        <v>0.95118973121134176</v>
+      </c>
+      <c r="AC4">
         <f>AVERAGE(T4:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>23.452380952380953</v>
+      </c>
+      <c r="AD4">
         <f>_xlfn.STDEV.S(T4:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
+        <v>2.1531937642124515</v>
+      </c>
+      <c r="AE4">
         <f>AVERAGE(V4:V10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF4" t="e">
+        <v>8.5952380952380967</v>
+      </c>
+      <c r="AF4">
         <f>_xlfn.STDEV.S(V4:V10)</f>
-        <v>#DIV/0!</v>
+        <v>0.87589712135373932</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="B5" s="3">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3">
+        <v>80</v>
+      </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="G5" s="2">
+        <v>66</v>
+      </c>
+      <c r="H5" s="2">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2">
+        <v>83</v>
+      </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="Q5" t="e">
+      <c r="L5" s="2">
+        <v>68</v>
+      </c>
+      <c r="M5" s="2">
+        <v>32</v>
+      </c>
+      <c r="N5" s="2">
+        <v>29</v>
+      </c>
+      <c r="O5" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q5">
         <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="R5">
         <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>25.5</v>
+      </c>
+      <c r="S5">
         <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>30.5</v>
+      </c>
+      <c r="T5">
         <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" t="e">
+        <v>23.5</v>
+      </c>
+      <c r="U5">
         <f t="shared" ref="U5:U10" si="4">MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="V5">
         <f t="shared" ref="V5:V10" si="5">T5-U5</f>
-        <v>#DIV/0!</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="B6" s="3">
+        <v>82</v>
+      </c>
+      <c r="C6" s="3">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3">
+        <v>92</v>
+      </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="G6" s="2">
+        <v>68</v>
+      </c>
+      <c r="H6" s="2">
+        <v>32</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>95</v>
+      </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="Q6" t="e">
+      <c r="L6" s="2">
+        <v>53</v>
+      </c>
+      <c r="M6" s="2">
+        <v>47</v>
+      </c>
+      <c r="N6" s="2">
+        <v>15</v>
+      </c>
+      <c r="O6" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S6" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" t="e">
+        <v>13</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.8333333333333321</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="B7" s="3">
+        <v>89</v>
+      </c>
+      <c r="C7" s="3">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3">
+        <v>82</v>
+      </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="G7" s="2">
+        <v>58</v>
+      </c>
+      <c r="H7" s="2">
+        <v>42</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2">
+        <v>92</v>
+      </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="Q7" t="e">
+      <c r="L7" s="2">
+        <v>55</v>
+      </c>
+      <c r="M7" s="2">
+        <v>45</v>
+      </c>
+      <c r="N7" s="2">
+        <v>19</v>
+      </c>
+      <c r="O7" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>9.3333333333333321</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="B8" s="3">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>90</v>
+      </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="G8" s="2">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2">
+        <v>37</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>92</v>
+      </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="Q8" t="e">
+      <c r="L8" s="2">
+        <v>55</v>
+      </c>
+      <c r="M8" s="2">
+        <v>45</v>
+      </c>
+      <c r="N8" s="2">
+        <v>20</v>
+      </c>
+      <c r="O8" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
+        <v>13</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>9.6666666666666679</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="B9" s="3">
+        <v>86</v>
+      </c>
+      <c r="C9" s="3">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3">
+        <v>15</v>
+      </c>
+      <c r="E9" s="3">
+        <v>85</v>
+      </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="G9" s="2">
+        <v>66</v>
+      </c>
+      <c r="H9" s="2">
+        <v>34</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2">
+        <v>90</v>
+      </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="Q9" t="e">
+      <c r="L9" s="2">
+        <v>69</v>
+      </c>
+      <c r="M9" s="2">
+        <v>31</v>
+      </c>
+      <c r="N9" s="2">
+        <v>33</v>
+      </c>
+      <c r="O9" s="2">
+        <v>67</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3">
+        <v>89</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="G10" s="2">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>97</v>
+      </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="Q10" t="e">
+      <c r="L10" s="2">
+        <v>60</v>
+      </c>
+      <c r="M10" s="2">
+        <v>40</v>
+      </c>
+      <c r="N10" s="2">
+        <v>20</v>
+      </c>
+      <c r="O10" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" t="e">
+        <v>15.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.1666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -5347,7 +5913,7 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.3">
@@ -5382,19 +5948,19 @@
         <v>5</v>
       </c>
       <c r="X2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
         <v>7</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="s">
         <v>9</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
@@ -5529,10 +6095,10 @@
         <v>0.19966535789673909</v>
       </c>
       <c r="AH3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AL3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.3">
@@ -5597,7 +6163,7 @@
         <v>2.5555555555555558</v>
       </c>
       <c r="AH4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI4">
         <v>28.666666666666671</v>
@@ -5606,7 +6172,7 @@
         <v>2.7777777777777772</v>
       </c>
       <c r="AL4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>28.666666666666671</v>
@@ -5741,7 +6307,7 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.3">
@@ -6039,7 +6605,7 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.3">
@@ -6193,7 +6759,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.3">
@@ -6347,7 +6913,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.3">
@@ -6553,22 +7119,22 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>75</v>
+      </c>
+      <c r="R39" t="s">
         <v>76</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="S39" t="s">
         <v>77</v>
-      </c>
-      <c r="R39" t="s">
-        <v>78</v>
-      </c>
-      <c r="S39" t="s">
-        <v>79</v>
       </c>
       <c r="T39" t="s">
         <v>15</v>
       </c>
       <c r="U39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="V39" t="s">
         <v>14</v>
@@ -6577,19 +7143,19 @@
         <v>5</v>
       </c>
       <c r="X39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y39" t="s">
         <v>7</v>
       </c>
       <c r="Z39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA39" t="s">
         <v>9</v>
       </c>
       <c r="AB39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AC39" t="s">
         <v>1</v>
@@ -6785,7 +7351,7 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
@@ -6889,10 +7455,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
@@ -6921,7 +7487,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AB4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AC4">
         <v>28.041666666666668</v>
@@ -6930,7 +7496,7 @@
         <v>2.5972222222222219</v>
       </c>
       <c r="AF4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AG4">
         <v>28.041666666666668</v>
@@ -6994,19 +7560,19 @@
         <v>5</v>
       </c>
       <c r="AD6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AE6" t="s">
         <v>7</v>
       </c>
       <c r="AF6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AG6" t="s">
         <v>9</v>
       </c>
       <c r="AH6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI6" t="s">
         <v>1</v>
@@ -7023,7 +7589,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="AB7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AC7" t="e">
         <f>AVERAGE(Q17:Q20)</f>
@@ -7064,7 +7630,7 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
@@ -7194,7 +7760,7 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
@@ -7324,7 +7890,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.3">
@@ -7454,7 +8020,7 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.3">
@@ -7631,22 +8197,22 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>75</v>
+      </c>
+      <c r="R39" t="s">
         <v>76</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="S39" t="s">
         <v>77</v>
-      </c>
-      <c r="R39" t="s">
-        <v>78</v>
-      </c>
-      <c r="S39" t="s">
-        <v>79</v>
       </c>
       <c r="T39" t="s">
         <v>15</v>
       </c>
       <c r="U39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="V39" t="s">
         <v>14</v>
@@ -7655,19 +8221,19 @@
         <v>5</v>
       </c>
       <c r="X39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y39" t="s">
         <v>7</v>
       </c>
       <c r="Z39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA39" t="s">
         <v>9</v>
       </c>
       <c r="AB39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AC39" t="s">
         <v>1</v>
@@ -7898,19 +8464,19 @@
         <v>5</v>
       </c>
       <c r="X2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
         <v>7</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="s">
         <v>9</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
@@ -8271,19 +8837,19 @@
         <v>5</v>
       </c>
       <c r="AJ11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AK11" t="s">
         <v>7</v>
       </c>
       <c r="AL11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AM11" t="s">
         <v>9</v>
       </c>
       <c r="AN11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AO11" t="s">
         <v>1</v>
@@ -10426,19 +10992,19 @@
         <v>5</v>
       </c>
       <c r="X2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
         <v>7</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="s">
         <v>9</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
@@ -10687,12 +11253,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF11"/>
+  <dimension ref="A2:AF7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -10707,22 +11273,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -10748,251 +11314,301 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
-        <f>AVERAGE(C4,D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
-        <f>AVERAGE(H4,I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
-        <f>AVERAGE(M4,N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+      <c r="B4">
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>84</v>
+      </c>
+      <c r="G4">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>29</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>97</v>
+      </c>
+      <c r="L4">
+        <v>71</v>
+      </c>
+      <c r="M4">
+        <v>29</v>
+      </c>
+      <c r="N4">
+        <v>17</v>
+      </c>
+      <c r="O4">
+        <v>83</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>14</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>16</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>23</v>
+      </c>
+      <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
-        <f>AVERAGE(Q4:Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
-        <f>_xlfn.STDEV.S(Q4:Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" t="e">
-        <f>AVERAGE(R4:R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(R4:R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4" t="e">
-        <f>AVERAGE(S4:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(S4:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" t="e">
-        <f>AVERAGE(T4:T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(T4:T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4" t="e">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>15.625</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>1.6007810593582121</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R7)</f>
+        <v>18.625</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>2.75</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>20.291666666666668</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>4.6435439052516774</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>20.291666666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>1.8923579255834544</v>
+      </c>
+      <c r="AC4">
         <f>MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
-        <f>(1/3)*(T4-AC4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
-        <f>AVERAGE(AD4:AD5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(AD4:AD5)</f>
-        <v>#DIV/0!</v>
+        <v>14</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>3.6666666666666679</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>4.791666666666667</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>1.7393858004948073</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
-        <f t="shared" ref="Q5:Q11" si="0">AVERAGE(C5,D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
-        <f t="shared" ref="R5:R11" si="1">AVERAGE(H5,I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
-        <f t="shared" ref="S5:S11" si="2">AVERAGE(M5,N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
-        <f t="shared" ref="T5:T11" si="3">AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC5" t="e">
-        <f t="shared" ref="AC5:AC11" si="4">MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f t="shared" ref="AD5:AD11" si="5">(1/3)*(T5-AC5)</f>
-        <v>#DIV/0!</v>
+      <c r="B5">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>81</v>
+      </c>
+      <c r="G5">
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>92</v>
+      </c>
+      <c r="L5">
+        <v>67</v>
+      </c>
+      <c r="M5">
+        <v>33</v>
+      </c>
+      <c r="N5">
+        <v>31</v>
+      </c>
+      <c r="O5">
+        <v>69</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5:D5)</f>
+        <v>17</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5:I5)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5:N5)</f>
+        <v>32</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
+        <v>16.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
+        <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>87</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>79</v>
+      </c>
+      <c r="G6">
+        <v>70</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>88</v>
+      </c>
+      <c r="L6">
+        <v>66</v>
+      </c>
+      <c r="M6">
+        <v>34</v>
+      </c>
+      <c r="N6">
+        <v>11</v>
+      </c>
+      <c r="O6">
+        <v>89</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>3.1666666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q8" t="e">
+      <c r="B7">
+        <v>89</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="G7">
+        <v>73</v>
+      </c>
+      <c r="H7">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>85</v>
+      </c>
+      <c r="L7">
+        <v>68</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>26</v>
+      </c>
+      <c r="O7">
+        <v>74</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <f>AVERAGE(Q8:Q11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
-        <f>_xlfn.STDEV.S(Q8:Q11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W8" t="e">
-        <f>AVERAGE(R8:R11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X8" t="e">
-        <f>_xlfn.STDEV.S(R8:R11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y8" t="e">
-        <f>AVERAGE(S8:S11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z8" t="e">
-        <f>_xlfn.STDEV.S(S8:S11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA8" t="e">
-        <f>AVERAGE(T8:T11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB8" t="e">
-        <f>_xlfn.STDEV.S(T8:T11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC8" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD8" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21.5</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE8" t="e">
-        <f>AVERAGE(AD8:AD11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF8" t="e">
-        <f>_xlfn.STDEV.S(AD8:AD11)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC10" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD10" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q11" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC11" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -11007,7 +11623,7 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -11022,22 +11638,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -11063,7 +11679,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -11168,12 +11784,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF10"/>
+  <dimension ref="A2:AF7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -11188,22 +11804,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -11229,133 +11845,301 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>66</v>
+      </c>
+      <c r="H4">
+        <v>34</v>
+      </c>
+      <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4">
+        <v>89</v>
+      </c>
+      <c r="L4">
+        <v>73</v>
+      </c>
+      <c r="M4">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>25</v>
+      </c>
+      <c r="O4">
+        <v>75</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>20</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>22.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>26</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>16.375</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>3.3008837200563934</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R7)</f>
+        <v>20</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>3.3166247903553998</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S7)</f>
+        <v>26.875</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>1.796988221070652</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>21.083333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>1.5898986690282424</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>20</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>2.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>4.708333333333333</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>2.9071272570854019</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>87</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>78</v>
+      </c>
+      <c r="H5">
+        <v>22</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>91</v>
+      </c>
+      <c r="L5">
+        <v>78</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>31</v>
+      </c>
+      <c r="O5">
+        <v>69</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5:D5)</f>
+        <v>15</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5:I5)</f>
+        <v>15.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5:N5)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
+        <v>19</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
+        <v>15</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>88</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>87</v>
+      </c>
+      <c r="G6">
+        <v>70</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>85</v>
+      </c>
+      <c r="L6">
+        <v>67</v>
+      </c>
+      <c r="M6">
+        <v>33</v>
+      </c>
+      <c r="N6">
+        <v>26</v>
+      </c>
+      <c r="O6">
+        <v>74</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>21.5</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q8" t="e">
-        <f>AVERAGE(C8,D8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" t="e">
-        <f>AVERAGE(H8:I8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
-        <f>AVERAGE(M8,N8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
-        <f>AVERAGE(Q8:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <f>AVERAGE(Q8,Q9:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
-        <f>_xlfn.STDEV.S(Q8,Q9:Q10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W8" t="e">
-        <f>AVERAGE(R8,R9:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X8" t="e">
-        <f>_xlfn.STDEV.S(R8,R9:R10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y8" t="e">
-        <f>AVERAGE(S8,S9:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z8" t="e">
-        <f>_xlfn.STDEV.S(S8,S9:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA8" t="e">
-        <f>AVERAGE(T8,T9:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB8" t="e">
-        <f>_xlfn.STDEV.S(T8,T9:T10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC8" t="e">
-        <f>MIN(Q8:S8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD8" t="e">
-        <f>(1/3)*(T8-AC8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE8" t="e">
-        <f>AVERAGE(AD8,AD9:AD10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF8" t="e">
-        <f>_xlfn.STDEV.S(AD8,AD9:AD10)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
-        <f>AVERAGE(C9,D9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
-        <f>AVERAGE(H9:I9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
-        <f>AVERAGE(M9,N9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
-        <f>AVERAGE(Q9:S9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" t="e">
-        <f>MIN(Q9:S9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <f>(1/3)*(T9-AC9)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
-        <f>AVERAGE(C10,D10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
-        <f>AVERAGE(H10:I10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
-        <f>AVERAGE(M10,N10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
-        <f>AVERAGE(Q10:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC10" t="e">
-        <f>MIN(Q10:S10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD10" t="e">
-        <f>(1/3)*(T10-AC10)</f>
-        <v>#DIV/0!</v>
+      <c r="B7">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>78</v>
+      </c>
+      <c r="G7">
+        <v>77</v>
+      </c>
+      <c r="H7">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <v>84</v>
+      </c>
+      <c r="L7">
+        <v>77</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>28</v>
+      </c>
+      <c r="O7">
+        <v>72</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -11364,13 +12148,13 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
+  <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -11385,22 +12169,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -11426,277 +12210,360 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
-        <f>AVERAGE(C4,D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
-        <f>AVERAGE(H4,I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
-        <f>AVERAGE(M4,N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+      <c r="B4">
+        <v>91</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>76</v>
+      </c>
+      <c r="G4">
+        <v>81</v>
+      </c>
+      <c r="H4">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <v>85</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
+        <v>66</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>16.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>17</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>31</v>
+      </c>
+      <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
-        <f>AVERAGE(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
-        <f>_xlfn.STDEV.S(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" t="e">
-        <f>AVERAGE(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4" t="e">
-        <f>AVERAGE(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" t="e">
-        <f>AVERAGE(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4" t="e">
+        <v>21.5</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q8)</f>
+        <v>16.8</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q8)</f>
+        <v>0.57008771254956903</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R8)</f>
+        <v>17.7</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R8)</f>
+        <v>1.7175564037317668</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S8)</f>
+        <v>28.9</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S8)</f>
+        <v>3.8794329482541587</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T8)</f>
+        <v>21.133333333333333</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T8)</f>
+        <v>1.5696779570628134</v>
+      </c>
+      <c r="AC4">
         <f>MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
-        <f>(1/3)*(T4-AC4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
-        <f>AVERAGE(AD4,AD5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(AD5,AD4)</f>
-        <v>#DIV/0!</v>
+        <v>16.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD8)</f>
+        <v>4.7333333333333325</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD8)</f>
+        <v>0.90215790684828923</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
-        <f t="shared" ref="Q5:Q12" si="0">AVERAGE(C5,D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
-        <f t="shared" ref="R5:R12" si="1">AVERAGE(H5,I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
-        <f t="shared" ref="S5:S12" si="2">AVERAGE(M5,N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
-        <f t="shared" ref="T5:T12" si="3">AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC5" t="e">
-        <f t="shared" ref="AC5:AC12" si="4">MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f t="shared" ref="AD5:AD12" si="5">(1/3)*(T5-AC5)</f>
-        <v>#DIV/0!</v>
+      <c r="B5">
+        <v>86</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>79</v>
+      </c>
+      <c r="G5">
+        <v>69</v>
+      </c>
+      <c r="H5">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>94</v>
+      </c>
+      <c r="L5">
+        <v>64</v>
+      </c>
+      <c r="M5">
+        <v>36</v>
+      </c>
+      <c r="N5">
+        <v>26</v>
+      </c>
+      <c r="O5">
+        <v>74</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q8" si="0">AVERAGE(C5:D5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R8" si="1">AVERAGE(H5:I5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S8" si="2">AVERAGE(M5:N5)</f>
+        <v>31</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T8" si="3">AVERAGE(Q5:S5)</f>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC8" si="4">MIN(Q5:S5)</f>
+        <v>17.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD8" si="5">T5-AC5</f>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>86</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>97</v>
+      </c>
+      <c r="L6">
+        <v>73</v>
+      </c>
+      <c r="M6">
+        <v>27</v>
+      </c>
+      <c r="N6">
+        <v>27</v>
+      </c>
+      <c r="O6">
+        <v>73</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>4.6666666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>81</v>
+      </c>
+      <c r="G7">
+        <v>66</v>
+      </c>
+      <c r="H7">
+        <v>34</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>30</v>
+      </c>
+      <c r="N7">
+        <v>16</v>
+      </c>
+      <c r="O7">
+        <v>84</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>3.3333333333333321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q8" t="e">
+      <c r="E8">
+        <v>78</v>
+      </c>
+      <c r="G8">
+        <v>73</v>
+      </c>
+      <c r="H8">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>89</v>
+      </c>
+      <c r="L8">
+        <v>52</v>
+      </c>
+      <c r="M8">
+        <v>48</v>
+      </c>
+      <c r="N8">
+        <v>17</v>
+      </c>
+      <c r="O8">
+        <v>83</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <f>AVERAGE(Q8,Q9:Q12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
-        <f>_xlfn.STDEV.S(Q8,Q9:Q12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W8" t="e">
-        <f>AVERAGE(R8,R9:R12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X8" t="e">
-        <f>_xlfn.STDEV.S(R8,R9:R12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y8" t="e">
-        <f>AVERAGE(S8,S9:S12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z8" t="e">
-        <f>_xlfn.STDEV.S(S8,S9:S12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA8" t="e">
-        <f>AVERAGE(T8,T9:T12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB8" t="e">
-        <f>_xlfn.STDEV.S(T8,T9:T12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC8" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD8" t="e">
+        <v>17</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AD8">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE8" t="e">
-        <f>AVERAGE(AD8:AD12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF8" t="e">
-        <f>_xlfn.STDEV.S(AD8:AD12)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q9" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q10" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC10" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD10" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q11" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T11" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC11" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD11" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q12" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R12" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S12" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T12" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC12" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD12" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>5.8333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -11705,13 +12572,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
-  <dimension ref="A2:AF8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
+  <dimension ref="A2:AF31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -11726,22 +12596,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -11767,7 +12637,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -11775,40 +12645,40 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G4">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L4">
+        <v>83</v>
+      </c>
+      <c r="M4">
+        <v>17</v>
+      </c>
+      <c r="N4">
+        <v>28</v>
+      </c>
+      <c r="O4">
         <v>72</v>
-      </c>
-      <c r="M4">
-        <v>28</v>
-      </c>
-      <c r="N4">
-        <v>34</v>
-      </c>
-      <c r="O4">
-        <v>66</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4:D4)</f>
@@ -11816,47 +12686,47 @@
       </c>
       <c r="R4">
         <f>AVERAGE(H4:I4)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4:N4)</f>
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="U4">
-        <f>AVERAGE(Q4:Q8)</f>
-        <v>16.8</v>
+        <f>AVERAGE(Q4:Q13)</f>
+        <v>15.05</v>
       </c>
       <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q8)</f>
-        <v>0.57008771254956903</v>
+        <f>_xlfn.STDEV.S(Q4:Q13)</f>
+        <v>1.571446608843089</v>
       </c>
       <c r="W4">
-        <f>AVERAGE(R4:R8)</f>
-        <v>17.7</v>
+        <f>AVERAGE(R4:R13)</f>
+        <v>19.8</v>
       </c>
       <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R8)</f>
-        <v>1.7175564037317668</v>
+        <f>_xlfn.STDEV.S(R4:R13)</f>
+        <v>2.9925834249951238</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(S4:S8)</f>
-        <v>28.9</v>
+        <f>AVERAGE(S4:S13)</f>
+        <v>27.35</v>
       </c>
       <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S8)</f>
-        <v>3.8794329482541587</v>
+        <f>_xlfn.STDEV.S(S4:S13)</f>
+        <v>3.1976553910638899</v>
       </c>
       <c r="AA4">
-        <f>AVERAGE(T4:T8)</f>
-        <v>21.133333333333333</v>
+        <f>AVERAGE(T4:T13)</f>
+        <v>20.733333333333334</v>
       </c>
       <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T8)</f>
-        <v>1.5696779570628134</v>
+        <f>_xlfn.STDEV.S(T4:T13)</f>
+        <v>1.2794674818208691</v>
       </c>
       <c r="AC4">
         <f>MIN(Q4:S4)</f>
@@ -11864,29 +12734,29 @@
       </c>
       <c r="AD4">
         <f>T4-AC4</f>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE4">
-        <f>AVERAGE(AD4:AD8)</f>
-        <v>4.7333333333333325</v>
+        <f>AVERAGE(AD4:AD13)</f>
+        <v>5.6833333333333327</v>
       </c>
       <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD8)</f>
-        <v>0.90215790684828923</v>
+        <f>_xlfn.STDEV.S(AD4:AD13)</f>
+        <v>1.780293359096877</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5">
         <v>69</v>
@@ -11895,54 +12765,54 @@
         <v>31</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L5">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M5">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q8" si="0">AVERAGE(C5:D5)</f>
-        <v>17.5</v>
+        <f t="shared" ref="Q5:Q13" si="0">AVERAGE(C5:D5)</f>
+        <v>14</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R8" si="1">AVERAGE(H5:I5)</f>
-        <v>18.5</v>
+        <f t="shared" ref="R5:R13" si="1">AVERAGE(H5:I5)</f>
+        <v>18</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S8" si="2">AVERAGE(M5:N5)</f>
+        <f t="shared" ref="S5:S13" si="2">AVERAGE(M5:N5)</f>
         <v>31</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T8" si="3">AVERAGE(Q5:S5)</f>
-        <v>22.333333333333332</v>
+        <f t="shared" ref="T5:T13" si="3">AVERAGE(Q5:S5)</f>
+        <v>21</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5:AC8" si="4">MIN(Q5:S5)</f>
-        <v>17.5</v>
+        <f t="shared" ref="AC5:AC13" si="4">MIN(Q5:S5)</f>
+        <v>14</v>
       </c>
       <c r="AD5">
-        <f t="shared" ref="AD5:AD8" si="5">T5-AC5</f>
-        <v>4.8333333333333321</v>
+        <f t="shared" ref="AD5:AD13" si="5">T5-AC5</f>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -11957,46 +12827,46 @@
         <v>27</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L6">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M6">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O6">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>19.666666666666668</v>
+        <v>22.833333333333332</v>
       </c>
       <c r="AC6">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AD6">
         <f t="shared" si="5"/>
-        <v>4.6666666666666679</v>
+        <v>4.3333333333333321</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
@@ -12007,120 +12877,1271 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G7">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L7">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>19.333333333333332</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="AC7">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD7">
         <f t="shared" si="5"/>
-        <v>3.3333333333333321</v>
+        <v>5.3333333333333321</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H8">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L8">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="M8">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="N8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O8">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>32.5</v>
+        <v>24.5</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>22.833333333333332</v>
+        <v>22.166666666666668</v>
       </c>
       <c r="AC8">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AD8">
         <f t="shared" si="5"/>
-        <v>5.8333333333333321</v>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>93</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>76</v>
+      </c>
+      <c r="G9">
+        <v>72</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>76</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>21</v>
+      </c>
+      <c r="O9">
+        <v>79</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>3.6666666666666679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>88</v>
+      </c>
+      <c r="G10">
+        <v>76</v>
+      </c>
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>90</v>
+      </c>
+      <c r="L10">
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>18</v>
+      </c>
+      <c r="O10">
+        <v>82</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>91</v>
+      </c>
+      <c r="G11">
+        <v>63</v>
+      </c>
+      <c r="H11">
+        <v>37</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>94</v>
+      </c>
+      <c r="L11">
+        <v>70</v>
+      </c>
+      <c r="M11">
+        <v>30</v>
+      </c>
+      <c r="N11">
+        <v>29</v>
+      </c>
+      <c r="O11">
+        <v>71</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>89</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <v>73</v>
+      </c>
+      <c r="H12">
+        <v>27</v>
+      </c>
+      <c r="I12">
+        <v>14</v>
+      </c>
+      <c r="J12">
+        <v>86</v>
+      </c>
+      <c r="L12">
+        <v>79</v>
+      </c>
+      <c r="M12">
+        <v>21</v>
+      </c>
+      <c r="N12">
+        <v>38</v>
+      </c>
+      <c r="O12">
+        <v>62</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>83</v>
+      </c>
+      <c r="G13">
+        <v>80</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>13</v>
+      </c>
+      <c r="J13">
+        <v>87</v>
+      </c>
+      <c r="L13">
+        <v>71</v>
+      </c>
+      <c r="M13">
+        <v>29</v>
+      </c>
+      <c r="N13">
+        <v>29</v>
+      </c>
+      <c r="O13">
+        <v>71</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="5"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>90</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>77</v>
+      </c>
+      <c r="G16">
+        <v>71</v>
+      </c>
+      <c r="H16">
+        <v>29</v>
+      </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
+      <c r="J16">
+        <v>85</v>
+      </c>
+      <c r="L16">
+        <v>67</v>
+      </c>
+      <c r="M16">
+        <v>33</v>
+      </c>
+      <c r="N16">
+        <v>27</v>
+      </c>
+      <c r="O16">
+        <v>73</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" ref="Q14:Q23" si="6">AVERAGE(C16:D16)</f>
+        <v>16.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" ref="R14:R23" si="7">AVERAGE(H16:I16)</f>
+        <v>22</v>
+      </c>
+      <c r="S16">
+        <f t="shared" ref="S14:S23" si="8">AVERAGE(M16:N16)</f>
+        <v>30</v>
+      </c>
+      <c r="T16">
+        <f t="shared" ref="T14:T23" si="9">AVERAGE(Q16:S16)</f>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U16">
+        <f>AVERAGE(Q16:Q23)</f>
+        <v>15.875</v>
+      </c>
+      <c r="AA16">
+        <f>AVERAGE(T16:T23)</f>
+        <v>21.354166666666668</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" ref="AC14:AC23" si="10">MIN(Q16:S16)</f>
+        <v>16.5</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" ref="AD14:AD23" si="11">T16-AC16</f>
+        <v>6.3333333333333321</v>
+      </c>
+      <c r="AE16">
+        <f>AVERAGE(AD16:AD23)</f>
+        <v>5.4791666666666661</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>88</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>83</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17">
+        <v>40</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>90</v>
+      </c>
+      <c r="L17">
+        <v>66</v>
+      </c>
+      <c r="M17">
+        <v>34</v>
+      </c>
+      <c r="N17">
+        <v>21</v>
+      </c>
+      <c r="O17">
+        <v>79</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>14.5</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="8"/>
+        <v>27.5</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="9"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="10"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="11"/>
+        <v>7.8333333333333321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>22</v>
+      </c>
+      <c r="E18">
+        <v>78</v>
+      </c>
+      <c r="G18">
+        <v>69</v>
+      </c>
+      <c r="H18">
+        <v>31</v>
+      </c>
+      <c r="I18">
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <v>94</v>
+      </c>
+      <c r="L18">
+        <v>66</v>
+      </c>
+      <c r="M18">
+        <v>34</v>
+      </c>
+      <c r="N18">
+        <v>22</v>
+      </c>
+      <c r="O18">
+        <v>78</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="6"/>
+        <v>18.5</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="9"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="10"/>
+        <v>18.5</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="11"/>
+        <v>3.1666666666666679</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>79</v>
+      </c>
+      <c r="G19">
+        <v>68</v>
+      </c>
+      <c r="H19">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <v>12</v>
+      </c>
+      <c r="J19">
+        <v>88</v>
+      </c>
+      <c r="L19">
+        <v>68</v>
+      </c>
+      <c r="M19">
+        <v>32</v>
+      </c>
+      <c r="N19">
+        <v>30</v>
+      </c>
+      <c r="O19">
+        <v>70</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="9"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="11"/>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>88</v>
+      </c>
+      <c r="C20">
+        <v>12</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>83</v>
+      </c>
+      <c r="G20">
+        <v>72</v>
+      </c>
+      <c r="H20">
+        <v>28</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>92</v>
+      </c>
+      <c r="L20">
+        <v>82</v>
+      </c>
+      <c r="M20">
+        <v>18</v>
+      </c>
+      <c r="N20">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>71</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="6"/>
+        <v>14.5</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="8"/>
+        <v>23.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="9"/>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="10"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>87</v>
+      </c>
+      <c r="C21">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>18</v>
+      </c>
+      <c r="E21">
+        <v>82</v>
+      </c>
+      <c r="G21">
+        <v>70</v>
+      </c>
+      <c r="H21">
+        <v>30</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
+      </c>
+      <c r="J21">
+        <v>93</v>
+      </c>
+      <c r="L21">
+        <v>71</v>
+      </c>
+      <c r="M21">
+        <v>29</v>
+      </c>
+      <c r="N21">
+        <v>33</v>
+      </c>
+      <c r="O21">
+        <v>67</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="9"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="11"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>79</v>
+      </c>
+      <c r="G22">
+        <v>75</v>
+      </c>
+      <c r="H22">
+        <v>25</v>
+      </c>
+      <c r="I22">
+        <v>8</v>
+      </c>
+      <c r="J22">
+        <v>92</v>
+      </c>
+      <c r="L22">
+        <v>79</v>
+      </c>
+      <c r="M22">
+        <v>21</v>
+      </c>
+      <c r="N22">
+        <v>33</v>
+      </c>
+      <c r="O22">
+        <v>67</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="11"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>92</v>
+      </c>
+      <c r="C23">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <v>77</v>
+      </c>
+      <c r="G23">
+        <v>73</v>
+      </c>
+      <c r="H23">
+        <v>27</v>
+      </c>
+      <c r="I23">
+        <v>9</v>
+      </c>
+      <c r="J23">
+        <v>91</v>
+      </c>
+      <c r="L23">
+        <v>77</v>
+      </c>
+      <c r="M23">
+        <v>23</v>
+      </c>
+      <c r="N23">
+        <v>35</v>
+      </c>
+      <c r="O23">
+        <v>65</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="8"/>
+        <v>29</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="9"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="11"/>
+        <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>88</v>
+      </c>
+      <c r="C27">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>19</v>
+      </c>
+      <c r="E27">
+        <v>81</v>
+      </c>
+      <c r="G27">
+        <v>77</v>
+      </c>
+      <c r="H27">
+        <v>23</v>
+      </c>
+      <c r="I27">
+        <v>11</v>
+      </c>
+      <c r="J27">
+        <v>89</v>
+      </c>
+      <c r="L27">
+        <v>76</v>
+      </c>
+      <c r="M27">
+        <v>24</v>
+      </c>
+      <c r="N27">
+        <v>31</v>
+      </c>
+      <c r="O27">
+        <v>69</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" ref="Q24:Q31" si="12">AVERAGE(C27:D27)</f>
+        <v>15.5</v>
+      </c>
+      <c r="R27">
+        <f t="shared" ref="R24:R31" si="13">AVERAGE(H27:I27)</f>
+        <v>17</v>
+      </c>
+      <c r="S27">
+        <f t="shared" ref="S24:S31" si="14">AVERAGE(M27:N27)</f>
+        <v>27.5</v>
+      </c>
+      <c r="T27">
+        <f t="shared" ref="T24:T31" si="15">AVERAGE(Q27:S27)</f>
+        <v>20</v>
+      </c>
+      <c r="AA27">
+        <f>AVERAGE(T27:T31)</f>
+        <v>21.566666666666666</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" ref="AC24:AC31" si="16">MIN(Q27:S27)</f>
+        <v>15.5</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" ref="AD24:AD31" si="17">T27-AC27</f>
+        <v>4.5</v>
+      </c>
+      <c r="AE27">
+        <f>AVERAGE(AD27:AD31)</f>
+        <v>3.9666666666666663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>85</v>
+      </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>82</v>
+      </c>
+      <c r="G28">
+        <v>72</v>
+      </c>
+      <c r="H28">
+        <v>28</v>
+      </c>
+      <c r="I28">
+        <v>9</v>
+      </c>
+      <c r="J28">
+        <v>91</v>
+      </c>
+      <c r="L28">
+        <v>65</v>
+      </c>
+      <c r="M28">
+        <v>35</v>
+      </c>
+      <c r="N28">
+        <v>20</v>
+      </c>
+      <c r="O28">
+        <v>80</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="12"/>
+        <v>16.5</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="13"/>
+        <v>18.5</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="14"/>
+        <v>27.5</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="15"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="16"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="17"/>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>83</v>
+      </c>
+      <c r="C29">
+        <v>17</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>72</v>
+      </c>
+      <c r="G29">
+        <v>71</v>
+      </c>
+      <c r="H29">
+        <v>29</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <v>90</v>
+      </c>
+      <c r="L29">
+        <v>73</v>
+      </c>
+      <c r="M29">
+        <v>27</v>
+      </c>
+      <c r="N29">
+        <v>32</v>
+      </c>
+      <c r="O29">
+        <v>68</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="12"/>
+        <v>22.5</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="13"/>
+        <v>19.5</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="14"/>
+        <v>29.5</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="15"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="16"/>
+        <v>19.5</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="17"/>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>88</v>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <v>27</v>
+      </c>
+      <c r="E30">
+        <v>73</v>
+      </c>
+      <c r="G30">
+        <v>76</v>
+      </c>
+      <c r="H30">
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30">
+        <v>90</v>
+      </c>
+      <c r="L30">
+        <v>80</v>
+      </c>
+      <c r="M30">
+        <v>20</v>
+      </c>
+      <c r="N30">
+        <v>33</v>
+      </c>
+      <c r="O30">
+        <v>67</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="12"/>
+        <v>19.5</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="14"/>
+        <v>26.5</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>19</v>
+      </c>
+      <c r="E31">
+        <v>81</v>
+      </c>
+      <c r="G31">
+        <v>64</v>
+      </c>
+      <c r="H31">
+        <v>36</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>95</v>
+      </c>
+      <c r="L31">
+        <v>72</v>
+      </c>
+      <c r="M31">
+        <v>28</v>
+      </c>
+      <c r="N31">
+        <v>25</v>
+      </c>
+      <c r="O31">
+        <v>75</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="12"/>
+        <v>19.5</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="13"/>
+        <v>20.5</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="14"/>
+        <v>26.5</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="15"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="16"/>
+        <v>19.5</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="17"/>
+        <v>2.6666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -12147,22 +14168,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -12188,7 +14209,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -12298,7 +14319,7 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -12313,22 +14334,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -12354,7 +14375,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -12784,7 +14805,7 @@
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="s">
         <v>11</v>
@@ -12799,22 +14820,22 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
         <v>61</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
-      </c>
-      <c r="W2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
       </c>
       <c r="AA2" t="s">
         <v>1</v>
@@ -12840,7 +14861,7 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B343D2EE-9133-4F32-902A-F5041EE2736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EACD23-A803-4453-92A3-24F75265FA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="81">
   <si>
     <t>Dati originali</t>
   </si>
@@ -344,13 +344,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1044,72 +1043,34 @@
         <v>20</v>
       </c>
       <c r="G21">
-        <v>15.05</v>
+        <v>18.7</v>
       </c>
       <c r="H21">
-        <v>1.571446608843089</v>
+        <v>2.7748873851023195</v>
       </c>
       <c r="I21">
-        <v>19.8</v>
+        <v>18.5</v>
       </c>
       <c r="J21">
-        <v>2.9925834249951238</v>
+        <v>1.541103500742244</v>
       </c>
       <c r="K21">
-        <v>27.35</v>
+        <v>27.5</v>
       </c>
       <c r="L21">
-        <v>3.1976553910638899</v>
+        <v>1.2247448713915889</v>
       </c>
       <c r="M21">
-        <v>20.733333333333334</v>
+        <v>21.566666666666666</v>
       </c>
       <c r="N21">
-        <v>1.2794674818208691</v>
+        <v>1.4841757907262121</v>
       </c>
       <c r="O21">
-        <v>5.6833333333333327</v>
+        <v>3.9666666666666663</v>
       </c>
       <c r="P21">
-        <v>1.780293359096877</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22">
-        <v>15.05</v>
-      </c>
-      <c r="H22">
-        <v>1.571446608843089</v>
-      </c>
-      <c r="I22">
-        <v>19.8</v>
-      </c>
-      <c r="J22">
-        <v>2.9925834249951238</v>
-      </c>
-      <c r="K22">
-        <v>27.35</v>
-      </c>
-      <c r="L22">
-        <v>3.1976553910638899</v>
-      </c>
-      <c r="M22">
-        <v>20.733333333333334</v>
-      </c>
-      <c r="N22">
-        <v>1.2794674818208691</v>
-      </c>
-      <c r="O22">
-        <v>5.6833333333333327</v>
-      </c>
-      <c r="P22">
-        <v>1.780293359096877</v>
+        <v>0.74907350180814036</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
@@ -4816,23 +4777,23 @@
         <v>73</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
+        <f t="shared" ref="R3:R11" si="0">AVERAGE(C3:D3)</f>
         <v>15</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
+        <f t="shared" ref="S3:S11" si="1">AVERAGE(H3,I3)</f>
         <v>22</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
+        <f t="shared" ref="T3:T11" si="2">AVERAGE(M3:N3)</f>
         <v>24.5</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
+        <f t="shared" ref="U3:U11" si="3">AVERAGE(R3:T3)</f>
         <v>20.5</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
+        <f t="shared" ref="AD3:AD11" si="4">MIN(R3:T3)</f>
         <v>15</v>
       </c>
       <c r="AE3">
@@ -5411,16 +5372,16 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
+      <c r="B4">
         <v>82</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>18</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>20</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>80</v>
       </c>
       <c r="F4" s="2"/>
@@ -5515,16 +5476,16 @@
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+      <c r="B5">
         <v>91</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>20</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>80</v>
       </c>
       <c r="F5" s="2"/>
@@ -5579,16 +5540,16 @@
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
+      <c r="B6">
         <v>82</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>18</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>8</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>92</v>
       </c>
       <c r="F6" s="2"/>
@@ -5643,16 +5604,16 @@
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
+      <c r="B7">
         <v>89</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>11</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>18</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>82</v>
       </c>
       <c r="F7" s="2"/>
@@ -5707,16 +5668,16 @@
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+      <c r="B8">
         <v>84</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>16</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>10</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>90</v>
       </c>
       <c r="F8" s="2"/>
@@ -5771,16 +5732,16 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+      <c r="B9">
         <v>86</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>14</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>15</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9">
         <v>85</v>
       </c>
       <c r="F9" s="2"/>
@@ -5835,16 +5796,16 @@
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
+      <c r="B10">
         <v>80</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>20</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>11</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
         <v>89</v>
       </c>
       <c r="F10" s="2"/>
@@ -13346,43 +13307,71 @@
         <v>73</v>
       </c>
       <c r="Q16">
-        <f t="shared" ref="Q14:Q23" si="6">AVERAGE(C16:D16)</f>
+        <f t="shared" ref="Q16:Q23" si="6">AVERAGE(C16:D16)</f>
         <v>16.5</v>
       </c>
       <c r="R16">
-        <f t="shared" ref="R14:R23" si="7">AVERAGE(H16:I16)</f>
+        <f t="shared" ref="R16:R23" si="7">AVERAGE(H16:I16)</f>
         <v>22</v>
       </c>
       <c r="S16">
-        <f t="shared" ref="S14:S23" si="8">AVERAGE(M16:N16)</f>
+        <f t="shared" ref="S16:S23" si="8">AVERAGE(M16:N16)</f>
         <v>30</v>
       </c>
       <c r="T16">
-        <f t="shared" ref="T14:T23" si="9">AVERAGE(Q16:S16)</f>
+        <f t="shared" ref="T16:T23" si="9">AVERAGE(Q16:S16)</f>
         <v>22.833333333333332</v>
       </c>
       <c r="U16">
-        <f>AVERAGE(Q16:Q23)</f>
+        <f>AVERAGE(Q16:Q25)</f>
         <v>15.875</v>
       </c>
+      <c r="V16">
+        <f>_xlfn.STDEV.S(Q16:Q25)</f>
+        <v>1.3024701806293193</v>
+      </c>
+      <c r="W16">
+        <f>AVERAGE(R16:R25)</f>
+        <v>19.8125</v>
+      </c>
+      <c r="X16">
+        <f>_xlfn.STDEV.S(R16:R25)</f>
+        <v>2.8652785952802966</v>
+      </c>
+      <c r="Y16">
+        <f>AVERAGE(S16:S25)</f>
+        <v>28.375</v>
+      </c>
+      <c r="Z16">
+        <f>_xlfn.STDEV.S(S16:S25)</f>
+        <v>2.489262656175232</v>
+      </c>
       <c r="AA16">
-        <f>AVERAGE(T16:T23)</f>
+        <f>AVERAGE(T16:T25)</f>
         <v>21.354166666666668</v>
       </c>
+      <c r="AB16">
+        <f>_xlfn.STDEV.S(T16:T25)</f>
+        <v>1.456887037923613</v>
+      </c>
       <c r="AC16">
-        <f t="shared" ref="AC14:AC23" si="10">MIN(Q16:S16)</f>
+        <f t="shared" ref="AC16:AC23" si="10">MIN(Q16:S16)</f>
         <v>16.5</v>
       </c>
       <c r="AD16">
-        <f t="shared" ref="AD14:AD23" si="11">T16-AC16</f>
+        <f t="shared" ref="AD16:AD23" si="11">T16-AC16</f>
         <v>6.3333333333333321</v>
       </c>
       <c r="AE16">
-        <f>AVERAGE(AD16:AD23)</f>
+        <f>AVERAGE(AD16:AD25)</f>
         <v>5.4791666666666661</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF16">
+        <f>_xlfn.STDEV.S(AD16:AD25)</f>
+        <v>1.7399085453068361</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>88</v>
       </c>
@@ -13444,7 +13433,7 @@
         <v>7.8333333333333321</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>85</v>
       </c>
@@ -13506,7 +13495,7 @@
         <v>3.1666666666666679</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>90</v>
       </c>
@@ -13568,7 +13557,7 @@
         <v>7.3333333333333321</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>88</v>
       </c>
@@ -13630,7 +13619,7 @@
         <v>4.1666666666666679</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>87</v>
       </c>
@@ -13692,7 +13681,7 @@
         <v>6.1666666666666679</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>88</v>
       </c>
@@ -13754,7 +13743,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>92</v>
       </c>
@@ -13816,17 +13805,17 @@
         <v>5.3333333333333321</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>88</v>
       </c>
@@ -13864,39 +13853,71 @@
         <v>69</v>
       </c>
       <c r="Q27">
-        <f t="shared" ref="Q24:Q31" si="12">AVERAGE(C27:D27)</f>
+        <f t="shared" ref="Q27:Q31" si="12">AVERAGE(C27:D27)</f>
         <v>15.5</v>
       </c>
       <c r="R27">
-        <f t="shared" ref="R24:R31" si="13">AVERAGE(H27:I27)</f>
+        <f t="shared" ref="R27:R31" si="13">AVERAGE(H27:I27)</f>
         <v>17</v>
       </c>
       <c r="S27">
-        <f t="shared" ref="S24:S31" si="14">AVERAGE(M27:N27)</f>
+        <f t="shared" ref="S27:S31" si="14">AVERAGE(M27:N27)</f>
         <v>27.5</v>
       </c>
       <c r="T27">
-        <f t="shared" ref="T24:T31" si="15">AVERAGE(Q27:S27)</f>
+        <f t="shared" ref="T27:T31" si="15">AVERAGE(Q27:S27)</f>
         <v>20</v>
       </c>
+      <c r="U27">
+        <f>AVERAGE(Q27:Q36)</f>
+        <v>18.7</v>
+      </c>
+      <c r="V27">
+        <f>_xlfn.STDEV.S(Q27:Q36)</f>
+        <v>2.7748873851023195</v>
+      </c>
+      <c r="W27">
+        <f>AVERAGE(R27:R36)</f>
+        <v>18.5</v>
+      </c>
+      <c r="X27">
+        <f>_xlfn.STDEV.S(R27:R36)</f>
+        <v>1.541103500742244</v>
+      </c>
+      <c r="Y27">
+        <f>AVERAGE(S27:S36)</f>
+        <v>27.5</v>
+      </c>
+      <c r="Z27">
+        <f>_xlfn.STDEV.S(S27:S36)</f>
+        <v>1.2247448713915889</v>
+      </c>
       <c r="AA27">
-        <f>AVERAGE(T27:T31)</f>
+        <f>AVERAGE(T27:T36)</f>
         <v>21.566666666666666</v>
       </c>
+      <c r="AB27">
+        <f>_xlfn.STDEV.S(T27:T36)</f>
+        <v>1.4841757907262121</v>
+      </c>
       <c r="AC27">
-        <f t="shared" ref="AC24:AC31" si="16">MIN(Q27:S27)</f>
+        <f t="shared" ref="AC27:AC31" si="16">MIN(Q27:S27)</f>
         <v>15.5</v>
       </c>
       <c r="AD27">
-        <f t="shared" ref="AD24:AD31" si="17">T27-AC27</f>
+        <f t="shared" ref="AD27:AD31" si="17">T27-AC27</f>
         <v>4.5</v>
       </c>
       <c r="AE27">
-        <f>AVERAGE(AD27:AD31)</f>
+        <f>AVERAGE(AD27:AD36)</f>
         <v>3.9666666666666663</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF27">
+        <f>_xlfn.STDEV.S(AD27:AD36)</f>
+        <v>0.74907350180814036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>85</v>
       </c>
@@ -13958,7 +13979,7 @@
         <v>4.3333333333333321</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>83</v>
       </c>
@@ -14020,7 +14041,7 @@
         <v>4.3333333333333321</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>88</v>
       </c>
@@ -14082,7 +14103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>80</v>
       </c>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EACD23-A803-4453-92A3-24F75265FA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46356DC-3BE6-49E9-B246-3E1A1199FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1073,166 +1073,166 @@
         <v>0.74907350180814036</v>
       </c>
     </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
+      <c r="E23" t="s">
         <v>71</v>
       </c>
-      <c r="G24">
+      <c r="G23">
         <v>15.625</v>
       </c>
-      <c r="H24">
+      <c r="H23">
         <v>1.6007810593582121</v>
       </c>
-      <c r="I24">
+      <c r="I23">
         <v>18.625</v>
       </c>
-      <c r="J24">
+      <c r="J23">
         <v>2.75</v>
       </c>
-      <c r="K24">
+      <c r="K23">
+        <v>26.625</v>
+      </c>
+      <c r="L23">
+        <v>4.6435439052516774</v>
+      </c>
+      <c r="M23">
         <v>20.291666666666668</v>
       </c>
-      <c r="L24">
-        <v>4.6435439052516774</v>
-      </c>
-      <c r="M24">
-        <v>20.291666666666668</v>
-      </c>
-      <c r="N24">
+      <c r="N23">
         <v>1.8923579255834544</v>
       </c>
-      <c r="O24">
+      <c r="O23">
         <v>4.791666666666667</v>
       </c>
-      <c r="P24">
+      <c r="P23">
         <v>1.7393858004948073</v>
       </c>
     </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>72</v>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>16.416666666666668</v>
+      </c>
+      <c r="H26">
+        <v>2.8881943609574914</v>
+      </c>
+      <c r="I26">
+        <v>15.416666666666666</v>
+      </c>
+      <c r="J26">
+        <v>1.2812754062521714</v>
+      </c>
+      <c r="K26">
+        <v>29.916666666666668</v>
+      </c>
+      <c r="L26">
+        <v>2.437553418218084</v>
+      </c>
+      <c r="M26">
+        <v>20.583333333333332</v>
+      </c>
+      <c r="N26">
+        <v>1.3570801990548194</v>
+      </c>
+      <c r="O26">
+        <v>5.916666666666667</v>
+      </c>
+      <c r="P26">
+        <v>1.0527741131569135</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>4</v>
+        <v>71</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
       </c>
       <c r="G27">
-        <v>16.416666666666668</v>
+        <v>16.8</v>
       </c>
       <c r="H27">
-        <v>2.8881943609574914</v>
+        <v>0.57008771254956903</v>
       </c>
       <c r="I27">
-        <v>15.416666666666666</v>
+        <v>17.7</v>
       </c>
       <c r="J27">
-        <v>1.2812754062521714</v>
+        <v>1.7175564037317668</v>
       </c>
       <c r="K27">
-        <v>29.916666666666668</v>
+        <v>28.9</v>
       </c>
       <c r="L27">
-        <v>2.437553418218084</v>
+        <v>3.8794329482541587</v>
       </c>
       <c r="M27">
-        <v>20.583333333333332</v>
+        <v>21.133333333333333</v>
       </c>
       <c r="N27">
-        <v>1.3570801990548194</v>
+        <v>1.5696779570628134</v>
       </c>
       <c r="O27">
-        <v>5.916666666666667</v>
+        <v>4.7333333333333325</v>
       </c>
       <c r="P27">
-        <v>1.0527741131569135</v>
+        <v>0.90215790684828923</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
         <v>71</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G30">
+        <v>16.375</v>
+      </c>
+      <c r="H30">
+        <v>3.3008837200563934</v>
+      </c>
+      <c r="I30">
         <v>20</v>
       </c>
-      <c r="G28">
-        <v>16.8</v>
-      </c>
-      <c r="H28">
-        <v>0.57008771254956903</v>
-      </c>
-      <c r="I28">
-        <v>17.7</v>
-      </c>
-      <c r="J28">
-        <v>1.7175564037317668</v>
-      </c>
-      <c r="K28">
-        <v>28.9</v>
-      </c>
-      <c r="L28">
-        <v>3.8794329482541587</v>
-      </c>
-      <c r="M28">
-        <v>21.133333333333333</v>
-      </c>
-      <c r="N28">
-        <v>1.5696779570628134</v>
-      </c>
-      <c r="O28">
-        <v>4.7333333333333325</v>
-      </c>
-      <c r="P28">
-        <v>0.90215790684828923</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31">
-        <v>16.375</v>
-      </c>
-      <c r="H31">
-        <v>3.3008837200563934</v>
-      </c>
-      <c r="I31">
-        <v>20</v>
-      </c>
-      <c r="J31">
+      <c r="J30">
         <v>3.3166247903553998</v>
       </c>
-      <c r="K31">
+      <c r="K30">
         <v>26.875</v>
       </c>
-      <c r="L31">
+      <c r="L30">
         <v>1.796988221070652</v>
       </c>
-      <c r="M31">
+      <c r="M30">
         <v>21.083333333333332</v>
       </c>
-      <c r="N31">
+      <c r="N30">
         <v>1.5898986690282424</v>
       </c>
-      <c r="O31">
+      <c r="O30">
         <v>4.708333333333333</v>
       </c>
-      <c r="P31">
+      <c r="P30">
         <v>2.9071272570854019</v>
       </c>
     </row>
@@ -11351,8 +11351,8 @@
         <v>2.75</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(T4:T7)</f>
-        <v>20.291666666666668</v>
+        <f>AVERAGE(S4:S7)</f>
+        <v>26.625</v>
       </c>
       <c r="Z4">
         <f>_xlfn.STDEV.S(S4:S7)</f>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46356DC-3BE6-49E9-B246-3E1A1199FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE49676-538D-4FC1-B49D-DF8244159C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="83">
   <si>
     <t>Dati originali</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>88,12,19,81</t>
+  </si>
+  <si>
+    <t>try3</t>
+  </si>
+  <si>
+    <t>DIFFTry3</t>
   </si>
 </sst>
 </file>
@@ -869,6 +875,41 @@
         <v>0.87589712135373932</v>
       </c>
     </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11">
+        <v>17.625</v>
+      </c>
+      <c r="H11">
+        <v>1.796988221070652</v>
+      </c>
+      <c r="I11">
+        <v>21.375</v>
+      </c>
+      <c r="J11">
+        <v>1.8874586088176875</v>
+      </c>
+      <c r="K11">
+        <v>31.375</v>
+      </c>
+      <c r="L11">
+        <v>1.6520189667999174</v>
+      </c>
+      <c r="M11">
+        <v>23.458333333333332</v>
+      </c>
+      <c r="N11">
+        <v>0.49767980186580402</v>
+      </c>
+      <c r="O11">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="P11">
+        <v>1.3402597868683128</v>
+      </c>
+    </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>62</v>
@@ -5304,7 +5345,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A2:AF10"/>
+  <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -5857,6 +5898,299 @@
       <c r="V10">
         <f t="shared" si="5"/>
         <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>82</v>
+      </c>
+      <c r="C12">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>85</v>
+      </c>
+      <c r="G12">
+        <v>63</v>
+      </c>
+      <c r="H12">
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12">
+        <v>91</v>
+      </c>
+      <c r="L12">
+        <v>57</v>
+      </c>
+      <c r="M12">
+        <v>43</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>82</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q11:Q15" si="6">AVERAGE(C12,D12)</f>
+        <v>16.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R11:R15" si="7">AVERAGE(H12,I12)</f>
+        <v>23</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S11:S15" si="8">AVERAGE(M12,N12)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T11:T15" si="9">AVERAGE(Q12:S12)</f>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ref="U11:U15" si="10">MIN(Q12:S12)</f>
+        <v>16.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V11:V15" si="11">T12-U12</f>
+        <v>6.8333333333333321</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>17.625</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>1.796988221070652</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(R12:R18)</f>
+        <v>21.375</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>1.8874586088176875</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(S12:S18)</f>
+        <v>31.375</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>1.6520189667999174</v>
+      </c>
+      <c r="AC12">
+        <f>AVERAGE(T12:T18)</f>
+        <v>23.458333333333332</v>
+      </c>
+      <c r="AD12">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>0.49767980186580402</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(V12:V18)</f>
+        <v>5.833333333333333</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>1.3402597868683128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>84</v>
+      </c>
+      <c r="G13">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>37</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>97</v>
+      </c>
+      <c r="L13">
+        <v>56</v>
+      </c>
+      <c r="M13">
+        <v>44</v>
+      </c>
+      <c r="N13">
+        <v>22</v>
+      </c>
+      <c r="O13">
+        <v>78</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>33</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>82</v>
+      </c>
+      <c r="C14">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>78</v>
+      </c>
+      <c r="G14">
+        <v>67</v>
+      </c>
+      <c r="H14">
+        <v>33</v>
+      </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
+      <c r="J14">
+        <v>87</v>
+      </c>
+      <c r="L14">
+        <v>67</v>
+      </c>
+      <c r="M14">
+        <v>33</v>
+      </c>
+      <c r="N14">
+        <v>26</v>
+      </c>
+      <c r="O14">
+        <v>74</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>76</v>
+      </c>
+      <c r="G15">
+        <v>67</v>
+      </c>
+      <c r="H15">
+        <v>33</v>
+      </c>
+      <c r="I15">
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <v>94</v>
+      </c>
+      <c r="L15">
+        <v>68</v>
+      </c>
+      <c r="M15">
+        <v>32</v>
+      </c>
+      <c r="N15">
+        <v>33</v>
+      </c>
+      <c r="O15">
+        <v>67</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>19.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>32.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="11"/>
+        <v>5.3333333333333321</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE49676-538D-4FC1-B49D-DF8244159C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BA85B2-4747-4CE2-A493-53BBEDD0B5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="83">
   <si>
     <t>Dati originali</t>
   </si>
@@ -636,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1115,165 +1115,170 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
         <v>71</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>15.625</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>1.6007810593582121</v>
       </c>
-      <c r="I23">
+      <c r="I24">
         <v>18.625</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>2.75</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>26.625</v>
       </c>
-      <c r="L23">
+      <c r="L24">
         <v>4.6435439052516774</v>
       </c>
-      <c r="M23">
+      <c r="M24">
         <v>20.291666666666668</v>
       </c>
-      <c r="N23">
+      <c r="N24">
         <v>1.8923579255834544</v>
       </c>
-      <c r="O23">
+      <c r="O24">
         <v>4.791666666666667</v>
       </c>
-      <c r="P23">
+      <c r="P24">
         <v>1.7393858004948073</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26">
-        <v>16.416666666666668</v>
-      </c>
-      <c r="H26">
-        <v>2.8881943609574914</v>
-      </c>
-      <c r="I26">
-        <v>15.416666666666666</v>
-      </c>
-      <c r="J26">
-        <v>1.2812754062521714</v>
-      </c>
-      <c r="K26">
-        <v>29.916666666666668</v>
-      </c>
-      <c r="L26">
-        <v>2.437553418218084</v>
-      </c>
-      <c r="M26">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N26">
-        <v>1.3570801990548194</v>
-      </c>
-      <c r="O26">
-        <v>5.916666666666667</v>
-      </c>
-      <c r="P26">
-        <v>1.0527741131569135</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>16.8</v>
+        <v>16.416666666666668</v>
       </c>
       <c r="H27">
-        <v>0.57008771254956903</v>
+        <v>2.8881943609574914</v>
       </c>
       <c r="I27">
-        <v>17.7</v>
+        <v>15.416666666666666</v>
       </c>
       <c r="J27">
-        <v>1.7175564037317668</v>
+        <v>1.2812754062521714</v>
       </c>
       <c r="K27">
-        <v>28.9</v>
+        <v>29.916666666666668</v>
       </c>
       <c r="L27">
-        <v>3.8794329482541587</v>
+        <v>2.437553418218084</v>
       </c>
       <c r="M27">
-        <v>21.133333333333333</v>
+        <v>20.583333333333332</v>
       </c>
       <c r="N27">
-        <v>1.5696779570628134</v>
+        <v>1.3570801990548194</v>
       </c>
       <c r="O27">
-        <v>4.7333333333333325</v>
+        <v>5.916666666666667</v>
       </c>
       <c r="P27">
-        <v>0.90215790684828923</v>
+        <v>1.0527741131569135</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28">
+        <v>16.8</v>
+      </c>
+      <c r="H28">
+        <v>0.57008771254956903</v>
+      </c>
+      <c r="I28">
+        <v>17.7</v>
+      </c>
+      <c r="J28">
+        <v>1.7175564037317668</v>
+      </c>
+      <c r="K28">
+        <v>28.9</v>
+      </c>
+      <c r="L28">
+        <v>3.8794329482541587</v>
+      </c>
+      <c r="M28">
+        <v>21.133333333333333</v>
+      </c>
+      <c r="N28">
+        <v>1.5696779570628134</v>
+      </c>
+      <c r="O28">
+        <v>4.7333333333333325</v>
+      </c>
+      <c r="P28">
+        <v>0.90215790684828923</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E30" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
         <v>71</v>
       </c>
-      <c r="G30">
+      <c r="G31">
         <v>16.375</v>
       </c>
-      <c r="H30">
+      <c r="H31">
         <v>3.3008837200563934</v>
       </c>
-      <c r="I30">
+      <c r="I31">
         <v>20</v>
       </c>
-      <c r="J30">
+      <c r="J31">
         <v>3.3166247903553998</v>
       </c>
-      <c r="K30">
+      <c r="K31">
         <v>26.875</v>
       </c>
-      <c r="L30">
+      <c r="L31">
         <v>1.796988221070652</v>
       </c>
-      <c r="M30">
+      <c r="M31">
         <v>21.083333333333332</v>
       </c>
-      <c r="N30">
+      <c r="N31">
         <v>1.5898986690282424</v>
       </c>
-      <c r="O30">
+      <c r="O31">
         <v>4.708333333333333</v>
       </c>
-      <c r="P30">
+      <c r="P31">
         <v>2.9071272570854019</v>
       </c>
     </row>
@@ -5943,27 +5948,27 @@
         <v>82</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q11:Q15" si="6">AVERAGE(C12,D12)</f>
+        <f t="shared" ref="Q12:Q15" si="6">AVERAGE(C12,D12)</f>
         <v>16.5</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R11:R15" si="7">AVERAGE(H12,I12)</f>
+        <f t="shared" ref="R12:R15" si="7">AVERAGE(H12,I12)</f>
         <v>23</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S11:S15" si="8">AVERAGE(M12,N12)</f>
+        <f t="shared" ref="S12:S15" si="8">AVERAGE(M12,N12)</f>
         <v>30.5</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T11:T15" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T15" si="9">AVERAGE(Q12:S12)</f>
         <v>23.333333333333332</v>
       </c>
       <c r="U12">
-        <f t="shared" ref="U11:U15" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="U12:U15" si="10">MIN(Q12:S12)</f>
         <v>16.5</v>
       </c>
       <c r="V12">
-        <f t="shared" ref="V11:V15" si="11">T12-U12</f>
+        <f t="shared" ref="V12:V15" si="11">T12-U12</f>
         <v>6.8333333333333321</v>
       </c>
       <c r="W12">
@@ -14669,7 +14674,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF9"/>
+  <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -15146,6 +15151,11 @@
       <c r="AD9">
         <f t="shared" si="5"/>
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BA85B2-4747-4CE2-A493-53BBEDD0B5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD836C5-5436-4C50-9C59-2E78A5A61823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId5"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId8"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId9"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId6"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId7"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId8"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="84">
   <si>
     <t>Dati originali</t>
   </si>
@@ -301,6 +302,9 @@
   </si>
   <si>
     <t>DIFFTry3</t>
+  </si>
+  <si>
+    <t>try</t>
   </si>
 </sst>
 </file>
@@ -636,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1118,6 +1122,36 @@
       <c r="F22" t="s">
         <v>81</v>
       </c>
+      <c r="G22">
+        <v>16.5</v>
+      </c>
+      <c r="H22">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="I22">
+        <v>17.25</v>
+      </c>
+      <c r="J22">
+        <v>3.378855822118882</v>
+      </c>
+      <c r="K22">
+        <v>31.25</v>
+      </c>
+      <c r="L22">
+        <v>3.1754264805429417</v>
+      </c>
+      <c r="M22">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="N22">
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="O22">
+        <v>5.7916666666666679</v>
+      </c>
+      <c r="P22">
+        <v>1.6007810593582092</v>
+      </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
@@ -1159,6 +1193,41 @@
         <v>1.7393858004948073</v>
       </c>
     </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25">
+        <v>14.875</v>
+      </c>
+      <c r="H25">
+        <v>4.0697051490249265</v>
+      </c>
+      <c r="I25">
+        <v>16.5</v>
+      </c>
+      <c r="J25">
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="K25">
+        <v>27</v>
+      </c>
+      <c r="L25">
+        <v>3.3416562759605704</v>
+      </c>
+      <c r="M25">
+        <v>19.458333333333332</v>
+      </c>
+      <c r="N25">
+        <v>2.1273135553939757</v>
+      </c>
+      <c r="O25">
+        <v>5.2083333333333304</v>
+      </c>
+      <c r="P25">
+        <v>1.674288129546627</v>
+      </c>
+    </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>72</v>
@@ -1237,49 +1306,122 @@
         <v>0.90215790684828923</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31">
+        <v>16</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>15.75</v>
+      </c>
+      <c r="J31">
+        <v>4.5961940777125587</v>
+      </c>
+      <c r="K31">
+        <v>30</v>
+      </c>
+      <c r="L31">
+        <v>3.5355339059327378</v>
+      </c>
+      <c r="M31">
+        <v>20.583333333333332</v>
+      </c>
+      <c r="N31">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="O31">
+        <v>6.3333333333333321</v>
+      </c>
+      <c r="P31">
+        <v>2.1213203435596459</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E31" t="s">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
         <v>71</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>16.375</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>3.3008837200563934</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>20</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>3.3166247903553998</v>
       </c>
-      <c r="K31">
+      <c r="K33">
         <v>26.875</v>
       </c>
-      <c r="L31">
+      <c r="L33">
         <v>1.796988221070652</v>
       </c>
-      <c r="M31">
+      <c r="M33">
         <v>21.083333333333332</v>
       </c>
-      <c r="N31">
+      <c r="N33">
         <v>1.5898986690282424</v>
       </c>
-      <c r="O31">
+      <c r="O33">
         <v>4.708333333333333</v>
       </c>
-      <c r="P31">
+      <c r="P33">
         <v>2.9071272570854019</v>
+      </c>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34">
+        <v>14.333333333333334</v>
+      </c>
+      <c r="H34">
+        <v>3.2145502536643153</v>
+      </c>
+      <c r="I34">
+        <v>17.166666666666668</v>
+      </c>
+      <c r="J34">
+        <v>1.2583057392117916</v>
+      </c>
+      <c r="K34">
+        <v>26.6666666666667</v>
+      </c>
+      <c r="L34">
+        <v>4.1633319989322564</v>
+      </c>
+      <c r="M34">
+        <v>19.3888888888889</v>
+      </c>
+      <c r="N34">
+        <v>2.4962935487400935</v>
+      </c>
+      <c r="O34">
+        <v>5.0555555555555562</v>
+      </c>
+      <c r="P34">
+        <v>1.3977495139343468</v>
       </c>
     </row>
   </sheetData>
@@ -1289,6 +1431,557 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>85</v>
+      </c>
+      <c r="G4">
+        <v>61</v>
+      </c>
+      <c r="H4">
+        <v>39</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>93</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>20</v>
+      </c>
+      <c r="O4">
+        <v>80</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>23</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>24</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q10)</f>
+        <v>14.214285714285714</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q10)</f>
+        <v>2.0987524639084736</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R10)</f>
+        <v>23</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R10)</f>
+        <v>2.5495097567963922</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S10)</f>
+        <v>31.428571428571427</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S10)</f>
+        <v>5.2870011303555522</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T10)</f>
+        <v>22.88095238095238</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T10)</f>
+        <v>2.2601914981845255</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>7.3333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD10)</f>
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD10)</f>
+        <v>2.0971762320196583</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>87</v>
+      </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>85</v>
+      </c>
+      <c r="G5">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>51</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>98</v>
+      </c>
+      <c r="L5">
+        <v>58</v>
+      </c>
+      <c r="M5">
+        <v>42</v>
+      </c>
+      <c r="N5">
+        <v>25</v>
+      </c>
+      <c r="O5">
+        <v>75</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
+        <v>14</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
+        <v>26.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
+        <v>33.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
+        <v>14</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
+        <v>10.666666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>84</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>81</v>
+      </c>
+      <c r="G6">
+        <v>56</v>
+      </c>
+      <c r="H6">
+        <v>44</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>92</v>
+      </c>
+      <c r="L6">
+        <v>69</v>
+      </c>
+      <c r="M6">
+        <v>31</v>
+      </c>
+      <c r="N6">
+        <v>25</v>
+      </c>
+      <c r="O6">
+        <v>75</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>6.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>88</v>
+      </c>
+      <c r="G7">
+        <v>67</v>
+      </c>
+      <c r="H7">
+        <v>33</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>92</v>
+      </c>
+      <c r="L7">
+        <v>58</v>
+      </c>
+      <c r="M7">
+        <v>42</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>77</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>20.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>89</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>81</v>
+      </c>
+      <c r="G8">
+        <v>62</v>
+      </c>
+      <c r="H8">
+        <v>38</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>91</v>
+      </c>
+      <c r="L8">
+        <v>52</v>
+      </c>
+      <c r="M8">
+        <v>48</v>
+      </c>
+      <c r="N8">
+        <v>34</v>
+      </c>
+      <c r="O8">
+        <v>66</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>23.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>26.5</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>84</v>
+      </c>
+      <c r="G9">
+        <v>65</v>
+      </c>
+      <c r="H9">
+        <v>35</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>92</v>
+      </c>
+      <c r="L9">
+        <v>65</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
+      </c>
+      <c r="N9">
+        <v>24</v>
+      </c>
+      <c r="O9">
+        <v>76</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>29.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>7.6666666666666679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>83</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>86</v>
+      </c>
+      <c r="G10">
+        <v>64</v>
+      </c>
+      <c r="H10">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>96</v>
+      </c>
+      <c r="L10">
+        <v>64</v>
+      </c>
+      <c r="M10">
+        <v>36</v>
+      </c>
+      <c r="N10">
+        <v>27</v>
+      </c>
+      <c r="O10">
+        <v>73</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>6.8333333333333321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1777,7 +2470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AO99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4616,7 +5309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5348,7 +6041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6203,7 +6896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AN41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7640,7 +8333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AL41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8717,7 +9410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11253,7 +11946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11553,7 +12246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11909,6 +12602,299 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>84</v>
+      </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>89</v>
+      </c>
+      <c r="G10">
+        <v>76</v>
+      </c>
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10">
+        <v>94</v>
+      </c>
+      <c r="L10">
+        <v>67</v>
+      </c>
+      <c r="M10">
+        <v>33</v>
+      </c>
+      <c r="N10">
+        <v>27</v>
+      </c>
+      <c r="O10">
+        <v>73</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q10:Q13" si="6">AVERAGE(C10:D10)</f>
+        <v>13.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R10:R13" si="7">AVERAGE(H10:I10)</f>
+        <v>15</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S10:S13" si="8">AVERAGE(M10:N10)</f>
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T10:T13" si="9">AVERAGE(Q10:S10)</f>
+        <v>19.5</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q13)</f>
+        <v>14.875</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q13)</f>
+        <v>4.0697051490249265</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R13)</f>
+        <v>16.5</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R13)</f>
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S13)</f>
+        <v>27</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S13)</f>
+        <v>3.3416562759605704</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T13)</f>
+        <v>19.458333333333332</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
+        <v>2.1273135553939757</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" ref="AC10:AC13" si="10">MIN(Q10:S10)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" ref="AD10:AD13" si="11">T10-AC10</f>
+        <v>6</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD13)</f>
+        <v>5.208333333333333</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD13)</f>
+        <v>1.674288129546627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>87</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>78</v>
+      </c>
+      <c r="H11">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <v>17</v>
+      </c>
+      <c r="J11">
+        <v>83</v>
+      </c>
+      <c r="L11">
+        <v>70</v>
+      </c>
+      <c r="M11">
+        <v>30</v>
+      </c>
+      <c r="N11">
+        <v>29</v>
+      </c>
+      <c r="O11">
+        <v>71</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>19.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>78</v>
+      </c>
+      <c r="G12">
+        <v>74</v>
+      </c>
+      <c r="H12">
+        <v>26</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12">
+        <v>92</v>
+      </c>
+      <c r="L12">
+        <v>72</v>
+      </c>
+      <c r="M12">
+        <v>28</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>82</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>19.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>2.8333333333333321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>92</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>88</v>
+      </c>
+      <c r="G13">
+        <v>79</v>
+      </c>
+      <c r="H13">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>8</v>
+      </c>
+      <c r="J13">
+        <v>92</v>
+      </c>
+      <c r="L13">
+        <v>72</v>
+      </c>
+      <c r="M13">
+        <v>28</v>
+      </c>
+      <c r="N13">
+        <v>23</v>
+      </c>
+      <c r="O13">
+        <v>77</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>14.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>25.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>6.6666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -11917,6 +12903,230 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1341680-B8DF-484F-AD8E-90C5FE6FD057}">
+  <dimension ref="B1:AF3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" t="s">
+        <v>51</v>
+      </c>
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>87</v>
+      </c>
+      <c r="G2">
+        <v>78</v>
+      </c>
+      <c r="H2">
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>97</v>
+      </c>
+      <c r="L2">
+        <v>65</v>
+      </c>
+      <c r="M2">
+        <v>35</v>
+      </c>
+      <c r="N2">
+        <v>30</v>
+      </c>
+      <c r="O2">
+        <v>70</v>
+      </c>
+      <c r="Q2">
+        <f>AVERAGE(C2,D2)</f>
+        <v>16</v>
+      </c>
+      <c r="R2">
+        <f>AVERAGE(H2,I2)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGE(M2,N2)</f>
+        <v>32.5</v>
+      </c>
+      <c r="T2">
+        <f>AVERAGE(Q2:S2)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2,Q3)</f>
+        <v>16</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2,Q3)</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2,R3)</f>
+        <v>15.75</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2,R3)</f>
+        <v>4.5961940777125587</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2,S3)</f>
+        <v>30</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2,S3)</f>
+        <v>3.5355339059327378</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2,T3)</f>
+        <v>20.583333333333332</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2,T3)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="AC2">
+        <f>MIN(Q2:S2)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <f>(T2-AC2)</f>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2,AD3)</f>
+        <v>6.3333333333333321</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2,AD3)</f>
+        <v>2.1213203435596459</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>88</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>82</v>
+      </c>
+      <c r="L3">
+        <v>72</v>
+      </c>
+      <c r="M3">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>27</v>
+      </c>
+      <c r="O3">
+        <v>73</v>
+      </c>
+      <c r="Q3">
+        <f>AVERAGE(C3,D3)</f>
+        <v>16</v>
+      </c>
+      <c r="R3">
+        <f>AVERAGE(H3,I3)</f>
+        <v>19</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGE(M3,N3)</f>
+        <v>27.5</v>
+      </c>
+      <c r="T3">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC3">
+        <f>MIN(Q3:S3)</f>
+        <v>16</v>
+      </c>
+      <c r="AD3">
+        <f>(T3-AC3)</f>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12082,9 +13292,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -12442,12 +13652,243 @@
         <v>3</v>
       </c>
     </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>79</v>
+      </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>11</v>
+      </c>
+      <c r="J10">
+        <v>89</v>
+      </c>
+      <c r="L10">
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <v>84</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q10:Q12" si="6">AVERAGE(C10:D10)</f>
+        <v>12</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R10:R12" si="7">AVERAGE(H10:I10)</f>
+        <v>16</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S10:S12" si="8">AVERAGE(M10:N10)</f>
+        <v>28</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T10:T12" si="9">AVERAGE(Q10:S10)</f>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q13)</f>
+        <v>14.333333333333334</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q13)</f>
+        <v>3.2145502536643153</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R13)</f>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R13)</f>
+        <v>1.2583057392117916</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S13)</f>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S13)</f>
+        <v>4.1633319989322564</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T13)</f>
+        <v>19.388888888888889</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
+        <v>2.4962935487400935</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" ref="AC10:AC12" si="10">MIN(Q10:S10)</f>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" ref="AD10:AD12" si="11">T10-AC10</f>
+        <v>6.6666666666666679</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD13)</f>
+        <v>5.0555555555555562</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD13)</f>
+        <v>1.3977495139343468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>81</v>
+      </c>
+      <c r="H11">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="L11">
+        <v>78</v>
+      </c>
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>38</v>
+      </c>
+      <c r="O11">
+        <v>62</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>91</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>83</v>
+      </c>
+      <c r="G12">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>13</v>
+      </c>
+      <c r="J12">
+        <v>87</v>
+      </c>
+      <c r="L12">
+        <v>74</v>
+      </c>
+      <c r="M12">
+        <v>26</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>82</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>4.3333333333333321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12871,7 +14312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14509,7 +15950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14672,9 +16113,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF10"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -15158,555 +16599,292 @@
         <v>81</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q2" t="s">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>75</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>92</v>
+      </c>
+      <c r="L11">
+        <v>67</v>
+      </c>
+      <c r="M11">
+        <v>33</v>
+      </c>
+      <c r="N11">
+        <v>27</v>
+      </c>
+      <c r="O11">
+        <v>73</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ref="Q11:Q14" si="6">AVERAGE(C11,D11)</f>
+        <v>17</v>
+      </c>
+      <c r="R11">
+        <f t="shared" ref="R11:R14" si="7">AVERAGE(H11,I11)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" ref="S11:S14" si="8">AVERAGE(M11,N11)</f>
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ref="T11:T14" si="9">AVERAGE(Q11:S11)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f>AVERAGE(Q11:Q16)</f>
+        <v>16.5</v>
+      </c>
+      <c r="V11">
+        <f>_xlfn.STDEV.S(Q11:Q16)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W11">
+        <f>AVERAGE(R11:R16)</f>
+        <v>17.25</v>
+      </c>
+      <c r="X11">
+        <f>_xlfn.STDEV.S(R11:R16)</f>
+        <v>3.378855822118882</v>
+      </c>
+      <c r="Y11">
+        <f>AVERAGE(S11:S16)</f>
+        <v>31.25</v>
+      </c>
+      <c r="Z11">
+        <f>_xlfn.STDEV.S(S11:S16)</f>
+        <v>3.1754264805429417</v>
+      </c>
+      <c r="AA11">
+        <f>AVERAGE(T11:T16)</f>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AB11">
+        <f>_xlfn.STDEV.S(T11:T16)</f>
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" ref="AC11:AC14" si="10">MIN(Q11:S11)</f>
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" ref="AD11:AD14" si="11">(T11-AC11)</f>
+        <v>4.6666666666666679</v>
+      </c>
+      <c r="AE11">
+        <f>AVERAGE(AD11:AD16)</f>
+        <v>5.7916666666666679</v>
+      </c>
+      <c r="AF11">
+        <f>_xlfn.STDEV.S(AD11:AD16)</f>
+        <v>1.6007810593582092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>72</v>
+      </c>
+      <c r="G12">
+        <v>67</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12">
         <v>11</v>
       </c>
-      <c r="R2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="J12">
+        <v>89</v>
+      </c>
+      <c r="L12">
+        <v>65</v>
+      </c>
+      <c r="M12">
+        <v>35</v>
+      </c>
+      <c r="N12">
+        <v>36</v>
+      </c>
+      <c r="O12">
+        <v>64</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>35.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>8.1666666666666679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>87</v>
+      </c>
+      <c r="C13">
         <v>13</v>
       </c>
-      <c r="T2" t="s">
-        <v>15</v>
-      </c>
-      <c r="U2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC2" t="s">
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>82</v>
+      </c>
+      <c r="G13">
+        <v>76</v>
+      </c>
+      <c r="H13">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>96</v>
+      </c>
+      <c r="L13">
+        <v>70</v>
+      </c>
+      <c r="M13">
+        <v>30</v>
+      </c>
+      <c r="N13">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>5.1666666666666679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>80</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>86</v>
+      </c>
+      <c r="G14">
+        <v>71</v>
+      </c>
+      <c r="H14">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>96</v>
+      </c>
+      <c r="L14">
+        <v>62</v>
+      </c>
+      <c r="M14">
+        <v>38</v>
+      </c>
+      <c r="N14">
+        <v>25</v>
+      </c>
+      <c r="O14">
+        <v>75</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="AD2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>90</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>85</v>
-      </c>
-      <c r="G4">
-        <v>61</v>
-      </c>
-      <c r="H4">
-        <v>39</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>93</v>
-      </c>
-      <c r="L4">
-        <v>72</v>
-      </c>
-      <c r="M4">
-        <v>28</v>
-      </c>
-      <c r="N4">
-        <v>20</v>
-      </c>
-      <c r="O4">
-        <v>80</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>23</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>24</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q10)</f>
-        <v>14.214285714285714</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q10)</f>
-        <v>2.0987524639084736</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R10)</f>
-        <v>23</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R10)</f>
-        <v>2.5495097567963922</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S10)</f>
-        <v>31.428571428571427</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S10)</f>
-        <v>5.2870011303555522</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T10)</f>
-        <v>22.88095238095238</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T10)</f>
-        <v>2.2601914981845255</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>7.3333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD10)</f>
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD10)</f>
-        <v>2.0971762320196583</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>87</v>
-      </c>
-      <c r="C5">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>85</v>
-      </c>
-      <c r="G5">
-        <v>49</v>
-      </c>
-      <c r="H5">
-        <v>51</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>98</v>
-      </c>
-      <c r="L5">
-        <v>58</v>
-      </c>
-      <c r="M5">
-        <v>42</v>
-      </c>
-      <c r="N5">
-        <v>25</v>
-      </c>
-      <c r="O5">
-        <v>75</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
-        <v>14</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
-        <v>26.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
-        <v>33.5</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
-        <v>14</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
-        <v>10.666666666666668</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>84</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>81</v>
-      </c>
-      <c r="G6">
-        <v>56</v>
-      </c>
-      <c r="H6">
-        <v>44</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>92</v>
-      </c>
-      <c r="L6">
-        <v>69</v>
-      </c>
-      <c r="M6">
-        <v>31</v>
-      </c>
-      <c r="N6">
-        <v>25</v>
-      </c>
-      <c r="O6">
-        <v>75</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>23.833333333333332</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>17.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>6.3333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>90</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>12</v>
-      </c>
-      <c r="E7">
-        <v>88</v>
-      </c>
-      <c r="G7">
-        <v>67</v>
-      </c>
-      <c r="H7">
-        <v>33</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>92</v>
-      </c>
-      <c r="L7">
-        <v>58</v>
-      </c>
-      <c r="M7">
-        <v>42</v>
-      </c>
-      <c r="N7">
-        <v>23</v>
-      </c>
-      <c r="O7">
-        <v>77</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>20.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>32.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>21.333333333333332</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>10.333333333333332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>89</v>
-      </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>81</v>
-      </c>
-      <c r="G8">
-        <v>62</v>
-      </c>
-      <c r="H8">
-        <v>38</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>91</v>
-      </c>
-      <c r="L8">
-        <v>52</v>
-      </c>
-      <c r="M8">
-        <v>48</v>
-      </c>
-      <c r="N8">
-        <v>34</v>
-      </c>
-      <c r="O8">
-        <v>66</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>23.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>26.5</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>88</v>
-      </c>
-      <c r="C9">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
-      <c r="G9">
-        <v>65</v>
-      </c>
-      <c r="H9">
-        <v>35</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>92</v>
-      </c>
-      <c r="L9">
-        <v>65</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-      <c r="N9">
-        <v>24</v>
-      </c>
-      <c r="O9">
-        <v>76</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>21.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>29.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
         <v>21.666666666666668</v>
       </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>7.6666666666666679</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>83</v>
-      </c>
-      <c r="C10">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>14</v>
-      </c>
-      <c r="E10">
-        <v>86</v>
-      </c>
-      <c r="G10">
-        <v>64</v>
-      </c>
-      <c r="H10">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>4</v>
-      </c>
-      <c r="J10">
-        <v>96</v>
-      </c>
-      <c r="L10">
-        <v>64</v>
-      </c>
-      <c r="M10">
-        <v>36</v>
-      </c>
-      <c r="N10">
-        <v>27</v>
-      </c>
-      <c r="O10">
-        <v>73</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="2"/>
-        <v>31.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="3"/>
-        <v>22.333333333333332</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="5"/>
-        <v>6.8333333333333321</v>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>5.1666666666666679</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CI/0.05/Results.xlsx
+++ b/DataAnalysis/CI/0.05/Results.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD836C5-5436-4C50-9C59-2E78A5A61823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BA1E91-2D0C-4A17-9D0E-FC10BF2B56CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId3"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId6"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId7"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId8"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId11"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="21" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId4"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId5"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId6"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId8"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId9"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId12"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId13"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId14"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId16"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId17"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId18"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="85">
   <si>
     <t>Dati originali</t>
   </si>
@@ -305,6 +306,9 @@
   </si>
   <si>
     <t>try</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFF </t>
   </si>
 </sst>
 </file>
@@ -640,13 +644,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -681,12 +685,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -721,7 +725,7 @@
         <v>0.69388866648871195</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -759,17 +763,17 @@
         <v>1.7506612507320798</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>74</v>
       </c>
@@ -804,12 +808,12 @@
         <v>1.7677669529663689</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
         <v>74</v>
       </c>
@@ -844,7 +848,7 @@
         <v>3.1819805153394638</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>54</v>
       </c>
@@ -879,7 +883,7 @@
         <v>0.87589712135373932</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>82</v>
       </c>
@@ -913,514 +917,584 @@
       <c r="P11">
         <v>1.3402597868683128</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="R11">
+        <v>16</v>
+      </c>
+      <c r="S11">
+        <v>1.1547005383792515</v>
+      </c>
+      <c r="T11">
+        <v>19.5</v>
+      </c>
+      <c r="U11">
+        <v>2.0816659994661326</v>
+      </c>
+      <c r="V11">
+        <v>30.875</v>
+      </c>
+      <c r="W11">
+        <v>2.5289984842489197</v>
+      </c>
+      <c r="X11">
+        <v>22.125000000000004</v>
+      </c>
+      <c r="Y11">
+        <v>0.41666666666666685</v>
+      </c>
+      <c r="Z11">
+        <v>6.1250000000000009</v>
+      </c>
+      <c r="AA11">
+        <v>0.97539165922663384</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13">
+        <v>16</v>
+      </c>
+      <c r="H13">
+        <v>1.1547005383792515</v>
+      </c>
+      <c r="I13">
+        <v>19.5</v>
+      </c>
+      <c r="J13">
+        <v>2.0816659994661326</v>
+      </c>
+      <c r="K13">
+        <v>30.875</v>
+      </c>
+      <c r="L13">
+        <v>2.5289984842489197</v>
+      </c>
+      <c r="M13">
+        <v>22.125000000000004</v>
+      </c>
+      <c r="N13">
+        <v>0.41666666666666685</v>
+      </c>
+      <c r="O13">
+        <v>6.1250000000000009</v>
+      </c>
+      <c r="P13">
+        <v>0.97539165922663384</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
         <v>4</v>
       </c>
-      <c r="G13">
+      <c r="G15">
         <v>17.149999999999999</v>
       </c>
-      <c r="H13">
+      <c r="H15">
         <v>1.8715709384839754</v>
       </c>
-      <c r="I13">
+      <c r="I15">
         <v>21</v>
       </c>
-      <c r="J13">
+      <c r="J15">
         <v>2.4832774042918899</v>
       </c>
-      <c r="K13">
+      <c r="K15">
         <v>31.5</v>
       </c>
-      <c r="L13">
+      <c r="L15">
         <v>3.3499585403736298</v>
       </c>
-      <c r="M13">
+      <c r="M15">
         <v>23.216666666666669</v>
       </c>
-      <c r="N13">
+      <c r="N15">
         <v>1.8510090674821758</v>
       </c>
-      <c r="O13">
+      <c r="O15">
         <v>6.2666666666666657</v>
       </c>
-      <c r="P13">
+      <c r="P15">
         <v>1.354462218459632</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F17" t="s">
         <v>20</v>
       </c>
-      <c r="G15">
+      <c r="G17">
         <v>17</v>
       </c>
-      <c r="H15">
+      <c r="H17">
         <v>2.8771127502720115</v>
       </c>
-      <c r="I15">
+      <c r="I17">
         <v>19.95</v>
       </c>
-      <c r="J15">
+      <c r="J17">
         <v>1.6741498671796915</v>
       </c>
-      <c r="K15">
+      <c r="K17">
         <v>29.75</v>
       </c>
-      <c r="L15">
+      <c r="L17">
         <v>2.226731535981231</v>
       </c>
-      <c r="M15">
+      <c r="M17">
         <v>22.233333333333327</v>
       </c>
-      <c r="N15">
+      <c r="N17">
         <v>1.3314801936840213</v>
       </c>
-      <c r="O15">
+      <c r="O17">
         <v>5.2833333333333341</v>
       </c>
-      <c r="P15">
+      <c r="P17">
         <v>1.777864581214158</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>4</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>14.214285714285714</v>
       </c>
-      <c r="H18">
+      <c r="H20">
         <v>2.0987524639084736</v>
       </c>
-      <c r="I18">
+      <c r="I20">
         <v>23</v>
       </c>
-      <c r="J18">
+      <c r="J20">
         <v>2.5495097567963922</v>
       </c>
-      <c r="K18">
+      <c r="K20">
         <v>31.428571428571427</v>
       </c>
-      <c r="L18">
+      <c r="L20">
         <v>5.2870011303555522</v>
       </c>
-      <c r="M18">
+      <c r="M20">
         <v>22.88095238095238</v>
       </c>
-      <c r="N18">
+      <c r="N20">
         <v>2.2601914981845255</v>
       </c>
-      <c r="O18">
+      <c r="O20">
         <v>8.6666666666666661</v>
       </c>
-      <c r="P18">
+      <c r="P20">
         <v>2.0971762320196583</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19">
-        <v>14.916666666666666</v>
-      </c>
-      <c r="H19">
-        <v>2.1775368347439388</v>
-      </c>
-      <c r="I19">
-        <v>20.416666666666668</v>
-      </c>
-      <c r="J19">
-        <v>2.4983327774071045</v>
-      </c>
-      <c r="K19">
-        <v>26.416666666666668</v>
-      </c>
-      <c r="L19">
-        <v>1.4288690166235207</v>
-      </c>
-      <c r="M19">
-        <v>20.583333333333332</v>
-      </c>
-      <c r="N19">
-        <v>1.0368220676663862</v>
-      </c>
-      <c r="O19">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="P19">
-        <v>1.7224014243685055</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>71</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
       </c>
       <c r="G21">
+        <v>14.916666666666666</v>
+      </c>
+      <c r="H21">
+        <v>2.1775368347439388</v>
+      </c>
+      <c r="I21">
+        <v>20.416666666666668</v>
+      </c>
+      <c r="J21">
+        <v>2.4983327774071045</v>
+      </c>
+      <c r="K21">
+        <v>26.416666666666668</v>
+      </c>
+      <c r="L21">
+        <v>1.4288690166235207</v>
+      </c>
+      <c r="M21">
+        <v>20.583333333333332</v>
+      </c>
+      <c r="N21">
+        <v>1.0368220676663862</v>
+      </c>
+      <c r="O21">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="P21">
+        <v>1.7224014243685055</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23">
         <v>18.7</v>
       </c>
-      <c r="H21">
+      <c r="H23">
         <v>2.7748873851023195</v>
       </c>
-      <c r="I21">
+      <c r="I23">
         <v>18.5</v>
       </c>
-      <c r="J21">
+      <c r="J23">
         <v>1.541103500742244</v>
       </c>
-      <c r="K21">
+      <c r="K23">
         <v>27.5</v>
       </c>
-      <c r="L21">
+      <c r="L23">
         <v>1.2247448713915889</v>
       </c>
-      <c r="M21">
+      <c r="M23">
         <v>21.566666666666666</v>
       </c>
-      <c r="N21">
+      <c r="N23">
         <v>1.4841757907262121</v>
       </c>
-      <c r="O21">
+      <c r="O23">
         <v>3.9666666666666663</v>
       </c>
-      <c r="P21">
+      <c r="P23">
         <v>0.74907350180814036</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F22" t="s">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
         <v>81</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>16.5</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>0.70710678118654757</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>17.25</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>3.378855822118882</v>
       </c>
-      <c r="K22">
+      <c r="K24">
         <v>31.25</v>
       </c>
-      <c r="L22">
+      <c r="L24">
         <v>3.1754264805429417</v>
       </c>
-      <c r="M22">
+      <c r="M24">
         <v>21.6666666666667</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>2.2730302828309759</v>
       </c>
-      <c r="O22">
+      <c r="O24">
         <v>5.7916666666666679</v>
       </c>
-      <c r="P22">
+      <c r="P24">
         <v>1.6007810593582092</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
         <v>71</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>15.625</v>
       </c>
-      <c r="H24">
+      <c r="H26">
         <v>1.6007810593582121</v>
       </c>
-      <c r="I24">
+      <c r="I26">
         <v>18.625</v>
       </c>
-      <c r="J24">
+      <c r="J26">
         <v>2.75</v>
       </c>
-      <c r="K24">
+      <c r="K26">
         <v>26.625</v>
       </c>
-      <c r="L24">
+      <c r="L26">
         <v>4.6435439052516774</v>
       </c>
-      <c r="M24">
+      <c r="M26">
         <v>20.291666666666668</v>
       </c>
-      <c r="N24">
+      <c r="N26">
         <v>1.8923579255834544</v>
       </c>
-      <c r="O24">
+      <c r="O26">
         <v>4.791666666666667</v>
       </c>
-      <c r="P24">
+      <c r="P26">
         <v>1.7393858004948073</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F25" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
         <v>81</v>
       </c>
-      <c r="G25">
+      <c r="G27">
         <v>14.875</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>4.0697051490249265</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>16.5</v>
       </c>
-      <c r="J25">
+      <c r="J27">
         <v>2.2730302828309759</v>
       </c>
-      <c r="K25">
+      <c r="K27">
         <v>27</v>
       </c>
-      <c r="L25">
+      <c r="L27">
         <v>3.3416562759605704</v>
       </c>
-      <c r="M25">
+      <c r="M27">
         <v>19.458333333333332</v>
       </c>
-      <c r="N25">
+      <c r="N27">
         <v>2.1273135553939757</v>
       </c>
-      <c r="O25">
+      <c r="O27">
         <v>5.2083333333333304</v>
       </c>
-      <c r="P25">
+      <c r="P27">
         <v>1.674288129546627</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>4</v>
       </c>
-      <c r="G27">
+      <c r="G29">
         <v>16.416666666666668</v>
       </c>
-      <c r="H27">
+      <c r="H29">
         <v>2.8881943609574914</v>
       </c>
-      <c r="I27">
+      <c r="I29">
         <v>15.416666666666666</v>
       </c>
-      <c r="J27">
+      <c r="J29">
         <v>1.2812754062521714</v>
       </c>
-      <c r="K27">
+      <c r="K29">
         <v>29.916666666666668</v>
       </c>
-      <c r="L27">
+      <c r="L29">
         <v>2.437553418218084</v>
       </c>
-      <c r="M27">
+      <c r="M29">
         <v>20.583333333333332</v>
       </c>
-      <c r="N27">
+      <c r="N29">
         <v>1.3570801990548194</v>
       </c>
-      <c r="O27">
+      <c r="O29">
         <v>5.916666666666667</v>
       </c>
-      <c r="P27">
+      <c r="P29">
         <v>1.0527741131569135</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>71</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F30" t="s">
         <v>20</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>16.8</v>
       </c>
-      <c r="H28">
+      <c r="H30">
         <v>0.57008771254956903</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>17.7</v>
       </c>
-      <c r="J28">
+      <c r="J30">
         <v>1.7175564037317668</v>
       </c>
-      <c r="K28">
+      <c r="K30">
         <v>28.9</v>
       </c>
-      <c r="L28">
+      <c r="L30">
         <v>3.8794329482541587</v>
       </c>
-      <c r="M28">
+      <c r="M30">
         <v>21.133333333333333</v>
       </c>
-      <c r="N28">
+      <c r="N30">
         <v>1.5696779570628134</v>
       </c>
-      <c r="O28">
+      <c r="O30">
         <v>4.7333333333333325</v>
       </c>
-      <c r="P28">
+      <c r="P30">
         <v>0.90215790684828923</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
         <v>71</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>81</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>16</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>0</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>15.75</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>4.5961940777125587</v>
       </c>
-      <c r="K31">
+      <c r="K33">
         <v>30</v>
       </c>
-      <c r="L31">
+      <c r="L33">
         <v>3.5355339059327378</v>
       </c>
-      <c r="M31">
+      <c r="M33">
         <v>20.583333333333332</v>
       </c>
-      <c r="N31">
+      <c r="N33">
         <v>0.35355339059327379</v>
       </c>
-      <c r="O31">
+      <c r="O33">
         <v>6.3333333333333321</v>
       </c>
-      <c r="P31">
+      <c r="P33">
         <v>2.1213203435596459</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D32" t="s">
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E33" t="s">
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
         <v>71</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>16.375</v>
       </c>
-      <c r="H33">
+      <c r="H35">
         <v>3.3008837200563934</v>
       </c>
-      <c r="I33">
+      <c r="I35">
         <v>20</v>
       </c>
-      <c r="J33">
+      <c r="J35">
         <v>3.3166247903553998</v>
       </c>
-      <c r="K33">
+      <c r="K35">
         <v>26.875</v>
       </c>
-      <c r="L33">
+      <c r="L35">
         <v>1.796988221070652</v>
       </c>
-      <c r="M33">
+      <c r="M35">
         <v>21.083333333333332</v>
       </c>
-      <c r="N33">
+      <c r="N35">
         <v>1.5898986690282424</v>
       </c>
-      <c r="O33">
+      <c r="O35">
         <v>4.708333333333333</v>
       </c>
-      <c r="P33">
+      <c r="P35">
         <v>2.9071272570854019</v>
       </c>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="F34" t="s">
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
         <v>81</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <v>14.333333333333334</v>
       </c>
-      <c r="H34">
+      <c r="H36">
         <v>3.2145502536643153</v>
       </c>
-      <c r="I34">
+      <c r="I36">
         <v>17.166666666666668</v>
       </c>
-      <c r="J34">
+      <c r="J36">
         <v>1.2583057392117916</v>
       </c>
-      <c r="K34">
+      <c r="K36">
         <v>26.6666666666667</v>
       </c>
-      <c r="L34">
+      <c r="L36">
         <v>4.1633319989322564</v>
       </c>
-      <c r="M34">
+      <c r="M36">
         <v>19.3888888888889</v>
       </c>
-      <c r="N34">
+      <c r="N36">
         <v>2.4962935487400935</v>
       </c>
-      <c r="O34">
+      <c r="O36">
         <v>5.0555555555555562</v>
       </c>
-      <c r="P34">
+      <c r="P36">
         <v>1.3977495139343468</v>
       </c>
     </row>
@@ -1431,6 +1505,785 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>85</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="G4">
+        <v>72</v>
+      </c>
+      <c r="H4">
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>68</v>
+      </c>
+      <c r="M4">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>25</v>
+      </c>
+      <c r="O4">
+        <v>75</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>20</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q9)</f>
+        <v>14.916666666666666</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q9)</f>
+        <v>2.1775368347439388</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R9)</f>
+        <v>20.416666666666668</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R9)</f>
+        <v>2.4983327774071045</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S9)</f>
+        <v>26.416666666666668</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S9)</f>
+        <v>1.4288690166235207</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T9)</f>
+        <v>20.583333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T9)</f>
+        <v>1.0368220676663862</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD4">
+        <f>(T4-AC4)</f>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD9)</f>
+        <v>5.666666666666667</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD9)</f>
+        <v>1.7224014243685055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>88</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>95</v>
+      </c>
+      <c r="L5">
+        <v>67</v>
+      </c>
+      <c r="M5">
+        <v>33</v>
+      </c>
+      <c r="N5">
+        <v>18</v>
+      </c>
+      <c r="O5">
+        <v>82</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>16</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>17</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
+        <v>16</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD9" si="5">(T5-AC5)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>92</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>79</v>
+      </c>
+      <c r="G6">
+        <v>78</v>
+      </c>
+      <c r="H6">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>85</v>
+      </c>
+      <c r="L6">
+        <v>62</v>
+      </c>
+      <c r="M6">
+        <v>38</v>
+      </c>
+      <c r="N6">
+        <v>18</v>
+      </c>
+      <c r="O6">
+        <v>82</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>5.8333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>81</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>87</v>
+      </c>
+      <c r="G7">
+        <v>65</v>
+      </c>
+      <c r="H7">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>67</v>
+      </c>
+      <c r="M7">
+        <v>33</v>
+      </c>
+      <c r="N7">
+        <v>18</v>
+      </c>
+      <c r="O7">
+        <v>82</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>84</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <v>92</v>
+      </c>
+      <c r="L8">
+        <v>66</v>
+      </c>
+      <c r="M8">
+        <v>34</v>
+      </c>
+      <c r="N8">
+        <v>17</v>
+      </c>
+      <c r="O8">
+        <v>83</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>91</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>84</v>
+      </c>
+      <c r="G9">
+        <v>66</v>
+      </c>
+      <c r="H9">
+        <v>34</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="L9">
+        <v>68</v>
+      </c>
+      <c r="M9">
+        <v>32</v>
+      </c>
+      <c r="N9">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>81</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>75</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>92</v>
+      </c>
+      <c r="L11">
+        <v>67</v>
+      </c>
+      <c r="M11">
+        <v>33</v>
+      </c>
+      <c r="N11">
+        <v>27</v>
+      </c>
+      <c r="O11">
+        <v>73</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ref="Q11:Q14" si="6">AVERAGE(C11,D11)</f>
+        <v>17</v>
+      </c>
+      <c r="R11">
+        <f t="shared" ref="R11:R14" si="7">AVERAGE(H11,I11)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" ref="S11:S14" si="8">AVERAGE(M11,N11)</f>
+        <v>30</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ref="T11:T14" si="9">AVERAGE(Q11:S11)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f>AVERAGE(Q11:Q16)</f>
+        <v>16.5</v>
+      </c>
+      <c r="V11">
+        <f>_xlfn.STDEV.S(Q11:Q16)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W11">
+        <f>AVERAGE(R11:R16)</f>
+        <v>17.25</v>
+      </c>
+      <c r="X11">
+        <f>_xlfn.STDEV.S(R11:R16)</f>
+        <v>3.378855822118882</v>
+      </c>
+      <c r="Y11">
+        <f>AVERAGE(S11:S16)</f>
+        <v>31.25</v>
+      </c>
+      <c r="Z11">
+        <f>_xlfn.STDEV.S(S11:S16)</f>
+        <v>3.1754264805429417</v>
+      </c>
+      <c r="AA11">
+        <f>AVERAGE(T11:T16)</f>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AB11">
+        <f>_xlfn.STDEV.S(T11:T16)</f>
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" ref="AC11:AC14" si="10">MIN(Q11:S11)</f>
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" ref="AD11:AD14" si="11">(T11-AC11)</f>
+        <v>4.6666666666666679</v>
+      </c>
+      <c r="AE11">
+        <f>AVERAGE(AD11:AD16)</f>
+        <v>5.7916666666666679</v>
+      </c>
+      <c r="AF11">
+        <f>_xlfn.STDEV.S(AD11:AD16)</f>
+        <v>1.6007810593582092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>72</v>
+      </c>
+      <c r="G12">
+        <v>67</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12">
+        <v>89</v>
+      </c>
+      <c r="L12">
+        <v>65</v>
+      </c>
+      <c r="M12">
+        <v>35</v>
+      </c>
+      <c r="N12">
+        <v>36</v>
+      </c>
+      <c r="O12">
+        <v>64</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>16.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>35.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>8.1666666666666679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>87</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>82</v>
+      </c>
+      <c r="G13">
+        <v>76</v>
+      </c>
+      <c r="H13">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>96</v>
+      </c>
+      <c r="L13">
+        <v>70</v>
+      </c>
+      <c r="M13">
+        <v>30</v>
+      </c>
+      <c r="N13">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>15.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>5.1666666666666679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>80</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>86</v>
+      </c>
+      <c r="G14">
+        <v>71</v>
+      </c>
+      <c r="H14">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>96</v>
+      </c>
+      <c r="L14">
+        <v>62</v>
+      </c>
+      <c r="M14">
+        <v>38</v>
+      </c>
+      <c r="N14">
+        <v>25</v>
+      </c>
+      <c r="O14">
+        <v>75</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>5.1666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1981,7 +2834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2470,7 +3323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AO99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5309,7 +6162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6041,7 +6894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6896,7 +7749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AN41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8333,7 +9186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AL41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9410,7 +10263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10199,6 +11052,11 @@
         <v>6.3333333333333321</v>
       </c>
     </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
@@ -11946,7 +12804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12245,6 +13103,354 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B1D148-F1AF-4FC9-8C19-77A1A130E3CB}">
+  <dimension ref="B2:AF7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="G4">
+        <v>72</v>
+      </c>
+      <c r="H4">
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="L4">
+        <v>66</v>
+      </c>
+      <c r="M4">
+        <v>34</v>
+      </c>
+      <c r="N4">
+        <v>26</v>
+      </c>
+      <c r="O4">
+        <v>74</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>17</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>19</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>30</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>22</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>16</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>1.1547005383792515</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R7)</f>
+        <v>19.5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>2.0816659994661326</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S7)</f>
+        <v>30.875</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>2.5289984842489197</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>22.125000000000004</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>0.41666666666666685</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>17</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>6.1250000000000009</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>0.97539165922663384</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>89</v>
+      </c>
+      <c r="G5">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>89</v>
+      </c>
+      <c r="L5">
+        <v>55</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+      <c r="N5">
+        <v>18</v>
+      </c>
+      <c r="O5">
+        <v>82</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5:D5)</f>
+        <v>15</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5:I5)</f>
+        <v>20</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5:N5)</f>
+        <v>31.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
+        <v>15</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>84</v>
+      </c>
+      <c r="G6">
+        <v>69</v>
+      </c>
+      <c r="H6">
+        <v>31</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>97</v>
+      </c>
+      <c r="L6">
+        <v>53</v>
+      </c>
+      <c r="M6">
+        <v>47</v>
+      </c>
+      <c r="N6">
+        <v>21</v>
+      </c>
+      <c r="O6">
+        <v>79</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>5.6666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>86</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>84</v>
+      </c>
+      <c r="G7">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>65</v>
+      </c>
+      <c r="M7">
+        <v>35</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+      <c r="O7">
+        <v>79</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>6.6666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12902,7 +14108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1341680-B8DF-484F-AD8E-90C5FE6FD057}">
   <dimension ref="B1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13126,7 +14332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13292,7 +14498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13888,7 +15094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14312,7 +15518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -15950,7 +17156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16111,783 +17317,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" t="s">
-        <v>15</v>
-      </c>
-      <c r="U2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>85</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>90</v>
-      </c>
-      <c r="G4">
-        <v>72</v>
-      </c>
-      <c r="H4">
-        <v>28</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>88</v>
-      </c>
-      <c r="L4">
-        <v>68</v>
-      </c>
-      <c r="M4">
-        <v>32</v>
-      </c>
-      <c r="N4">
-        <v>25</v>
-      </c>
-      <c r="O4">
-        <v>75</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>20</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>28.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q9)</f>
-        <v>14.916666666666666</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>2.1775368347439388</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R9)</f>
-        <v>20.416666666666668</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>2.4983327774071045</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S9)</f>
-        <v>26.416666666666668</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>1.4288690166235207</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T9)</f>
-        <v>20.583333333333332</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>1.0368220676663862</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="AD4">
-        <f>(T4-AC4)</f>
-        <v>7.8333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>5.666666666666667</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>1.7224014243685055</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>88</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>80</v>
-      </c>
-      <c r="G5">
-        <v>71</v>
-      </c>
-      <c r="H5">
-        <v>29</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>95</v>
-      </c>
-      <c r="L5">
-        <v>67</v>
-      </c>
-      <c r="M5">
-        <v>33</v>
-      </c>
-      <c r="N5">
-        <v>18</v>
-      </c>
-      <c r="O5">
-        <v>82</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>16</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>17</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>25.5</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>19.5</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>16</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD9" si="5">(T5-AC5)</f>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>92</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>79</v>
-      </c>
-      <c r="G6">
-        <v>78</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>85</v>
-      </c>
-      <c r="L6">
-        <v>62</v>
-      </c>
-      <c r="M6">
-        <v>38</v>
-      </c>
-      <c r="N6">
-        <v>18</v>
-      </c>
-      <c r="O6">
-        <v>82</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>14.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>18.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>14.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>5.8333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>81</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>87</v>
-      </c>
-      <c r="G7">
-        <v>65</v>
-      </c>
-      <c r="H7">
-        <v>35</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>93</v>
-      </c>
-      <c r="L7">
-        <v>67</v>
-      </c>
-      <c r="M7">
-        <v>33</v>
-      </c>
-      <c r="N7">
-        <v>18</v>
-      </c>
-      <c r="O7">
-        <v>82</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>20.833333333333332</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>4.8333333333333321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>80</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>84</v>
-      </c>
-      <c r="G8">
-        <v>60</v>
-      </c>
-      <c r="H8">
-        <v>40</v>
-      </c>
-      <c r="I8">
-        <v>8</v>
-      </c>
-      <c r="J8">
-        <v>92</v>
-      </c>
-      <c r="L8">
-        <v>66</v>
-      </c>
-      <c r="M8">
-        <v>34</v>
-      </c>
-      <c r="N8">
-        <v>17</v>
-      </c>
-      <c r="O8">
-        <v>83</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>22.5</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>91</v>
-      </c>
-      <c r="C9">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
-      <c r="G9">
-        <v>66</v>
-      </c>
-      <c r="H9">
-        <v>34</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-      <c r="L9">
-        <v>68</v>
-      </c>
-      <c r="M9">
-        <v>32</v>
-      </c>
-      <c r="N9">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>81</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>86</v>
-      </c>
-      <c r="C11">
-        <v>14</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11">
-        <v>80</v>
-      </c>
-      <c r="G11">
-        <v>75</v>
-      </c>
-      <c r="H11">
-        <v>25</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>92</v>
-      </c>
-      <c r="L11">
-        <v>67</v>
-      </c>
-      <c r="M11">
-        <v>33</v>
-      </c>
-      <c r="N11">
-        <v>27</v>
-      </c>
-      <c r="O11">
-        <v>73</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" ref="Q11:Q14" si="6">AVERAGE(C11,D11)</f>
-        <v>17</v>
-      </c>
-      <c r="R11">
-        <f t="shared" ref="R11:R14" si="7">AVERAGE(H11,I11)</f>
-        <v>16.5</v>
-      </c>
-      <c r="S11">
-        <f t="shared" ref="S11:S14" si="8">AVERAGE(M11,N11)</f>
-        <v>30</v>
-      </c>
-      <c r="T11">
-        <f t="shared" ref="T11:T14" si="9">AVERAGE(Q11:S11)</f>
-        <v>21.166666666666668</v>
-      </c>
-      <c r="U11">
-        <f>AVERAGE(Q11:Q16)</f>
-        <v>16.5</v>
-      </c>
-      <c r="V11">
-        <f>_xlfn.STDEV.S(Q11:Q16)</f>
-        <v>0.70710678118654757</v>
-      </c>
-      <c r="W11">
-        <f>AVERAGE(R11:R16)</f>
-        <v>17.25</v>
-      </c>
-      <c r="X11">
-        <f>_xlfn.STDEV.S(R11:R16)</f>
-        <v>3.378855822118882</v>
-      </c>
-      <c r="Y11">
-        <f>AVERAGE(S11:S16)</f>
-        <v>31.25</v>
-      </c>
-      <c r="Z11">
-        <f>_xlfn.STDEV.S(S11:S16)</f>
-        <v>3.1754264805429417</v>
-      </c>
-      <c r="AA11">
-        <f>AVERAGE(T11:T16)</f>
-        <v>21.666666666666668</v>
-      </c>
-      <c r="AB11">
-        <f>_xlfn.STDEV.S(T11:T16)</f>
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="AC11">
-        <f t="shared" ref="AC11:AC14" si="10">MIN(Q11:S11)</f>
-        <v>16.5</v>
-      </c>
-      <c r="AD11">
-        <f t="shared" ref="AD11:AD14" si="11">(T11-AC11)</f>
-        <v>4.6666666666666679</v>
-      </c>
-      <c r="AE11">
-        <f>AVERAGE(AD11:AD16)</f>
-        <v>5.7916666666666679</v>
-      </c>
-      <c r="AF11">
-        <f>_xlfn.STDEV.S(AD11:AD16)</f>
-        <v>1.6007810593582092</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>95</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12">
-        <v>28</v>
-      </c>
-      <c r="E12">
-        <v>72</v>
-      </c>
-      <c r="G12">
-        <v>67</v>
-      </c>
-      <c r="H12">
-        <v>33</v>
-      </c>
-      <c r="I12">
-        <v>11</v>
-      </c>
-      <c r="J12">
-        <v>89</v>
-      </c>
-      <c r="L12">
-        <v>65</v>
-      </c>
-      <c r="M12">
-        <v>35</v>
-      </c>
-      <c r="N12">
-        <v>36</v>
-      </c>
-      <c r="O12">
-        <v>64</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="6"/>
-        <v>16.5</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="8"/>
-        <v>35.5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="9"/>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="AC12">
-        <f t="shared" si="10"/>
-        <v>16.5</v>
-      </c>
-      <c r="AD12">
-        <f t="shared" si="11"/>
-        <v>8.1666666666666679</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>87</v>
-      </c>
-      <c r="C13">
-        <v>13</v>
-      </c>
-      <c r="D13">
-        <v>18</v>
-      </c>
-      <c r="E13">
-        <v>82</v>
-      </c>
-      <c r="G13">
-        <v>76</v>
-      </c>
-      <c r="H13">
-        <v>24</v>
-      </c>
-      <c r="I13">
-        <v>4</v>
-      </c>
-      <c r="J13">
-        <v>96</v>
-      </c>
-      <c r="L13">
-        <v>70</v>
-      </c>
-      <c r="M13">
-        <v>30</v>
-      </c>
-      <c r="N13">
-        <v>26</v>
-      </c>
-      <c r="O13">
-        <v>74</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="6"/>
-        <v>15.5</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="9"/>
-        <v>19.166666666666668</v>
-      </c>
-      <c r="AC13">
-        <f t="shared" si="10"/>
-        <v>14</v>
-      </c>
-      <c r="AD13">
-        <f t="shared" si="11"/>
-        <v>5.1666666666666679</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>80</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-      <c r="D14">
-        <v>14</v>
-      </c>
-      <c r="E14">
-        <v>86</v>
-      </c>
-      <c r="G14">
-        <v>71</v>
-      </c>
-      <c r="H14">
-        <v>29</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
-      </c>
-      <c r="J14">
-        <v>96</v>
-      </c>
-      <c r="L14">
-        <v>62</v>
-      </c>
-      <c r="M14">
-        <v>38</v>
-      </c>
-      <c r="N14">
-        <v>25</v>
-      </c>
-      <c r="O14">
-        <v>75</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>17</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="7"/>
-        <v>16.5</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="8"/>
-        <v>31.5</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="9"/>
-        <v>21.666666666666668</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="10"/>
-        <v>16.5</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="11"/>
-        <v>5.1666666666666679</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>